--- a/public/adsplay/plano-nfl.xlsx
+++ b/public/adsplay/plano-nfl.xlsx
@@ -40,22 +40,22 @@
     <t>Investimento Líquido Total</t>
   </si>
   <si>
+    <t>Investimento Total</t>
+  </si>
+  <si>
     <t>Investimento Bruto Total</t>
   </si>
   <si>
-    <t>Investimento Total</t>
+    <t>Investimento Mensal</t>
+  </si>
+  <si>
+    <t>Brand Safety/Brand Suitability | O algoritmo de Brand Safety protege a marca de 95% dos riscos de exposição a conteúdos prejudiciais. Com Brand Suitability, além de evitar conteúdos impróprios, os anúncios são posicionados em contextos que refletem os valores da marca, garantindo uma comunicação segura e alinhada.</t>
   </si>
   <si>
     <t>Investimento Líquido Mensal</t>
   </si>
   <si>
-    <t>Investimento Mensal</t>
-  </si>
-  <si>
     <t>Investimento Bruto Mensal</t>
-  </si>
-  <si>
-    <t>Brand Safety/Brand Suitability | O algoritmo de Brand Safety protege a marca de 95% dos riscos de exposição a conteúdos prejudiciais. Com Brand Suitability, além de evitar conteúdos impróprios, os anúncios são posicionados em contextos que refletem os valores da marca, garantindo uma comunicação segura e alinhada.</t>
   </si>
   <si>
     <t>PROGRAMÁTICA DISPLAY</t>
@@ -309,46 +309,67 @@
     <t>SLA DA CAMPANHA</t>
   </si>
   <si>
+    <t>CAMPANHA - ENTERPRISE 3</t>
+  </si>
+  <si>
+    <t>Alinhamento com o time de CS</t>
+  </si>
+  <si>
+    <t>Até 8 horas</t>
+  </si>
+  <si>
+    <t>Quantidade de Peças</t>
+  </si>
+  <si>
+    <t>Troca de Peças</t>
+  </si>
+  <si>
+    <t>2 por mês</t>
+  </si>
+  <si>
+    <t>Tempo de Subida</t>
+  </si>
+  <si>
+    <t>48 horas</t>
+  </si>
+  <si>
+    <t>Atualização de Relatório</t>
+  </si>
+  <si>
+    <t>Diário</t>
+  </si>
+  <si>
+    <t>Análise de BI</t>
+  </si>
+  <si>
+    <t>Semanal</t>
+  </si>
+  <si>
+    <t>Análise de GA</t>
+  </si>
+  <si>
+    <t>Quinzenal</t>
+  </si>
+  <si>
     <t>CAMPANHA - ENTERPRISE 1</t>
   </si>
   <si>
-    <t>Alinhamento com o time de CS</t>
-  </si>
-  <si>
     <t>Até 4 horas</t>
   </si>
   <si>
-    <t>Quantidade de Peças</t>
-  </si>
-  <si>
     <t>24+</t>
   </si>
   <si>
-    <t>Troca de Peças</t>
+    <t>CAMPANHA - ENTERPRISE 2</t>
   </si>
   <si>
     <t>4 por mês</t>
   </si>
   <si>
-    <t>Tempo de Subida</t>
-  </si>
-  <si>
     <t>24 horas</t>
   </si>
   <si>
-    <t>Atualização de Relatório</t>
-  </si>
-  <si>
-    <t>Diário</t>
-  </si>
-  <si>
-    <t>Análise de BI</t>
-  </si>
-  <si>
-    <t>Semanal</t>
-  </si>
-  <si>
-    <t>Análise de GA</t>
+    <t>3 por mês</t>
   </si>
   <si>
     <t>CAMPANHA - STARTER 6</t>
@@ -357,100 +378,103 @@
     <t>Até 24 horas</t>
   </si>
   <si>
-    <t>CAMPANHA - ENTERPRISE 2</t>
-  </si>
-  <si>
-    <t>2 por mês</t>
-  </si>
-  <si>
-    <t>Até 8 horas</t>
-  </si>
-  <si>
     <t>72 horas</t>
   </si>
   <si>
-    <t>3 por mês</t>
-  </si>
-  <si>
-    <t>CAMPANHA - ENTERPRISE 3</t>
-  </si>
-  <si>
-    <t>48 horas</t>
+    <t>Adsplay Mídia Ltda</t>
+  </si>
+  <si>
+    <t>AUDIÊNCIAS — METLIFE | Campanha NFL | Mídia Programática DV360</t>
+  </si>
+  <si>
+    <t>PI NÚMERO</t>
+  </si>
+  <si>
+    <t>CNPJ 29.835.275/0001-27</t>
   </si>
   <si>
     <t>Mensal</t>
   </si>
   <si>
-    <t>Quinzenal</t>
-  </si>
-  <si>
-    <t>Adsplay Mídia Ltda</t>
-  </si>
-  <si>
-    <t>PI NÚMERO</t>
-  </si>
-  <si>
-    <t>AUDIÊNCIAS — METLIFE | Campanha NFL | Mídia Programática DV360</t>
+    <t>Segmentos de audiência para ativação via DV360 | Foco: NFL, New York Giants e New York Jets | ADSPLAY 2026</t>
+  </si>
+  <si>
+    <t>#</t>
+  </si>
+  <si>
+    <t>Segmento / Audiência</t>
+  </si>
+  <si>
+    <t>Tipo</t>
+  </si>
+  <si>
+    <t>Fonte / DMP</t>
+  </si>
+  <si>
+    <t>Descrição do Público</t>
+  </si>
+  <si>
+    <t>Prioridade</t>
+  </si>
+  <si>
+    <t>1. 3RD PARTY — DEMOGRÁFICO E PROFISSIONAL</t>
   </si>
   <si>
     <t>WISHLIST DE SITES — METLIFE | Campanha NFL | Mídia Programática DV360</t>
   </si>
   <si>
-    <t>CNPJ 29.835.275/0001-27</t>
-  </si>
-  <si>
     <t>Rua Fernão Dias, 110, Pinheiros - SP - CEP 05427-000</t>
   </si>
   <si>
+    <t>Millennials e Gen Z Alta Renda (18–39)</t>
+  </si>
+  <si>
     <t>11 3031 0240</t>
   </si>
   <si>
+    <t>3rd Party</t>
+  </si>
+  <si>
+    <t>Serasa Experian</t>
+  </si>
+  <si>
+    <t>Homens e mulheres 18–39 anos, classe A/B, com padrão de consumo digital elevado — perfil-base da campanha.</t>
+  </si>
+  <si>
     <t>EMITIDO EM:</t>
   </si>
   <si>
+    <t>Alta</t>
+  </si>
+  <si>
+    <t>Domínios para targeting de inventário via Google AdX | Foco: NFL, New York Giants e New York Jets | ADSPLAY 2026</t>
+  </si>
+  <si>
+    <t>Site / Domínio</t>
+  </si>
+  <si>
+    <t>Categoria</t>
+  </si>
+  <si>
+    <t>Perfil da Audiência</t>
+  </si>
+  <si>
+    <t>Relevância para o Target</t>
+  </si>
+  <si>
+    <t>Executivos, Gestores e Especialistas</t>
+  </si>
+  <si>
+    <t>1. NFL OFICIAL E PORTAIS GLOBAIS</t>
+  </si>
+  <si>
     <t>PEDIDO DE INSERÇÃO</t>
   </si>
   <si>
-    <t>Segmentos de audiência para ativação via DV360 | Foco: NFL, New York Giants e New York Jets | ADSPLAY 2026</t>
-  </si>
-  <si>
-    <t>#</t>
-  </si>
-  <si>
-    <t>Domínios para targeting de inventário via Google AdX | Foco: NFL, New York Giants e New York Jets | ADSPLAY 2026</t>
-  </si>
-  <si>
-    <t>Segmento / Audiência</t>
-  </si>
-  <si>
-    <t>Tipo</t>
-  </si>
-  <si>
-    <t>Fonte / DMP</t>
-  </si>
-  <si>
-    <t>Descrição do Público</t>
-  </si>
-  <si>
-    <t>Prioridade</t>
-  </si>
-  <si>
-    <t>1. 3RD PARTY — DEMOGRÁFICO E PROFISSIONAL</t>
-  </si>
-  <si>
-    <t>Site / Domínio</t>
-  </si>
-  <si>
-    <t>Categoria</t>
-  </si>
-  <si>
-    <t>Perfil da Audiência</t>
-  </si>
-  <si>
-    <t>Relevância para o Target</t>
-  </si>
-  <si>
-    <t>1. NFL OFICIAL E PORTAIS GLOBAIS</t>
+    <t>Navegg</t>
+  </si>
+  <si>
+    <t>Profissionais liberais e cargos de liderança em TI, finanças e negócios — alinhado ao perfil profissional do briefing.</t>
   </si>
   <si>
     <t>nfl.com</t>
@@ -465,24 +489,6 @@
     <t>Site oficial da liga, cobertura completa de todos os times e jogos.</t>
   </si>
   <si>
-    <t>Millennials e Gen Z Alta Renda (18–39)</t>
-  </si>
-  <si>
-    <t>3rd Party</t>
-  </si>
-  <si>
-    <t>Serasa Experian</t>
-  </si>
-  <si>
-    <t>Homens e mulheres 18–39 anos, classe A/B, com padrão de consumo digital elevado — perfil-base da campanha.</t>
-  </si>
-  <si>
-    <t>Alta</t>
-  </si>
-  <si>
-    <t>Executivos, Gestores e Especialistas</t>
-  </si>
-  <si>
     <t>giants.com</t>
   </si>
   <si>
@@ -492,51 +498,45 @@
     <t>Torcedores do New York Giants</t>
   </si>
   <si>
-    <t>Navegg</t>
-  </si>
-  <si>
     <t>Site oficial do New York Giants — audiência 100% aderente ao time foco.</t>
   </si>
   <si>
-    <t>Profissionais liberais e cargos de liderança em TI, finanças e negócios — alinhado ao perfil profissional do briefing.</t>
-  </si>
-  <si>
     <t>newyorkjets.com</t>
   </si>
   <si>
+    <t>Torcedores do New York Jets</t>
+  </si>
+  <si>
+    <t>Site oficial do New York Jets — audiência 100% aderente ao time foco.</t>
+  </si>
+  <si>
+    <t>espn.com</t>
+  </si>
+  <si>
     <t>Classe A/B Urbana Digitalizada</t>
   </si>
   <si>
-    <t>Torcedores do New York Jets</t>
+    <t>Esportes Global</t>
+  </si>
+  <si>
+    <t>Fãs de esportes americanos e NFL</t>
+  </si>
+  <si>
+    <t>Maior portal de esportes dos EUA, com cobertura intensa de NFL, Giants e Jets.</t>
   </si>
   <si>
     <t>Boa Vista</t>
   </si>
   <si>
-    <t>Site oficial do New York Jets — audiência 100% aderente ao time foco.</t>
-  </si>
-  <si>
     <t>Consumidores urbanos de alto poder aquisitivo, altamente conectados e consumidores de cultura global.</t>
   </si>
   <si>
-    <t>espn.com</t>
+    <t>si.com</t>
   </si>
   <si>
     <t>Média-Alta</t>
   </si>
   <si>
-    <t>Esportes Global</t>
-  </si>
-  <si>
-    <t>Fãs de esportes americanos e NFL</t>
-  </si>
-  <si>
-    <t>Maior portal de esportes dos EUA, com cobertura intensa de NFL, Giants e Jets.</t>
-  </si>
-  <si>
-    <t>si.com</t>
-  </si>
-  <si>
     <t>Fãs de esportes e cultura esportiva americana</t>
   </si>
   <si>
@@ -552,10 +552,13 @@
     <t>Retargetly</t>
   </si>
   <si>
+    <t>Base comportamental de consumo premium, cruzada com hábitos digitais e mobilidade urbana.</t>
+  </si>
+  <si>
     <t>ge.globo.com</t>
   </si>
   <si>
-    <t>Base comportamental de consumo premium, cruzada com hábitos digitais e mobilidade urbana.</t>
+    <t>2. B3 ADVANCED DATA ⭐</t>
   </si>
   <si>
     <t>Esportes BR</t>
@@ -567,94 +570,133 @@
     <t>Cobertura de NFL em português, com editoria dedicada à liga.</t>
   </si>
   <si>
-    <t>2. B3 ADVANCED DATA ⭐</t>
+    <t>Investidor PF Ativo — Renda R$10k+</t>
   </si>
   <si>
     <t>espn.com.br</t>
   </si>
   <si>
+    <t>B3 Advanced Data</t>
+  </si>
+  <si>
+    <t>B3 (Bolsa de Valores)</t>
+  </si>
+  <si>
+    <t>Investidores pessoa física ativos na bolsa, com renda declarada a partir de R$10 mil — alto poder de decisão financeira.</t>
+  </si>
+  <si>
     <t>Versão brasileira da ESPN, com cobertura de NFL e do jogo da liga no país.</t>
   </si>
   <si>
+    <t>Renda Declarada Acima de R$30k</t>
+  </si>
+  <si>
     <t>uol.com.br/esporte</t>
   </si>
   <si>
+    <t>Faixa de renda mais alta da base B3, aderente ao público A/B do briefing e a produtos de seguro/proteção patrimonial.</t>
+  </si>
+  <si>
     <t>Público brasileiro fã de esportes americanos</t>
   </si>
   <si>
-    <t>Investidor PF Ativo — Renda R$10k+</t>
-  </si>
-  <si>
-    <t>B3 Advanced Data</t>
-  </si>
-  <si>
     <t>Portal de grande audiência com seção de esportes internacionais e NFL.</t>
   </si>
   <si>
-    <t>B3 (Bolsa de Valores)</t>
-  </si>
-  <si>
-    <t>Investidores pessoa física ativos na bolsa, com renda declarada a partir de R$10 mil — alto poder de decisão financeira.</t>
+    <t>Perfil de Alocação Moderado/Arrojado</t>
   </si>
   <si>
     <t>lance.com.br</t>
   </si>
   <si>
-    <t>Renda Declarada Acima de R$30k</t>
-  </si>
-  <si>
     <t>Público brasileiro fã de esportes</t>
   </si>
   <si>
-    <t>Faixa de renda mais alta da base B3, aderente ao público A/B do briefing e a produtos de seguro/proteção patrimonial.</t>
-  </si>
-  <si>
     <t>Portal esportivo brasileiro com cobertura de NFL e eventos internacionais.</t>
   </si>
   <si>
-    <t>Perfil de Alocação Moderado/Arrojado</t>
+    <t>Investidores com apetite a risco moderado ou arrojado — indicativo de maior disposição de consumo e mobilidade financeira.</t>
+  </si>
+  <si>
+    <t>Interesse em Ações de Consumo e Entretenimento</t>
   </si>
   <si>
     <t>Média</t>
   </si>
   <si>
-    <t>Investidores com apetite a risco moderado ou arrojado — indicativo de maior disposição de consumo e mobilidade financeira.</t>
-  </si>
-  <si>
-    <t>Interesse em Ações de Consumo e Entretenimento</t>
-  </si>
-  <si>
     <t>Histórico de investimento em empresas de mídia, entretenimento e streaming — proxy de afinidade com o universo da campanha.</t>
   </si>
   <si>
+    <t>AGÊNCIA</t>
+  </si>
+  <si>
+    <t>3. IN-MARKET — INTENÇÃO ATIVA</t>
+  </si>
+  <si>
+    <t>In-Market for Sporting Goods</t>
+  </si>
+  <si>
+    <t>In-Market</t>
+  </si>
+  <si>
+    <t>DV360 Nativo</t>
+  </si>
+  <si>
+    <t>Usuários pesquisando ativamente artigos esportivos — camisas, bonés e colecionáveis oficiais.</t>
+  </si>
+  <si>
+    <t>In-Market for Apparel &amp; Streetwear</t>
+  </si>
+  <si>
+    <t>Intenção de compra em moda streetwear, alinhado ao consumo de produtos oficiais e colecionáveis do briefing.</t>
+  </si>
+  <si>
     <t>terra.com.br/esportes</t>
   </si>
   <si>
+    <t>In-Market for Event Tickets &amp; Travel (EUA)</t>
+  </si>
+  <si>
+    <t>DADOS DE FATURAMENTO</t>
+  </si>
+  <si>
+    <t>Pesquisa ativa por viagens e ingressos para eventos — conecta com o interesse em MetLife Stadium/NY.</t>
+  </si>
+  <si>
     <t>Portal de esportes com boa audiência em classes A/B urbanas.</t>
   </si>
   <si>
-    <t>3. IN-MARKET — INTENÇÃO ATIVA</t>
+    <t>In-Market for Streaming &amp; Electronics</t>
   </si>
   <si>
     <t>3. STREAMING E VÍDEO ESPORTIVO</t>
   </si>
   <si>
-    <t>In-Market for Sporting Goods</t>
-  </si>
-  <si>
-    <t>In-Market</t>
-  </si>
-  <si>
-    <t>DV360 Nativo</t>
-  </si>
-  <si>
-    <t>Usuários pesquisando ativamente artigos esportivos — camisas, bonés e colecionáveis oficiais.</t>
+    <t>Intenção de compra de dispositivos e assinaturas de streaming — hábito de consumo declarado no briefing.</t>
+  </si>
+  <si>
+    <t>Informações Adicionais de faturamento</t>
+  </si>
+  <si>
+    <t>4. AFFINITY — INTERESSES E COMPORTAMENTO</t>
+  </si>
+  <si>
+    <t>Sports Fans (Geral)</t>
+  </si>
+  <si>
+    <t>Affinity</t>
+  </si>
+  <si>
+    <t>Público com afinidade ampla e recorrente por conteúdo esportivo em geral.</t>
+  </si>
+  <si>
+    <t>Razão Social</t>
   </si>
   <si>
     <t>youtube.com</t>
   </si>
   <si>
-    <t>In-Market for Apparel &amp; Streetwear</t>
+    <t>Pro Football / American Football Enthusiasts</t>
   </si>
   <si>
     <t>Vídeo/Streaming</t>
@@ -663,39 +705,39 @@
     <t>Consumidores de vídeo e highlights de NFL</t>
   </si>
   <si>
+    <t>Consumidores frequentes de conteúdo sobre futebol americano e NFL — núcleo do público da campanha.</t>
+  </si>
+  <si>
     <t>Consumo de canais oficiais de NFL, Giants, Jets e criadores de conteúdo esportivo.</t>
   </si>
   <si>
-    <t>Intenção de compra em moda streetwear, alinhado ao consumo de produtos oficiais e colecionáveis do briefing.</t>
+    <t>Fantasy Sports Players</t>
+  </si>
+  <si>
+    <t>Usuários engajados em ligas de fantasy football, alinhado ao interesse declarado no briefing.</t>
   </si>
   <si>
     <t>twitch.tv</t>
   </si>
   <si>
-    <t>In-Market for Event Tickets &amp; Travel (EUA)</t>
+    <t>Gamers de Esportes e eSports (Madden NFL)</t>
   </si>
   <si>
     <t>Gamers e fãs de eSports (Madden NFL)</t>
   </si>
   <si>
-    <t>Pesquisa ativa por viagens e ingressos para eventos — conecta com o interesse em MetLife Stadium/NY.</t>
+    <t>Jogadores de games esportivos, com destaque para o público de Madden NFL citado no briefing.</t>
   </si>
   <si>
     <t>Plataforma de destaque para o público de Madden NFL e eSports citado no briefing.</t>
   </si>
   <si>
-    <t>In-Market for Streaming &amp; Electronics</t>
-  </si>
-  <si>
-    <t>Intenção de compra de dispositivos e assinaturas de streaming — hábito de consumo declarado no briefing.</t>
+    <t>5. CONTEXTUAL — TEMA DE CONTEÚDO</t>
   </si>
   <si>
     <t>bleacherreport.com</t>
   </si>
   <si>
-    <t>4. AFFINITY — INTERESSES E COMPORTAMENTO</t>
-  </si>
-  <si>
     <t>Fãs de esportes americanos, consumo mobile</t>
   </si>
   <si>
@@ -705,97 +747,145 @@
     <t>theathletic.com</t>
   </si>
   <si>
+    <t>Páginas de Notícias sobre NFL no Brasil</t>
+  </si>
+  <si>
+    <t>Contextual</t>
+  </si>
+  <si>
+    <t>DV360 Brand Controls</t>
+  </si>
+  <si>
     <t>Fãs de esportes com alto engajamento editorial</t>
   </si>
   <si>
+    <t>Impacto em páginas com cobertura de NFL em veículos brasileiros — contexto direto com a categoria.</t>
+  </si>
+  <si>
     <t>Cobertura aprofundada de times da NFL, incluindo Giants e Jets.</t>
   </si>
   <si>
-    <t>Sports Fans (Geral)</t>
-  </si>
-  <si>
-    <t>Affinity</t>
-  </si>
-  <si>
-    <t>AGÊNCIA</t>
+    <t>Conteúdo sobre New York Giants</t>
+  </si>
+  <si>
+    <t>Faturar após veiculação   (   x  ) Sim   (     ) Não</t>
+  </si>
+  <si>
+    <t>DV360 Brand Controls + Keywords</t>
   </si>
   <si>
     <t>4. FANTASY FOOTBALL, GAMES E CULTURA POP</t>
   </si>
   <si>
-    <t>Público com afinidade ampla e recorrente por conteúdo esportivo em geral.</t>
-  </si>
-  <si>
-    <t>Pro Football / American Football Enthusiasts</t>
-  </si>
-  <si>
-    <t>Consumidores frequentes de conteúdo sobre futebol americano e NFL — núcleo do público da campanha.</t>
-  </si>
-  <si>
-    <t>Fantasy Sports Players</t>
-  </si>
-  <si>
-    <t>Usuários engajados em ligas de fantasy football, alinhado ao interesse declarado no briefing.</t>
+    <t>Páginas com notícias, resultados e pautas específicas do New York Giants — atende ao pedido de foco em torcedores do time.</t>
+  </si>
+  <si>
+    <t>Conteúdo sobre New York Jets</t>
+  </si>
+  <si>
+    <t>Páginas com notícias, resultados e pautas específicas do New York Jets — atende ao pedido de foco em torcedores do time.</t>
+  </si>
+  <si>
+    <t>Fantasy Football e Madden NFL</t>
+  </si>
+  <si>
+    <t>Conteúdo editorial sobre ligas de fantasy e o game Madden NFL.</t>
+  </si>
+  <si>
+    <t>CNPJ</t>
+  </si>
+  <si>
+    <t>Cultura Pop Norte-Americana e Entretenimento</t>
+  </si>
+  <si>
+    <t>Páginas de entretenimento e cultura dos EUA, conectando com o eixo MetLife Stadium/NY do briefing.</t>
   </si>
   <si>
     <t>ea.com</t>
   </si>
   <si>
+    <t>6. CUSTOM INTENT &amp; CUSTOM AFFINITY</t>
+  </si>
+  <si>
     <t>Games</t>
   </si>
   <si>
     <t>Jogadores de Madden NFL</t>
   </si>
   <si>
-    <t>Gamers de Esportes e eSports (Madden NFL)</t>
-  </si>
-  <si>
     <t>Site oficial da EA Sports, publisher do game Madden NFL citado no briefing.</t>
   </si>
   <si>
-    <t>Jogadores de games esportivos, com destaque para o público de Madden NFL citado no briefing.</t>
-  </si>
-  <si>
-    <t>5. CONTEXTUAL — TEMA DE CONTEÚDO</t>
+    <t>Emissão NF</t>
   </si>
   <si>
     <t>ign.com</t>
   </si>
   <si>
+    <t>Custom Intent — New York Giants</t>
+  </si>
+  <si>
     <t>Games/Cultura Pop</t>
   </si>
   <si>
+    <t>Custom Intent</t>
+  </si>
+  <si>
+    <t>DV360 (URLs + Keywords)</t>
+  </si>
+  <si>
+    <t>Segmento construído com URLs e termos de busca ligados ao New York Giants (site oficial, notícias, escalação, jogos).</t>
+  </si>
+  <si>
     <t>Gamers e consumidores de cultura pop americana</t>
   </si>
   <si>
     <t>Portal de games com cobertura de Madden NFL e cultura pop dos EUA.</t>
   </si>
   <si>
+    <t>5 DFM</t>
+  </si>
+  <si>
+    <t>Custom Intent — New York Jets</t>
+  </si>
+  <si>
+    <t>Segmento construído com URLs e termos de busca ligados ao New York Jets (site oficial, notícias, escalação, jogos).</t>
+  </si>
+  <si>
     <t>yahoo.com/sports/fantasy</t>
   </si>
   <si>
+    <t>Custom Affinity — Torcedores de NFL no Brasil</t>
+  </si>
+  <si>
     <t>Fantasy Sports</t>
   </si>
   <si>
+    <t>Custom Affinity</t>
+  </si>
+  <si>
     <t>Jogadores de ligas de fantasy football</t>
   </si>
   <si>
+    <t>DV360 (URLs)</t>
+  </si>
+  <si>
     <t>Uma das maiores plataformas de fantasy football, alinhada ao interesse do briefing.</t>
   </si>
   <si>
-    <t>Páginas de Notícias sobre NFL no Brasil</t>
-  </si>
-  <si>
-    <t>Contextual</t>
-  </si>
-  <si>
-    <t>DV360 Brand Controls</t>
+    <t>Público com hábito recorrente de consumo de conteúdo NFL em português, construído a partir de sites e canais de nicho.</t>
+  </si>
+  <si>
+    <t>Custom Intent — Ingressos e Jogo NFL Brasil / MetLife Stadium</t>
+  </si>
+  <si>
+    <t>Contato Responsável</t>
   </si>
   <si>
     <t>polygon.com</t>
   </si>
   <si>
-    <t>Impacto em páginas com cobertura de NFL em veículos brasileiros — contexto direto com a categoria.</t>
+    <t>Intenção recente relacionada a ingressos, transmissão e cobertura do jogo de NFL no Brasil e ao MetLife Stadium.</t>
   </si>
   <si>
     <t>Consumidores de games e cultura pop</t>
@@ -804,72 +894,96 @@
     <t>Cobertura de games e cultura pop americana, reforço de contexto de entretenimento.</t>
   </si>
   <si>
-    <t>Conteúdo sobre New York Giants</t>
+    <t>Custom Affinity — Consumo de Streaming Esportivo (ESPN, NFL Game Pass)</t>
+  </si>
+  <si>
+    <t>Hábito de consumo de plataformas de streaming esportivo especializadas em NFL.</t>
   </si>
   <si>
     <t>5. VIAGENS, ENTRETENIMENTO E CULTURA POP EUA/NY</t>
   </si>
   <si>
-    <t>DV360 Brand Controls + Keywords</t>
-  </si>
-  <si>
-    <t>Páginas com notícias, resultados e pautas específicas do New York Giants — atende ao pedido de foco em torcedores do time.</t>
-  </si>
-  <si>
-    <t>DADOS DE FATURAMENTO</t>
-  </si>
-  <si>
-    <t>Conteúdo sobre New York Jets</t>
-  </si>
-  <si>
-    <t>Páginas com notícias, resultados e pautas específicas do New York Jets — atende ao pedido de foco em torcedores do time.</t>
+    <t>7. GEOLOCALIZAÇÃO — LIVETRACK E GEOTRACK</t>
+  </si>
+  <si>
+    <t>Responsável Financeiro</t>
+  </si>
+  <si>
+    <t>Vencimento</t>
+  </si>
+  <si>
+    <t>LiveTrack — Raio de 1km ao redor do Maracanã (dia do jogo)</t>
+  </si>
+  <si>
+    <t>15 DDL</t>
+  </si>
+  <si>
+    <t>Geolocalização</t>
+  </si>
+  <si>
+    <t>Adsplay LiveTrack</t>
   </si>
   <si>
     <t>tripadvisor.com.br</t>
   </si>
   <si>
+    <t>Impacto em tempo real de usuários presentes no entorno do Maracanã durante o jogo da NFL, conforme definido no plano.</t>
+  </si>
+  <si>
     <t>Viagem/Entretenimento</t>
   </si>
   <si>
-    <t>Fantasy Football e Madden NFL</t>
+    <t>GeoTrack — Frequentadores do Maracanã (janela de 90 dias)</t>
   </si>
   <si>
     <t>Interessados em viagens aos EUA/NY</t>
   </si>
   <si>
-    <t>Informações Adicionais de faturamento</t>
+    <t>Adsplay GeoTrack</t>
+  </si>
+  <si>
+    <t>Reimpacto de usuários que estiveram no raio de interesse do Maracanã antes ou depois do evento.</t>
   </si>
   <si>
     <t>Conecta com o interesse do briefing em viagens e entretenimento no eixo MetLife Stadium/NY.</t>
   </si>
   <si>
-    <t>Conteúdo editorial sobre ligas de fantasy e o game Madden NFL.</t>
+    <t>Email Responsável</t>
+  </si>
+  <si>
+    <t>LiveTrack — Bares e Esporte Bars durante transmissões de NFL</t>
   </si>
   <si>
     <t>panrotas.com.br</t>
   </si>
   <si>
-    <t>Cultura Pop Norte-Americana e Entretenimento</t>
+    <t>Impacto em tempo real de público presente em bares esportivos durante os jogos, ampliando o alcance do dia de jogo.</t>
   </si>
   <si>
     <t>Interessados em viagens internacionais</t>
   </si>
   <si>
+    <t>GeoTrack — Frequentadores de Lojas de Artigos Esportivos</t>
+  </si>
+  <si>
     <t>Portal de viagens com audiência de classe A/B, alinhado ao perfil do target.</t>
   </si>
   <si>
-    <t>Páginas de entretenimento e cultura dos EUA, conectando com o eixo MetLife Stadium/NY do briefing.</t>
+    <t>Email</t>
+  </si>
+  <si>
+    <t>Histórico de frequência a lojas de artigos esportivos e colecionáveis, indicando afinidade com o universo NFL.</t>
   </si>
   <si>
     <t>imdb.com</t>
   </si>
   <si>
+    <t>8. LOOK-A-LIKE &amp; REMARKETING</t>
+  </si>
+  <si>
     <t>Cultura Pop</t>
   </si>
   <si>
-    <t>6. CUSTOM INTENT &amp; CUSTOM AFFINITY</t>
-  </si>
-  <si>
     <t>Consumidores de cultura pop e entretenimento americano</t>
   </si>
   <si>
@@ -879,319 +993,205 @@
     <t>6. NOTÍCIAS E LIFESTYLE MASCULINO A/B</t>
   </si>
   <si>
-    <t>Razão Social</t>
-  </si>
-  <si>
-    <t>Custom Intent — New York Giants</t>
-  </si>
-  <si>
-    <t>Custom Intent</t>
+    <t>Look-a-Like de Compradores/Clientes Metlife</t>
+  </si>
+  <si>
+    <t>Look-a-Like</t>
+  </si>
+  <si>
+    <t>DV360 / Floodlight</t>
+  </si>
+  <si>
+    <t>Expansão de alcance a partir da similaridade com a base de clientes já convertidos da Metlife.</t>
+  </si>
+  <si>
+    <t>Remarketing — Visitantes do Site Metlife</t>
+  </si>
+  <si>
+    <t>Remarketing</t>
+  </si>
+  <si>
+    <t>Floodlight</t>
+  </si>
+  <si>
+    <t>Reimpacto de usuários que já visitaram o site da Metlife durante o período da campanha.</t>
+  </si>
+  <si>
+    <t>Look-a-Like de Torcedores Engajados — Giants/Jets</t>
   </si>
   <si>
     <t>forbes.com.br</t>
   </si>
   <si>
-    <t>DV360 (URLs + Keywords)</t>
+    <t>DV360</t>
+  </si>
+  <si>
+    <t>Expansão por similaridade a partir dos públicos Custom Intent/Affinity de torcedores do Giants e do Jets.</t>
   </si>
   <si>
     <t>Lifestyle/Negócios</t>
   </si>
   <si>
-    <t>Segmento construído com URLs e termos de busca ligados ao New York Giants (site oficial, notícias, escalação, jogos).</t>
-  </si>
-  <si>
     <t>Executivos e profissionais liberais</t>
   </si>
   <si>
+    <t>Remarketing — Engajados com Conteúdo NFL (Vídeo/Display)</t>
+  </si>
+  <si>
     <t>Alinhado ao perfil profissional de executivos e gestores do briefing.</t>
   </si>
   <si>
-    <t>Custom Intent — New York Jets</t>
+    <t>Reimpacto de usuários que assistiram/clicaram em peças da campanha com temática NFL.</t>
+  </si>
+  <si>
+    <t>9. KEYWORDS TARGETING</t>
   </si>
   <si>
     <t>gq.com.br</t>
   </si>
   <si>
-    <t>Segmento construído com URLs e termos de busca ligados ao New York Jets (site oficial, notícias, escalação, jogos).</t>
-  </si>
-  <si>
     <t>Lifestyle Masculino</t>
   </si>
   <si>
+    <t>TIPO DE CAMPANHA</t>
+  </si>
+  <si>
     <t>Homens 18-39, classe A/B, consumidores de streetwear</t>
   </si>
   <si>
-    <t>Custom Affinity — Torcedores de NFL no Brasil</t>
+    <t>Lista Produto — Seguro de Vida e Proteção Familiar</t>
   </si>
   <si>
     <t>Conecta com o público masculino do briefing e o interesse em moda streetwear.</t>
   </si>
   <si>
-    <t>Custom Affinity</t>
-  </si>
-  <si>
-    <t>DV360 (URLs)</t>
-  </si>
-  <si>
-    <t>Público com hábito recorrente de consumo de conteúdo NFL em português, construído a partir de sites e canais de nicho.</t>
+    <t>Keywords</t>
+  </si>
+  <si>
+    <t>Termos ligados ao produto Metlife: seguro de vida, proteção familiar, planejamento financeiro.</t>
+  </si>
+  <si>
+    <t>Lista NFL Geral</t>
   </si>
   <si>
     <t>uol.com.br</t>
   </si>
   <si>
+    <t>FORMATO</t>
+  </si>
+  <si>
     <t>Notícias Gerais</t>
   </si>
   <si>
-    <t>Custom Intent — Ingressos e Jogo NFL Brasil / MetLife Stadium</t>
+    <t>Termos amplos da categoria: NFL, futebol americano, Super Bowl, temporada NFL.</t>
   </si>
   <si>
     <t>Público geral de alto tráfego, classe A/B</t>
   </si>
   <si>
-    <t>Intenção recente relacionada a ingressos, transmissão e cobertura do jogo de NFL no Brasil e ao MetLife Stadium.</t>
+    <t>Lista Times — New York Giants e New York Jets</t>
   </si>
   <si>
     <t>Portal de notícias de grande alcance para reforço de volume qualificado.</t>
   </si>
   <si>
-    <t>Faturar após veiculação   (   x  ) Sim   (     ) Não</t>
-  </si>
-  <si>
-    <t>Custom Affinity — Consumo de Streaming Esportivo (ESPN, NFL Game Pass)</t>
-  </si>
-  <si>
-    <t>Hábito de consumo de plataformas de streaming esportivo especializadas em NFL.</t>
+    <t>Termos e apelidos específicos dos dois times foco: New York Giants, Big Blue, New York Jets, Gang Green.</t>
+  </si>
+  <si>
+    <t>VOLUME</t>
+  </si>
+  <si>
+    <t>Lista Contexto — Fantasy, Madden e MetLife Stadium</t>
+  </si>
+  <si>
+    <t>VALOR LIQUIDO</t>
+  </si>
+  <si>
+    <t>Termos de contexto complementar: fantasy football, Madden NFL, MetLife Stadium, jogo da NFL no Brasil.</t>
   </si>
   <si>
     <t>LEGENDA DE PRIORIDADE</t>
   </si>
   <si>
-    <t>7. GEOLOCALIZAÇÃO — LIVETRACK E GEOTRACK</t>
-  </si>
-  <si>
-    <t>LiveTrack — Raio de 1km ao redor do Maracanã (dia do jogo)</t>
-  </si>
-  <si>
-    <t>Geolocalização</t>
-  </si>
-  <si>
-    <t>Adsplay LiveTrack</t>
-  </si>
-  <si>
-    <t>Impacto em tempo real de usuários presentes no entorno do Maracanã durante o jogo da NFL, conforme definido no plano.</t>
-  </si>
-  <si>
-    <t>CNPJ</t>
+    <t>10. TOPIC TARGETING</t>
+  </si>
+  <si>
+    <t>PROGRAMÁTICA</t>
+  </si>
+  <si>
+    <t>Topic — Sports &gt; American Football</t>
+  </si>
+  <si>
+    <t>Topic</t>
+  </si>
+  <si>
+    <t>Inventário classificado por tópico editorial de futebol americano.</t>
+  </si>
+  <si>
+    <t>Topic — Sports &gt; Fantasy Sports</t>
+  </si>
+  <si>
+    <t>Inventário classificado por tópico editorial de esportes de fantasia.</t>
+  </si>
+  <si>
+    <t>Topic — Entertainment &amp; Pop Culture (EUA)</t>
+  </si>
+  <si>
+    <t>Inventário de entretenimento e cultura pop dos EUA, reforçando o eixo NY/MetLife Stadium.</t>
+  </si>
+  <si>
+    <t>11. YOUTUBE AUDIENCE SEGMENTS</t>
+  </si>
+  <si>
+    <t>YouTube — Espectadores de Canais de Esportes Americanos</t>
+  </si>
+  <si>
+    <t>YouTube Audience</t>
+  </si>
+  <si>
+    <t>DV360 / YouTube</t>
+  </si>
+  <si>
+    <t>Consumo recorrente de canais e conteúdo de esportes americanos no YouTube — aderente ao investimento em TrueView.</t>
+  </si>
+  <si>
+    <t>YouTube — Espectadores de Highlights NFL, Giants e Jets</t>
+  </si>
+  <si>
+    <t>Consumo de vídeos de melhores momentos, análises e resumos de jogos da NFL, com recorte para os dois times foco.</t>
+  </si>
+  <si>
+    <t>YouTube — Gamers de Madden NFL e eSports</t>
+  </si>
+  <si>
+    <t>Espectadores de conteúdo de gameplay e eSports do universo Madden NFL.</t>
   </si>
   <si>
     <t xml:space="preserve">  Alta</t>
   </si>
   <si>
-    <t>GeoTrack — Frequentadores do Maracanã (janela de 90 dias)</t>
-  </si>
-  <si>
-    <t>Adsplay GeoTrack</t>
-  </si>
-  <si>
-    <t>Reimpacto de usuários que estiveram no raio de interesse do Maracanã antes ou depois do evento.</t>
-  </si>
-  <si>
     <t>Segmento/site com alta precisão e relevância direta para o target</t>
   </si>
   <si>
-    <t>LiveTrack — Bares e Esporte Bars durante transmissões de NFL</t>
-  </si>
-  <si>
-    <t>Impacto em tempo real de público presente em bares esportivos durante os jogos, ampliando o alcance do dia de jogo.</t>
-  </si>
-  <si>
-    <t>GeoTrack — Frequentadores de Lojas de Artigos Esportivos</t>
-  </si>
-  <si>
-    <t>Histórico de frequência a lojas de artigos esportivos e colecionáveis, indicando afinidade com o universo NFL.</t>
-  </si>
-  <si>
-    <t>8. LOOK-A-LIKE &amp; REMARKETING</t>
-  </si>
-  <si>
-    <t>Emissão NF</t>
-  </si>
-  <si>
     <t xml:space="preserve">  Média-Alta</t>
   </si>
   <si>
-    <t>Look-a-Like de Compradores/Clientes Metlife</t>
-  </si>
-  <si>
-    <t>Look-a-Like</t>
-  </si>
-  <si>
-    <t>DV360 / Floodlight</t>
-  </si>
-  <si>
-    <t>5 DFM</t>
-  </si>
-  <si>
-    <t>Expansão de alcance a partir da similaridade com a base de clientes já convertidos da Metlife.</t>
-  </si>
-  <si>
-    <t>Remarketing — Visitantes do Site Metlife</t>
-  </si>
-  <si>
-    <t>Remarketing</t>
-  </si>
-  <si>
-    <t>Floodlight</t>
-  </si>
-  <si>
-    <t>Reimpacto de usuários que já visitaram o site da Metlife durante o período da campanha.</t>
-  </si>
-  <si>
     <t>Boa relevância — recomendado como complemento às audiências primárias</t>
   </si>
   <si>
-    <t>Look-a-Like de Torcedores Engajados — Giants/Jets</t>
-  </si>
-  <si>
-    <t>DV360</t>
-  </si>
-  <si>
-    <t>Expansão por similaridade a partir dos públicos Custom Intent/Affinity de torcedores do Giants e do Jets.</t>
-  </si>
-  <si>
-    <t>Remarketing — Engajados com Conteúdo NFL (Vídeo/Display)</t>
-  </si>
-  <si>
-    <t>Contato Responsável</t>
-  </si>
-  <si>
     <t xml:space="preserve">  Média</t>
   </si>
   <si>
-    <t>Reimpacto de usuários que assistiram/clicaram em peças da campanha com temática NFL.</t>
-  </si>
-  <si>
-    <t>9. KEYWORDS TARGETING</t>
-  </si>
-  <si>
     <t>Suporte para alcance — amplia volume com assertividade razoável</t>
   </si>
   <si>
-    <t>Responsável Financeiro</t>
-  </si>
-  <si>
-    <t>Lista Produto — Seguro de Vida e Proteção Familiar</t>
-  </si>
-  <si>
-    <t>Keywords</t>
-  </si>
-  <si>
-    <t>Termos ligados ao produto Metlife: seguro de vida, proteção familiar, planejamento financeiro.</t>
-  </si>
-  <si>
-    <t>Vencimento</t>
-  </si>
-  <si>
-    <t>15 DDL</t>
-  </si>
-  <si>
-    <t>Lista NFL Geral</t>
-  </si>
-  <si>
     <t>Todos os domínios listados possuem inventário disponível via Google Ad Exchange (AdX) para ativação em DV360. A disponibilidade pode variar por período e praça. Recomenda-se combinar a wishlist com segmentações de audiência B3 Advanced Data e Custom Intent/Affinity — em especial os segmentos voltados a torcedores do New York Giants e do New York Jets — para máxima assertividade.</t>
   </si>
   <si>
-    <t>Termos amplos da categoria: NFL, futebol americano, Super Bowl, temporada NFL.</t>
-  </si>
-  <si>
-    <t>Lista Times — New York Giants e New York Jets</t>
-  </si>
-  <si>
-    <t>Termos e apelidos específicos dos dois times foco: New York Giants, Big Blue, New York Jets, Gang Green.</t>
-  </si>
-  <si>
-    <t>Email Responsável</t>
-  </si>
-  <si>
-    <t>Lista Contexto — Fantasy, Madden e MetLife Stadium</t>
-  </si>
-  <si>
-    <t>Termos de contexto complementar: fantasy football, Madden NFL, MetLife Stadium, jogo da NFL no Brasil.</t>
-  </si>
-  <si>
-    <t>Email</t>
-  </si>
-  <si>
-    <t>10. TOPIC TARGETING</t>
-  </si>
-  <si>
-    <t>TIPO DE CAMPANHA</t>
-  </si>
-  <si>
-    <t>FORMATO</t>
-  </si>
-  <si>
-    <t>VOLUME</t>
-  </si>
-  <si>
-    <t>VALOR LIQUIDO</t>
-  </si>
-  <si>
-    <t>PROGRAMÁTICA</t>
-  </si>
-  <si>
-    <t>Topic — Sports &gt; American Football</t>
-  </si>
-  <si>
-    <t>Topic</t>
-  </si>
-  <si>
-    <t>Inventário classificado por tópico editorial de futebol americano.</t>
-  </si>
-  <si>
-    <t>Topic — Sports &gt; Fantasy Sports</t>
-  </si>
-  <si>
-    <t>Inventário classificado por tópico editorial de esportes de fantasia.</t>
-  </si>
-  <si>
-    <t>Topic — Entertainment &amp; Pop Culture (EUA)</t>
-  </si>
-  <si>
-    <t>Inventário de entretenimento e cultura pop dos EUA, reforçando o eixo NY/MetLife Stadium.</t>
-  </si>
-  <si>
-    <t>11. YOUTUBE AUDIENCE SEGMENTS</t>
-  </si>
-  <si>
-    <t>YouTube — Espectadores de Canais de Esportes Americanos</t>
-  </si>
-  <si>
-    <t>YouTube Audience</t>
-  </si>
-  <si>
-    <t>DV360 / YouTube</t>
-  </si>
-  <si>
-    <t>Consumo recorrente de canais e conteúdo de esportes americanos no YouTube — aderente ao investimento em TrueView.</t>
-  </si>
-  <si>
-    <t>YouTube — Espectadores de Highlights NFL, Giants e Jets</t>
-  </si>
-  <si>
-    <t>Consumo de vídeos de melhores momentos, análises e resumos de jogos da NFL, com recorte para os dois times foco.</t>
-  </si>
-  <si>
-    <t>YouTube — Gamers de Madden NFL e eSports</t>
-  </si>
-  <si>
-    <t>Espectadores de conteúdo de gameplay e eSports do universo Madden NFL.</t>
+    <t>Segmentos de audiência gerados pela Adsplay para ativação em DV360. B3 Advanced Data é tecnologia exclusiva Adsplay. Geoloc LiveTrack e GeoTrack são tecnologias proprietárias Adsplay. Recomenda-se combinar ao menos 1 segmento de cada categoria para máxima assertividade e cobertura, com atenção especial aos segmentos Custom Intent/Affinity, Contextual e Keywords voltados a torcedores do New York Giants e do New York Jets.</t>
   </si>
   <si>
     <t>TOTAL GERAL</t>
-  </si>
-  <si>
-    <t>Segmentos de audiência gerados pela Adsplay para ativação em DV360. B3 Advanced Data é tecnologia exclusiva Adsplay. Geoloc LiveTrack e GeoTrack são tecnologias proprietárias Adsplay. Recomenda-se combinar ao menos 1 segmento de cada categoria para máxima assertividade e cobertura, com atenção especial aos segmentos Custom Intent/Affinity, Contextual e Keywords voltados a torcedores do New York Giants e do New York Jets.</t>
   </si>
   <si>
     <t>TOTAL MENSAL</t>
@@ -1336,21 +1336,9 @@
     </font>
     <font>
       <b/>
-      <sz val="20.0"/>
-      <color rgb="FF831E9B"/>
-      <name val="Roboto"/>
-    </font>
-    <font>
-      <b/>
       <sz val="13.0"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18.0"/>
-      <color rgb="FF831E9B"/>
-      <name val="Roboto"/>
     </font>
     <font>
       <i/>
@@ -1360,9 +1348,21 @@
     </font>
     <font>
       <b/>
+      <sz val="20.0"/>
+      <color rgb="FF831E9B"/>
+      <name val="Roboto"/>
+    </font>
+    <font>
+      <b/>
       <sz val="10.0"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18.0"/>
+      <color rgb="FF831E9B"/>
+      <name val="Roboto"/>
     </font>
     <font>
       <sz val="9.0"/>
@@ -1394,6 +1394,11 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11.0"/>
+      <color rgb="FF20124D"/>
+      <name val="Roboto"/>
+    </font>
+    <font>
       <i/>
       <sz val="9.0"/>
       <color rgb="FF3B363B"/>
@@ -1404,11 +1409,6 @@
       <sz val="8.0"/>
       <color rgb="FF5D4037"/>
       <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11.0"/>
-      <color rgb="FF20124D"/>
-      <name val="Roboto"/>
     </font>
     <font>
       <b/>
@@ -1944,14 +1944,6 @@
       <bottom/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF831E9B"/>
-      </left>
-      <top style="thin">
-        <color rgb="FF831E9B"/>
-      </top>
-    </border>
-    <border>
       <right/>
       <top/>
       <bottom/>
@@ -1971,6 +1963,14 @@
       </bottom>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FF831E9B"/>
+      </left>
+      <top style="thin">
+        <color rgb="FF831E9B"/>
+      </top>
+    </border>
+    <border>
       <top style="thin">
         <color rgb="FF831E9B"/>
       </top>
@@ -1984,18 +1984,18 @@
       </top>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
     </border>
     <border>
       <right style="thin">
@@ -2235,29 +2235,29 @@
     <xf borderId="16" fillId="0" fontId="8" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="17" fillId="0" fontId="8" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="18" fillId="0" fontId="8" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="19" fillId="0" fontId="8" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
+    <xf borderId="19" fillId="0" fontId="8" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="8" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="7" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="9" numFmtId="3" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
     <xf borderId="20" fillId="0" fontId="8" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="21" fillId="0" fontId="8" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="9" numFmtId="3" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf borderId="0" fillId="0" fontId="9" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="5" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf borderId="8" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="9" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
     <xf borderId="1" fillId="2" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf borderId="7" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="22" fillId="0" fontId="8" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="6" fillId="0" fontId="8" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
@@ -2300,34 +2300,34 @@
     <xf borderId="24" fillId="0" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
+    <xf borderId="9" fillId="0" fontId="1" numFmtId="3" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="25" fillId="0" fontId="1" numFmtId="9" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
     <xf borderId="10" fillId="0" fontId="9" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="9" fillId="0" fontId="1" numFmtId="3" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="25" fillId="0" fontId="1" numFmtId="9" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="9" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="11" fillId="0" fontId="1" numFmtId="9" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="24" fillId="0" fontId="9" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="11" fillId="0" fontId="1" numFmtId="9" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="9" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
     <xf borderId="9" fillId="0" fontId="9" numFmtId="3" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="25" fillId="0" fontId="9" numFmtId="9" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="26" fillId="0" fontId="8" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="11" fillId="0" fontId="9" numFmtId="9" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
+    <xf borderId="26" fillId="0" fontId="8" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="27" fillId="0" fontId="8" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="28" fillId="2" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
@@ -2364,39 +2364,54 @@
     <xf borderId="30" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
+    <xf borderId="31" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="8" fillId="0" fontId="9" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="11" fillId="0" fontId="9" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="7" fillId="0" fontId="9" numFmtId="3" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="8" fillId="0" fontId="9" numFmtId="10" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="11" fillId="0" fontId="9" numFmtId="3" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="8" fillId="0" fontId="9" numFmtId="10" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
     <xf borderId="8" fillId="0" fontId="2" numFmtId="10" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="31" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="8" fillId="0" fontId="9" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="11" fillId="0" fontId="9" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="7" fillId="0" fontId="9" numFmtId="3" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="8" fillId="0" fontId="9" numFmtId="10" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="11" fillId="0" fontId="9" numFmtId="3" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
     <xf borderId="22" fillId="2" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="23" fillId="2" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="8" fillId="0" fontId="9" numFmtId="10" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
     <xf borderId="1" fillId="2" fontId="4" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
+    <xf borderId="32" fillId="0" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="33" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="34" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="33" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="30" fillId="0" fontId="9" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
     <xf borderId="32" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
@@ -2415,26 +2430,11 @@
     <xf borderId="30" fillId="0" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="32" fillId="0" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="35" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="33" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="34" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="33" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="30" fillId="0" fontId="9" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
+    <xf borderId="36" fillId="0" fontId="8" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="35" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="36" fillId="0" fontId="8" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="35" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
@@ -2573,72 +2573,72 @@
     <xf borderId="0" fillId="0" fontId="18" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
+    <xf borderId="45" fillId="7" fontId="20" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf borderId="46" fillId="0" fontId="8" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="20" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="47" fillId="0" fontId="8" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="45" fillId="2" fontId="21" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="45" fillId="7" fontId="21" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="22" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="22" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="48" fillId="6" fontId="23" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="45" fillId="2" fontId="23" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="24" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="48" fillId="3" fontId="25" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf borderId="48" fillId="3" fontId="26" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
-    <xf borderId="46" fillId="0" fontId="8" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="48" fillId="3" fontId="25" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="48" fillId="8" fontId="27" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf borderId="0" fillId="0" fontId="15" numFmtId="14" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="47" fillId="0" fontId="22" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="48" fillId="9" fontId="25" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf borderId="48" fillId="9" fontId="26" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf borderId="48" fillId="9" fontId="25" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="49" fillId="0" fontId="24" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="48" fillId="0" fontId="8" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="45" fillId="2" fontId="23" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="50" fillId="0" fontId="8" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="48" fillId="10" fontId="27" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="49" fillId="6" fontId="24" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="50" fillId="0" fontId="8" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="45" fillId="2" fontId="24" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf borderId="49" fillId="3" fontId="25" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf borderId="49" fillId="3" fontId="26" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf borderId="49" fillId="3" fontId="25" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
     <xf borderId="51" fillId="0" fontId="8" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="49" fillId="8" fontId="27" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="49" fillId="9" fontId="25" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf borderId="41" fillId="0" fontId="8" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="49" fillId="9" fontId="26" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf borderId="49" fillId="9" fontId="25" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="49" fillId="10" fontId="27" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf borderId="0" fillId="0" fontId="28" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="49" fillId="11" fontId="27" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="29" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="48" fillId="11" fontId="27" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="29" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="33" fillId="2" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
@@ -2657,58 +2657,58 @@
     <xf borderId="33" fillId="0" fontId="28" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
+    <xf borderId="32" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="33" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="32" fillId="3" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="30" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="27" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf borderId="45" fillId="7" fontId="27" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf borderId="52" fillId="8" fontId="27" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="52" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf borderId="53" fillId="8" fontId="27" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf borderId="45" fillId="9" fontId="30" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf borderId="32" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="52" fillId="10" fontId="27" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf borderId="33" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="32" fillId="3" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="52" fillId="11" fontId="27" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf borderId="45" fillId="12" fontId="31" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="32" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="27" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="53" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf borderId="54" fillId="0" fontId="8" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="55" fillId="0" fontId="8" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="45" fillId="9" fontId="31" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf borderId="27" fillId="3" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf borderId="56" fillId="3" fontId="2" numFmtId="3" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf borderId="53" fillId="10" fontId="27" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf borderId="56" fillId="3" fontId="2" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf borderId="53" fillId="11" fontId="27" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf borderId="0" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf borderId="0" fillId="3" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf borderId="45" fillId="12" fontId="32" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="6" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2746,11 +2746,11 @@
     <xf borderId="0" fillId="2" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
-    <xf borderId="47" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="49" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf borderId="38" fillId="0" fontId="8" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="47" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="49" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf borderId="60" fillId="0" fontId="8" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
@@ -3409,7 +3409,7 @@
     <row r="10">
       <c r="A10" s="1"/>
       <c r="B10" s="13" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C10" s="14">
         <f>C9/80%</f>
@@ -3436,7 +3436,7 @@
     <row r="11">
       <c r="A11" s="1"/>
       <c r="B11" s="8" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C11" s="12">
         <f>N72</f>
@@ -3463,7 +3463,7 @@
     <row r="12" ht="15.75" customHeight="1">
       <c r="A12" s="1"/>
       <c r="B12" s="13" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C12" s="14">
         <f>C11/80%</f>
@@ -3512,7 +3512,7 @@
     <row r="14" ht="15.75" customHeight="1">
       <c r="A14" s="1"/>
       <c r="B14" s="15" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15" ht="15.75" customHeight="1">
@@ -3875,23 +3875,23 @@
     </row>
     <row r="28" ht="32.25" customHeight="1">
       <c r="A28" s="1"/>
-      <c r="B28" s="50"/>
+      <c r="B28" s="51"/>
       <c r="C28" s="45" t="s">
         <v>46</v>
       </c>
-      <c r="D28" s="50"/>
-      <c r="E28" s="50"/>
+      <c r="D28" s="51"/>
+      <c r="E28" s="51"/>
       <c r="F28" s="34" t="s">
         <v>47</v>
       </c>
-      <c r="G28" s="50"/>
+      <c r="G28" s="51"/>
       <c r="H28" s="34" t="s">
         <v>45</v>
       </c>
-      <c r="I28" s="50"/>
+      <c r="I28" s="51"/>
       <c r="J28" s="35"/>
-      <c r="K28" s="52"/>
-      <c r="L28" s="53"/>
+      <c r="K28" s="55"/>
+      <c r="L28" s="56"/>
       <c r="M28" s="48"/>
       <c r="N28" s="48"/>
       <c r="P28" s="44"/>
@@ -3900,8 +3900,8 @@
       <c r="T28" s="39"/>
     </row>
     <row r="29" ht="15.75" customHeight="1">
-      <c r="A29" s="55"/>
-      <c r="B29" s="58"/>
+      <c r="A29" s="58"/>
+      <c r="B29" s="59"/>
       <c r="C29" s="60"/>
       <c r="D29" s="60"/>
       <c r="E29" s="60"/>
@@ -4138,14 +4138,14 @@
         <v>70000.0</v>
       </c>
       <c r="O35" s="39"/>
-      <c r="P35" s="76">
+      <c r="P35" s="75">
         <f t="shared" ref="P35:P36" si="5">N35/L35*1000</f>
         <v>1750000</v>
       </c>
-      <c r="Q35" s="77">
+      <c r="Q35" s="76">
         <v>0.9</v>
       </c>
-      <c r="R35" s="76">
+      <c r="R35" s="75">
         <f t="shared" ref="R35:R36" si="6">P35*Q35</f>
         <v>1575000</v>
       </c>
@@ -4181,14 +4181,14 @@
         <v>120000.0</v>
       </c>
       <c r="O36" s="39"/>
-      <c r="P36" s="76">
+      <c r="P36" s="75">
         <f t="shared" si="5"/>
         <v>5000000</v>
       </c>
       <c r="Q36" s="79">
         <v>0.4</v>
       </c>
-      <c r="R36" s="76">
+      <c r="R36" s="75">
         <f t="shared" si="6"/>
         <v>2000000</v>
       </c>
@@ -4210,8 +4210,8 @@
       <c r="J37" s="35"/>
       <c r="K37" s="46"/>
       <c r="L37" s="47"/>
-      <c r="M37" s="83"/>
-      <c r="N37" s="83"/>
+      <c r="M37" s="84"/>
+      <c r="N37" s="84"/>
       <c r="P37" s="46"/>
       <c r="Q37" s="48"/>
       <c r="R37" s="46"/>
@@ -4233,8 +4233,8 @@
       <c r="J38" s="35"/>
       <c r="K38" s="46"/>
       <c r="L38" s="47"/>
-      <c r="M38" s="83"/>
-      <c r="N38" s="83"/>
+      <c r="M38" s="84"/>
+      <c r="N38" s="84"/>
       <c r="P38" s="46"/>
       <c r="Q38" s="48"/>
       <c r="R38" s="46"/>
@@ -4256,8 +4256,8 @@
       <c r="J39" s="35"/>
       <c r="K39" s="46"/>
       <c r="L39" s="47"/>
-      <c r="M39" s="83"/>
-      <c r="N39" s="83"/>
+      <c r="M39" s="84"/>
+      <c r="N39" s="84"/>
       <c r="P39" s="46"/>
       <c r="Q39" s="48"/>
       <c r="R39" s="46"/>
@@ -4279,8 +4279,8 @@
       <c r="J40" s="35"/>
       <c r="K40" s="46"/>
       <c r="L40" s="47"/>
-      <c r="M40" s="83"/>
-      <c r="N40" s="83"/>
+      <c r="M40" s="84"/>
+      <c r="N40" s="84"/>
       <c r="P40" s="46"/>
       <c r="Q40" s="48"/>
       <c r="R40" s="46"/>
@@ -4289,21 +4289,21 @@
     </row>
     <row r="41" ht="27.75" customHeight="1">
       <c r="A41" s="1"/>
-      <c r="B41" s="50"/>
+      <c r="B41" s="51"/>
       <c r="C41" s="45" t="s">
         <v>42</v>
       </c>
-      <c r="D41" s="50"/>
-      <c r="E41" s="50"/>
-      <c r="F41" s="50"/>
-      <c r="G41" s="50"/>
-      <c r="H41" s="50"/>
-      <c r="I41" s="50"/>
+      <c r="D41" s="51"/>
+      <c r="E41" s="51"/>
+      <c r="F41" s="51"/>
+      <c r="G41" s="51"/>
+      <c r="H41" s="51"/>
+      <c r="I41" s="51"/>
       <c r="J41" s="35"/>
-      <c r="K41" s="52"/>
-      <c r="L41" s="53"/>
-      <c r="M41" s="83"/>
-      <c r="N41" s="83"/>
+      <c r="K41" s="55"/>
+      <c r="L41" s="56"/>
+      <c r="M41" s="84"/>
+      <c r="N41" s="84"/>
       <c r="P41" s="46"/>
       <c r="Q41" s="85"/>
       <c r="R41" s="46"/>
@@ -4311,8 +4311,8 @@
       <c r="T41" s="39"/>
     </row>
     <row r="42" ht="15.75" customHeight="1">
-      <c r="A42" s="55"/>
-      <c r="B42" s="58"/>
+      <c r="A42" s="58"/>
+      <c r="B42" s="59"/>
       <c r="C42" s="60"/>
       <c r="D42" s="60"/>
       <c r="E42" s="60"/>
@@ -4560,7 +4560,7 @@
         <f t="shared" ref="R48:R52" si="11">P48*Q48</f>
         <v>0</v>
       </c>
-      <c r="S48" s="77">
+      <c r="S48" s="76">
         <v>0.98</v>
       </c>
       <c r="T48" s="39"/>
@@ -4605,7 +4605,7 @@
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="S49" s="77">
+      <c r="S49" s="76">
         <v>0.98</v>
       </c>
       <c r="T49" s="39"/>
@@ -4650,7 +4650,7 @@
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="S50" s="77">
+      <c r="S50" s="76">
         <v>0.98</v>
       </c>
       <c r="T50" s="39"/>
@@ -4695,14 +4695,14 @@
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="S51" s="77">
+      <c r="S51" s="76">
         <v>0.98</v>
       </c>
       <c r="T51" s="39"/>
     </row>
     <row r="52" ht="25.5" customHeight="1">
       <c r="A52" s="1"/>
-      <c r="B52" s="50"/>
+      <c r="B52" s="51"/>
       <c r="C52" s="94" t="s">
         <v>61</v>
       </c>
@@ -4712,12 +4712,12 @@
       <c r="E52" s="95" t="s">
         <v>62</v>
       </c>
-      <c r="F52" s="50"/>
-      <c r="G52" s="50"/>
-      <c r="H52" s="50"/>
-      <c r="I52" s="50"/>
+      <c r="F52" s="51"/>
+      <c r="G52" s="51"/>
+      <c r="H52" s="51"/>
+      <c r="I52" s="51"/>
       <c r="J52" s="35"/>
-      <c r="K52" s="52"/>
+      <c r="K52" s="55"/>
       <c r="L52" s="96">
         <v>25.0</v>
       </c>
@@ -4733,21 +4733,21 @@
         <f t="shared" si="10"/>
         <v>4800000</v>
       </c>
-      <c r="Q52" s="99">
+      <c r="Q52" s="106">
         <v>0.01</v>
       </c>
       <c r="R52" s="42">
         <f t="shared" si="11"/>
         <v>48000</v>
       </c>
-      <c r="S52" s="77">
+      <c r="S52" s="76">
         <v>0.7</v>
       </c>
       <c r="T52" s="39"/>
     </row>
     <row r="53" ht="15.75" customHeight="1">
-      <c r="A53" s="55"/>
-      <c r="B53" s="58"/>
+      <c r="A53" s="58"/>
+      <c r="B53" s="59"/>
       <c r="C53" s="60"/>
       <c r="D53" s="60"/>
       <c r="E53" s="60"/>
@@ -4774,14 +4774,14 @@
         <f>SUM(P48:P52)</f>
         <v>10225689.78</v>
       </c>
-      <c r="Q53" s="106" t="s">
+      <c r="Q53" s="107" t="s">
         <v>63</v>
       </c>
       <c r="R53" s="63">
         <f>SUM(R48:R52)</f>
         <v>48000</v>
       </c>
-      <c r="S53" s="107" t="s">
+      <c r="S53" s="108" t="s">
         <v>63</v>
       </c>
       <c r="T53" s="62"/>
@@ -4931,19 +4931,19 @@
     </row>
     <row r="59" ht="55.5" customHeight="1">
       <c r="A59" s="1"/>
-      <c r="B59" s="110" t="s">
+      <c r="B59" s="115" t="s">
         <v>30</v>
       </c>
-      <c r="C59" s="111" t="s">
+      <c r="C59" s="116" t="s">
         <v>65</v>
       </c>
-      <c r="D59" s="112" t="s">
+      <c r="D59" s="117" t="s">
         <v>32</v>
       </c>
-      <c r="E59" s="111" t="s">
+      <c r="E59" s="116" t="s">
         <v>66</v>
       </c>
-      <c r="F59" s="113" t="str">
+      <c r="F59" s="118" t="str">
         <f t="shared" ref="F59:I59" si="13">F21</f>
         <v>Faixa etária: 18 a 39 anos (Millennials e Gen Z adultos)
 Gênero: Maioria masculina (~65%), com presença feminina expressiva e em expansão (~35%)
@@ -4951,7 +4951,7 @@
 Perfil profissional: Executivos, profissionais liberais, gestores e especialistas (TI, finanças, negócios)
 Estilo de vida: Urbano, altamente digitalized, social e consumidor de cultura global.</v>
       </c>
-      <c r="G59" s="113" t="str">
+      <c r="G59" s="118" t="str">
         <f t="shared" si="13"/>
         <v>Esportes americanos (futebol americano / NFL, NBA) e Fantasy Football
 Jogos virtuais e eSports (destaque para o game Madden NFL)
@@ -4959,19 +4959,19 @@
 Consumo via streaming, mídias digitais e redes sociais em tempo real
 Produtos oficiais, colecionáveis esportivos e moda streetwear.</v>
       </c>
-      <c r="H59" s="113" t="str">
+      <c r="H59" s="118" t="str">
         <f t="shared" si="13"/>
         <v>Brasil</v>
       </c>
-      <c r="I59" s="113">
+      <c r="I59" s="118">
         <f t="shared" si="13"/>
         <v>4</v>
       </c>
       <c r="J59" s="35"/>
-      <c r="K59" s="114" t="s">
+      <c r="K59" s="119" t="s">
         <v>67</v>
       </c>
-      <c r="L59" s="115">
+      <c r="L59" s="120">
         <v>0.9</v>
       </c>
       <c r="M59" s="38">
@@ -4982,7 +4982,7 @@
         <v>40000.0</v>
       </c>
       <c r="O59" s="39"/>
-      <c r="P59" s="76">
+      <c r="P59" s="75">
         <f>R59/Q59</f>
         <v>4444444.444</v>
       </c>
@@ -4993,14 +4993,14 @@
         <f>N59/L59</f>
         <v>44444.44444</v>
       </c>
-      <c r="S59" s="77">
+      <c r="S59" s="76">
         <v>0.7</v>
       </c>
       <c r="T59" s="39"/>
     </row>
     <row r="60" ht="15.75" customHeight="1">
-      <c r="A60" s="55"/>
-      <c r="B60" s="58"/>
+      <c r="A60" s="58"/>
+      <c r="B60" s="59"/>
       <c r="C60" s="60"/>
       <c r="D60" s="60"/>
       <c r="E60" s="60"/>
@@ -5189,16 +5189,16 @@
       <c r="B66" s="31" t="s">
         <v>30</v>
       </c>
-      <c r="C66" s="111" t="s">
+      <c r="C66" s="116" t="s">
         <v>69</v>
       </c>
       <c r="D66" s="72" t="s">
         <v>70</v>
       </c>
-      <c r="E66" s="111" t="s">
+      <c r="E66" s="116" t="s">
         <v>71</v>
       </c>
-      <c r="F66" s="121" t="str">
+      <c r="F66" s="123" t="str">
         <f t="shared" ref="F66:I66" si="15">F21</f>
         <v>Faixa etária: 18 a 39 anos (Millennials e Gen Z adultos)
 Gênero: Maioria masculina (~65%), com presença feminina expressiva e em expansão (~35%)
@@ -5206,7 +5206,7 @@
 Perfil profissional: Executivos, profissionais liberais, gestores e especialistas (TI, finanças, negócios)
 Estilo de vida: Urbano, altamente digitalized, social e consumidor de cultura global.</v>
       </c>
-      <c r="G66" s="121" t="str">
+      <c r="G66" s="123" t="str">
         <f t="shared" si="15"/>
         <v>Esportes americanos (futebol americano / NFL, NBA) e Fantasy Football
 Jogos virtuais e eSports (destaque para o game Madden NFL)
@@ -5214,11 +5214,11 @@
 Consumo via streaming, mídias digitais e redes sociais em tempo real
 Produtos oficiais, colecionáveis esportivos e moda streetwear.</v>
       </c>
-      <c r="H66" s="121" t="str">
+      <c r="H66" s="123" t="str">
         <f t="shared" si="15"/>
         <v>Brasil</v>
       </c>
-      <c r="I66" s="121">
+      <c r="I66" s="123">
         <f t="shared" si="15"/>
         <v>4</v>
       </c>
@@ -5226,7 +5226,7 @@
       <c r="K66" s="72" t="s">
         <v>72</v>
       </c>
-      <c r="L66" s="115">
+      <c r="L66" s="120">
         <v>0.7</v>
       </c>
       <c r="M66" s="38">
@@ -5237,7 +5237,7 @@
         <v>120000.0</v>
       </c>
       <c r="O66" s="39"/>
-      <c r="P66" s="76">
+      <c r="P66" s="75">
         <f t="shared" ref="P66:P67" si="17">N66/L66</f>
         <v>171428.5714</v>
       </c>
@@ -5255,25 +5255,25 @@
     </row>
     <row r="67" ht="36.75" customHeight="1">
       <c r="A67" s="1"/>
-      <c r="B67" s="50"/>
-      <c r="C67" s="111" t="s">
+      <c r="B67" s="51"/>
+      <c r="C67" s="116" t="s">
         <v>73</v>
       </c>
-      <c r="D67" s="52"/>
-      <c r="E67" s="111" t="s">
+      <c r="D67" s="55"/>
+      <c r="E67" s="116" t="s">
         <v>71</v>
       </c>
       <c r="F67" s="122"/>
       <c r="G67" s="122"/>
       <c r="H67" s="122"/>
-      <c r="I67" s="121">
+      <c r="I67" s="123">
         <v>1.0</v>
       </c>
       <c r="J67" s="35"/>
       <c r="K67" s="72" t="s">
         <v>72</v>
       </c>
-      <c r="L67" s="115">
+      <c r="L67" s="120">
         <v>0.7</v>
       </c>
       <c r="M67" s="38">
@@ -5284,7 +5284,7 @@
         <v>30000.0</v>
       </c>
       <c r="O67" s="39"/>
-      <c r="P67" s="76">
+      <c r="P67" s="75">
         <f t="shared" si="17"/>
         <v>42857.14286</v>
       </c>
@@ -5299,8 +5299,8 @@
       <c r="T67" s="39"/>
     </row>
     <row r="68" ht="15.75" customHeight="1">
-      <c r="A68" s="55"/>
-      <c r="B68" s="58"/>
+      <c r="A68" s="58"/>
+      <c r="B68" s="59"/>
       <c r="C68" s="60"/>
       <c r="D68" s="60"/>
       <c r="E68" s="60"/>
@@ -5750,7 +5750,7 @@
         <v>93</v>
       </c>
       <c r="D82" s="159" t="s">
-        <v>94</v>
+        <v>108</v>
       </c>
       <c r="G82" s="139"/>
       <c r="H82" s="139"/>
@@ -5774,7 +5774,7 @@
       </c>
       <c r="C83" s="161"/>
       <c r="D83" s="162" t="s">
-        <v>96</v>
+        <v>109</v>
       </c>
       <c r="F83" s="163"/>
       <c r="H83" s="139"/>
@@ -5798,7 +5798,7 @@
       </c>
       <c r="C84" s="161"/>
       <c r="D84" s="162" t="s">
-        <v>98</v>
+        <v>110</v>
       </c>
       <c r="F84" s="163"/>
       <c r="G84" s="139"/>
@@ -5819,11 +5819,11 @@
     <row r="85" ht="15.75" customHeight="1">
       <c r="A85" s="6"/>
       <c r="B85" s="160" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C85" s="161"/>
       <c r="D85" s="162" t="s">
-        <v>100</v>
+        <v>112</v>
       </c>
       <c r="F85" s="163"/>
       <c r="H85" s="139"/>
@@ -5843,11 +5843,11 @@
     <row r="86" ht="15.75" customHeight="1">
       <c r="A86" s="6"/>
       <c r="B86" s="160" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C86" s="161"/>
       <c r="D86" s="162" t="s">
-        <v>102</v>
+        <v>113</v>
       </c>
       <c r="F86" s="163"/>
       <c r="G86" s="139"/>
@@ -5868,11 +5868,11 @@
     <row r="87" ht="15.75" customHeight="1">
       <c r="A87" s="6"/>
       <c r="B87" s="160" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C87" s="161"/>
       <c r="D87" s="162" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F87" s="163"/>
       <c r="H87" s="139"/>
@@ -5892,11 +5892,11 @@
     <row r="88" ht="15.75" customHeight="1">
       <c r="A88" s="6"/>
       <c r="B88" s="160" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C88" s="161"/>
       <c r="D88" s="162" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F88" s="163"/>
       <c r="G88" s="139"/>
@@ -5917,11 +5917,11 @@
     <row r="89" ht="15.75" customHeight="1">
       <c r="A89" s="6"/>
       <c r="B89" s="164" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C89" s="165"/>
       <c r="D89" s="166" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E89" s="167"/>
       <c r="F89" s="168"/>
@@ -6320,7 +6320,7 @@
     <row r="10">
       <c r="A10" s="1"/>
       <c r="B10" s="13" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C10" s="14">
         <f>C9/80%</f>
@@ -6347,7 +6347,7 @@
     <row r="11">
       <c r="A11" s="1"/>
       <c r="B11" s="8" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C11" s="12">
         <f>N72</f>
@@ -6374,7 +6374,7 @@
     <row r="12">
       <c r="A12" s="1"/>
       <c r="B12" s="13" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C12" s="14">
         <f>C11/80%</f>
@@ -6423,7 +6423,7 @@
     <row r="14" ht="15.75" customHeight="1">
       <c r="A14" s="1"/>
       <c r="B14" s="15" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15" ht="15.75" customHeight="1">
@@ -6785,24 +6785,24 @@
       <c r="T27" s="39"/>
     </row>
     <row r="28" ht="32.25" customHeight="1">
-      <c r="A28" s="51"/>
-      <c r="B28" s="50"/>
+      <c r="A28" s="50"/>
+      <c r="B28" s="51"/>
       <c r="C28" s="45" t="s">
         <v>46</v>
       </c>
-      <c r="D28" s="50"/>
-      <c r="E28" s="50"/>
+      <c r="D28" s="51"/>
+      <c r="E28" s="51"/>
       <c r="F28" s="34" t="s">
         <v>47</v>
       </c>
-      <c r="G28" s="50"/>
+      <c r="G28" s="51"/>
       <c r="H28" s="34" t="s">
         <v>45</v>
       </c>
-      <c r="I28" s="50"/>
+      <c r="I28" s="51"/>
       <c r="J28" s="54"/>
-      <c r="K28" s="52"/>
-      <c r="L28" s="53"/>
+      <c r="K28" s="55"/>
+      <c r="L28" s="56"/>
       <c r="M28" s="48"/>
       <c r="N28" s="48"/>
       <c r="P28" s="44"/>
@@ -6811,8 +6811,8 @@
       <c r="T28" s="57"/>
     </row>
     <row r="29" ht="15.75" customHeight="1">
-      <c r="A29" s="55"/>
-      <c r="B29" s="58"/>
+      <c r="A29" s="58"/>
+      <c r="B29" s="59"/>
       <c r="C29" s="60"/>
       <c r="D29" s="60"/>
       <c r="E29" s="60"/>
@@ -7007,7 +7007,7 @@
       <c r="D35" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="E35" s="59" t="s">
+      <c r="E35" s="53" t="s">
         <v>52</v>
       </c>
       <c r="F35" s="34" t="str">
@@ -7038,14 +7038,14 @@
       <c r="K35" s="72" t="s">
         <v>37</v>
       </c>
-      <c r="L35" s="75">
+      <c r="L35" s="77">
         <v>40.0</v>
       </c>
-      <c r="M35" s="78">
+      <c r="M35" s="80">
         <f t="shared" ref="M35:M36" si="4">N35/80%</f>
         <v>0</v>
       </c>
-      <c r="N35" s="78">
+      <c r="N35" s="80">
         <v>0.0</v>
       </c>
       <c r="O35" s="57"/>
@@ -7092,14 +7092,14 @@
         <v>120000.0</v>
       </c>
       <c r="O36" s="39"/>
-      <c r="P36" s="76">
+      <c r="P36" s="75">
         <f t="shared" si="5"/>
         <v>5000000</v>
       </c>
       <c r="Q36" s="79">
         <v>0.4</v>
       </c>
-      <c r="R36" s="76">
+      <c r="R36" s="75">
         <f t="shared" si="6"/>
         <v>2000000</v>
       </c>
@@ -7121,8 +7121,8 @@
       <c r="J37" s="35"/>
       <c r="K37" s="46"/>
       <c r="L37" s="47"/>
-      <c r="M37" s="83"/>
-      <c r="N37" s="83"/>
+      <c r="M37" s="84"/>
+      <c r="N37" s="84"/>
       <c r="P37" s="46"/>
       <c r="Q37" s="48"/>
       <c r="R37" s="46"/>
@@ -7144,8 +7144,8 @@
       <c r="J38" s="35"/>
       <c r="K38" s="46"/>
       <c r="L38" s="47"/>
-      <c r="M38" s="83"/>
-      <c r="N38" s="83"/>
+      <c r="M38" s="84"/>
+      <c r="N38" s="84"/>
       <c r="P38" s="46"/>
       <c r="Q38" s="48"/>
       <c r="R38" s="46"/>
@@ -7167,8 +7167,8 @@
       <c r="J39" s="35"/>
       <c r="K39" s="46"/>
       <c r="L39" s="47"/>
-      <c r="M39" s="83"/>
-      <c r="N39" s="83"/>
+      <c r="M39" s="84"/>
+      <c r="N39" s="84"/>
       <c r="P39" s="46"/>
       <c r="Q39" s="48"/>
       <c r="R39" s="46"/>
@@ -7190,8 +7190,8 @@
       <c r="J40" s="35"/>
       <c r="K40" s="46"/>
       <c r="L40" s="47"/>
-      <c r="M40" s="83"/>
-      <c r="N40" s="83"/>
+      <c r="M40" s="84"/>
+      <c r="N40" s="84"/>
       <c r="P40" s="46"/>
       <c r="Q40" s="48"/>
       <c r="R40" s="46"/>
@@ -7200,21 +7200,21 @@
     </row>
     <row r="41" ht="27.75" customHeight="1">
       <c r="A41" s="1"/>
-      <c r="B41" s="50"/>
+      <c r="B41" s="51"/>
       <c r="C41" s="45" t="s">
         <v>42</v>
       </c>
-      <c r="D41" s="50"/>
-      <c r="E41" s="50"/>
-      <c r="F41" s="50"/>
-      <c r="G41" s="50"/>
-      <c r="H41" s="50"/>
-      <c r="I41" s="50"/>
+      <c r="D41" s="51"/>
+      <c r="E41" s="51"/>
+      <c r="F41" s="51"/>
+      <c r="G41" s="51"/>
+      <c r="H41" s="51"/>
+      <c r="I41" s="51"/>
       <c r="J41" s="35"/>
-      <c r="K41" s="52"/>
-      <c r="L41" s="53"/>
-      <c r="M41" s="83"/>
-      <c r="N41" s="83"/>
+      <c r="K41" s="55"/>
+      <c r="L41" s="56"/>
+      <c r="M41" s="84"/>
+      <c r="N41" s="84"/>
       <c r="P41" s="46"/>
       <c r="Q41" s="85"/>
       <c r="R41" s="46"/>
@@ -7222,8 +7222,8 @@
       <c r="T41" s="39"/>
     </row>
     <row r="42" ht="15.75" customHeight="1">
-      <c r="A42" s="55"/>
-      <c r="B42" s="58"/>
+      <c r="A42" s="58"/>
+      <c r="B42" s="59"/>
       <c r="C42" s="60"/>
       <c r="D42" s="60"/>
       <c r="E42" s="60"/>
@@ -7471,7 +7471,7 @@
         <f t="shared" ref="R48:R52" si="11">P48*Q48</f>
         <v>0</v>
       </c>
-      <c r="S48" s="77">
+      <c r="S48" s="76">
         <v>0.98</v>
       </c>
       <c r="T48" s="39"/>
@@ -7482,10 +7482,10 @@
       <c r="C49" s="98" t="s">
         <v>58</v>
       </c>
-      <c r="D49" s="59" t="s">
+      <c r="D49" s="53" t="s">
         <v>56</v>
       </c>
-      <c r="E49" s="100" t="s">
+      <c r="E49" s="99" t="s">
         <v>57</v>
       </c>
       <c r="F49" s="44"/>
@@ -7494,25 +7494,25 @@
       <c r="I49" s="44"/>
       <c r="J49" s="35"/>
       <c r="K49" s="46"/>
-      <c r="L49" s="101">
+      <c r="L49" s="100">
         <v>155.0</v>
       </c>
-      <c r="M49" s="102">
+      <c r="M49" s="101">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="N49" s="102">
+      <c r="N49" s="101">
         <v>0.0</v>
       </c>
       <c r="O49" s="57"/>
-      <c r="P49" s="103">
+      <c r="P49" s="102">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="Q49" s="104">
+      <c r="Q49" s="103">
         <v>0.0</v>
       </c>
-      <c r="R49" s="105">
+      <c r="R49" s="104">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
@@ -7527,10 +7527,10 @@
       <c r="C50" s="98" t="s">
         <v>59</v>
       </c>
-      <c r="D50" s="59" t="s">
+      <c r="D50" s="53" t="s">
         <v>56</v>
       </c>
-      <c r="E50" s="100" t="s">
+      <c r="E50" s="99" t="s">
         <v>57</v>
       </c>
       <c r="F50" s="44"/>
@@ -7539,25 +7539,25 @@
       <c r="I50" s="44"/>
       <c r="J50" s="35"/>
       <c r="K50" s="46"/>
-      <c r="L50" s="101">
+      <c r="L50" s="100">
         <v>177.0</v>
       </c>
-      <c r="M50" s="102">
+      <c r="M50" s="101">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="N50" s="102">
+      <c r="N50" s="101">
         <v>0.0</v>
       </c>
       <c r="O50" s="57"/>
-      <c r="P50" s="103">
+      <c r="P50" s="102">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="Q50" s="104">
+      <c r="Q50" s="103">
         <v>0.0</v>
       </c>
-      <c r="R50" s="105">
+      <c r="R50" s="104">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
@@ -7606,14 +7606,14 @@
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="S51" s="77">
+      <c r="S51" s="76">
         <v>0.98</v>
       </c>
       <c r="T51" s="39"/>
     </row>
     <row r="52" ht="25.5" customHeight="1">
       <c r="A52" s="1"/>
-      <c r="B52" s="50"/>
+      <c r="B52" s="51"/>
       <c r="C52" s="94" t="s">
         <v>61</v>
       </c>
@@ -7623,12 +7623,12 @@
       <c r="E52" s="95" t="s">
         <v>62</v>
       </c>
-      <c r="F52" s="50"/>
-      <c r="G52" s="50"/>
-      <c r="H52" s="50"/>
-      <c r="I52" s="50"/>
+      <c r="F52" s="51"/>
+      <c r="G52" s="51"/>
+      <c r="H52" s="51"/>
+      <c r="I52" s="51"/>
       <c r="J52" s="35"/>
-      <c r="K52" s="52"/>
+      <c r="K52" s="55"/>
       <c r="L52" s="96">
         <v>25.0</v>
       </c>
@@ -7644,21 +7644,21 @@
         <f t="shared" si="10"/>
         <v>4800000</v>
       </c>
-      <c r="Q52" s="99">
+      <c r="Q52" s="106">
         <v>0.01</v>
       </c>
       <c r="R52" s="42">
         <f t="shared" si="11"/>
         <v>48000</v>
       </c>
-      <c r="S52" s="77">
+      <c r="S52" s="76">
         <v>0.7</v>
       </c>
       <c r="T52" s="39"/>
     </row>
     <row r="53" ht="15.75" customHeight="1">
-      <c r="A53" s="55"/>
-      <c r="B53" s="58"/>
+      <c r="A53" s="58"/>
+      <c r="B53" s="59"/>
       <c r="C53" s="60"/>
       <c r="D53" s="60"/>
       <c r="E53" s="60"/>
@@ -7685,14 +7685,14 @@
         <f>SUM(P48:P52)</f>
         <v>7805423.695</v>
       </c>
-      <c r="Q53" s="106" t="s">
+      <c r="Q53" s="107" t="s">
         <v>63</v>
       </c>
       <c r="R53" s="63">
         <f>SUM(R48:R52)</f>
         <v>48000</v>
       </c>
-      <c r="S53" s="107" t="s">
+      <c r="S53" s="108" t="s">
         <v>63</v>
       </c>
       <c r="T53" s="62"/>
@@ -7841,20 +7841,20 @@
       <c r="T58" s="22"/>
     </row>
     <row r="59" ht="55.5" customHeight="1">
-      <c r="A59" s="51"/>
-      <c r="B59" s="116" t="s">
+      <c r="A59" s="50"/>
+      <c r="B59" s="110" t="s">
         <v>30</v>
       </c>
-      <c r="C59" s="56" t="s">
+      <c r="C59" s="52" t="s">
         <v>65</v>
       </c>
-      <c r="D59" s="117" t="s">
+      <c r="D59" s="111" t="s">
         <v>32</v>
       </c>
-      <c r="E59" s="56" t="s">
+      <c r="E59" s="52" t="s">
         <v>66</v>
       </c>
-      <c r="F59" s="118" t="str">
+      <c r="F59" s="112" t="str">
         <f t="shared" ref="F59:I59" si="13">F21</f>
         <v>Faixa etária: 18 a 39 anos (Millennials e Gen Z adultos)
 Gênero: Maioria masculina (~65%), com presença feminina expressiva e em expansão (~35%)
@@ -7862,7 +7862,7 @@
 Perfil profissional: Executivos, profissionais liberais, gestores e especialistas (TI, finanças, negócios)
 Estilo de vida: Urbano, altamente digitalized, social e consumidor de cultura global.</v>
       </c>
-      <c r="G59" s="118" t="str">
+      <c r="G59" s="112" t="str">
         <f t="shared" si="13"/>
         <v>Esportes americanos (futebol americano / NFL, NBA) e Fantasy Football
 Jogos virtuais e eSports (destaque para o game Madden NFL)
@@ -7870,26 +7870,26 @@
 Consumo via streaming, mídias digitais e redes sociais em tempo real
 Produtos oficiais, colecionáveis esportivos e moda streetwear.</v>
       </c>
-      <c r="H59" s="118" t="str">
+      <c r="H59" s="112" t="str">
         <f t="shared" si="13"/>
         <v>Brasil</v>
       </c>
-      <c r="I59" s="118">
+      <c r="I59" s="112">
         <f t="shared" si="13"/>
         <v>4</v>
       </c>
       <c r="J59" s="54"/>
-      <c r="K59" s="119" t="s">
+      <c r="K59" s="113" t="s">
         <v>67</v>
       </c>
-      <c r="L59" s="120">
+      <c r="L59" s="114">
         <v>0.9</v>
       </c>
-      <c r="M59" s="102">
+      <c r="M59" s="101">
         <f>N59/80%</f>
         <v>0</v>
       </c>
-      <c r="N59" s="102">
+      <c r="N59" s="101">
         <v>0.0</v>
       </c>
       <c r="O59" s="57"/>
@@ -7897,10 +7897,10 @@
         <f>R59/Q59</f>
         <v>0</v>
       </c>
-      <c r="Q59" s="104">
+      <c r="Q59" s="103">
         <v>0.01</v>
       </c>
-      <c r="R59" s="105">
+      <c r="R59" s="104">
         <f>N59/L59</f>
         <v>0</v>
       </c>
@@ -7910,8 +7910,8 @@
       <c r="T59" s="57"/>
     </row>
     <row r="60" ht="15.75" customHeight="1">
-      <c r="A60" s="55"/>
-      <c r="B60" s="58"/>
+      <c r="A60" s="58"/>
+      <c r="B60" s="59"/>
       <c r="C60" s="60"/>
       <c r="D60" s="60"/>
       <c r="E60" s="60"/>
@@ -8100,16 +8100,16 @@
       <c r="B66" s="31" t="s">
         <v>30</v>
       </c>
-      <c r="C66" s="111" t="s">
+      <c r="C66" s="116" t="s">
         <v>69</v>
       </c>
       <c r="D66" s="72" t="s">
         <v>70</v>
       </c>
-      <c r="E66" s="111" t="s">
+      <c r="E66" s="116" t="s">
         <v>71</v>
       </c>
-      <c r="F66" s="121" t="str">
+      <c r="F66" s="123" t="str">
         <f t="shared" ref="F66:H66" si="15">F21</f>
         <v>Faixa etária: 18 a 39 anos (Millennials e Gen Z adultos)
 Gênero: Maioria masculina (~65%), com presença feminina expressiva e em expansão (~35%)
@@ -8117,7 +8117,7 @@
 Perfil profissional: Executivos, profissionais liberais, gestores e especialistas (TI, finanças, negócios)
 Estilo de vida: Urbano, altamente digitalized, social e consumidor de cultura global.</v>
       </c>
-      <c r="G66" s="121" t="str">
+      <c r="G66" s="123" t="str">
         <f t="shared" si="15"/>
         <v>Esportes americanos (futebol americano / NFL, NBA) e Fantasy Football
 Jogos virtuais e eSports (destaque para o game Madden NFL)
@@ -8125,18 +8125,18 @@
 Consumo via streaming, mídias digitais e redes sociais em tempo real
 Produtos oficiais, colecionáveis esportivos e moda streetwear.</v>
       </c>
-      <c r="H66" s="121" t="str">
+      <c r="H66" s="123" t="str">
         <f t="shared" si="15"/>
         <v>Brasil</v>
       </c>
-      <c r="I66" s="121">
+      <c r="I66" s="123">
         <v>2.0</v>
       </c>
       <c r="J66" s="35"/>
       <c r="K66" s="72" t="s">
         <v>72</v>
       </c>
-      <c r="L66" s="115">
+      <c r="L66" s="120">
         <v>0.7</v>
       </c>
       <c r="M66" s="38">
@@ -8147,7 +8147,7 @@
         <v>60000.0</v>
       </c>
       <c r="O66" s="39"/>
-      <c r="P66" s="76">
+      <c r="P66" s="75">
         <f t="shared" ref="P66:P67" si="17">N66/L66</f>
         <v>85714.28571</v>
       </c>
@@ -8164,33 +8164,33 @@
       <c r="T66" s="39"/>
     </row>
     <row r="67" ht="36.75" customHeight="1">
-      <c r="A67" s="51"/>
-      <c r="B67" s="50"/>
-      <c r="C67" s="56" t="s">
+      <c r="A67" s="50"/>
+      <c r="B67" s="51"/>
+      <c r="C67" s="52" t="s">
         <v>73</v>
       </c>
-      <c r="D67" s="52"/>
-      <c r="E67" s="56" t="s">
+      <c r="D67" s="55"/>
+      <c r="E67" s="52" t="s">
         <v>71</v>
       </c>
       <c r="F67" s="122"/>
       <c r="G67" s="122"/>
       <c r="H67" s="122"/>
-      <c r="I67" s="123">
+      <c r="I67" s="121">
         <v>1.0</v>
       </c>
       <c r="J67" s="54"/>
-      <c r="K67" s="80" t="s">
+      <c r="K67" s="78" t="s">
         <v>72</v>
       </c>
-      <c r="L67" s="120">
+      <c r="L67" s="114">
         <v>0.7</v>
       </c>
-      <c r="M67" s="102">
+      <c r="M67" s="101">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="N67" s="102">
+      <c r="N67" s="101">
         <v>0.0</v>
       </c>
       <c r="O67" s="57"/>
@@ -8198,10 +8198,10 @@
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="Q67" s="104">
+      <c r="Q67" s="103">
         <v>0.02</v>
       </c>
-      <c r="R67" s="105">
+      <c r="R67" s="104">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
@@ -8209,8 +8209,8 @@
       <c r="T67" s="57"/>
     </row>
     <row r="68" ht="15.75" customHeight="1">
-      <c r="A68" s="55"/>
-      <c r="B68" s="58"/>
+      <c r="A68" s="58"/>
+      <c r="B68" s="59"/>
       <c r="C68" s="60"/>
       <c r="D68" s="60"/>
       <c r="E68" s="60"/>
@@ -8660,7 +8660,7 @@
         <v>93</v>
       </c>
       <c r="D82" s="159" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G82" s="139"/>
       <c r="H82" s="139"/>
@@ -8684,7 +8684,7 @@
       </c>
       <c r="C83" s="161"/>
       <c r="D83" s="162" t="s">
-        <v>112</v>
+        <v>96</v>
       </c>
       <c r="F83" s="163"/>
       <c r="H83" s="139"/>
@@ -8729,7 +8729,7 @@
     <row r="85" ht="15.75" customHeight="1">
       <c r="A85" s="6"/>
       <c r="B85" s="160" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C85" s="161"/>
       <c r="D85" s="162" t="s">
@@ -8753,11 +8753,11 @@
     <row r="86" ht="15.75" customHeight="1">
       <c r="A86" s="6"/>
       <c r="B86" s="160" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C86" s="161"/>
       <c r="D86" s="162" t="s">
-        <v>116</v>
+        <v>101</v>
       </c>
       <c r="F86" s="163"/>
       <c r="G86" s="139"/>
@@ -8778,11 +8778,11 @@
     <row r="87" ht="15.75" customHeight="1">
       <c r="A87" s="6"/>
       <c r="B87" s="160" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C87" s="161"/>
       <c r="D87" s="162" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F87" s="163"/>
       <c r="H87" s="139"/>
@@ -8802,11 +8802,11 @@
     <row r="88" ht="15.75" customHeight="1">
       <c r="A88" s="6"/>
       <c r="B88" s="160" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C88" s="161"/>
       <c r="D88" s="162" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F88" s="163"/>
       <c r="G88" s="139"/>
@@ -8827,11 +8827,11 @@
     <row r="89" ht="15.75" customHeight="1">
       <c r="A89" s="6"/>
       <c r="B89" s="164" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C89" s="165"/>
       <c r="D89" s="166" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E89" s="167"/>
       <c r="F89" s="168"/>
@@ -9230,7 +9230,7 @@
     <row r="10">
       <c r="A10" s="1"/>
       <c r="B10" s="13" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C10" s="14">
         <f>C9/80%</f>
@@ -9257,7 +9257,7 @@
     <row r="11">
       <c r="A11" s="1"/>
       <c r="B11" s="8" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C11" s="12">
         <f>N72</f>
@@ -9284,7 +9284,7 @@
     <row r="12">
       <c r="A12" s="1"/>
       <c r="B12" s="13" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C12" s="14">
         <f>C11/80%</f>
@@ -9333,7 +9333,7 @@
     <row r="14" ht="15.75" customHeight="1">
       <c r="A14" s="1"/>
       <c r="B14" s="15" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15" ht="15.75" customHeight="1">
@@ -9695,24 +9695,24 @@
       <c r="T27" s="39"/>
     </row>
     <row r="28" ht="32.25" customHeight="1">
-      <c r="A28" s="51"/>
-      <c r="B28" s="50"/>
-      <c r="C28" s="56" t="s">
+      <c r="A28" s="50"/>
+      <c r="B28" s="51"/>
+      <c r="C28" s="52" t="s">
         <v>46</v>
       </c>
-      <c r="D28" s="50"/>
-      <c r="E28" s="50"/>
-      <c r="F28" s="59" t="s">
+      <c r="D28" s="51"/>
+      <c r="E28" s="51"/>
+      <c r="F28" s="53" t="s">
         <v>47</v>
       </c>
-      <c r="G28" s="50"/>
-      <c r="H28" s="59" t="s">
+      <c r="G28" s="51"/>
+      <c r="H28" s="53" t="s">
         <v>45</v>
       </c>
-      <c r="I28" s="50"/>
+      <c r="I28" s="51"/>
       <c r="J28" s="54"/>
-      <c r="K28" s="52"/>
-      <c r="L28" s="53"/>
+      <c r="K28" s="55"/>
+      <c r="L28" s="56"/>
       <c r="M28" s="48"/>
       <c r="N28" s="48"/>
       <c r="P28" s="44"/>
@@ -9721,8 +9721,8 @@
       <c r="T28" s="57"/>
     </row>
     <row r="29" ht="15.75" customHeight="1">
-      <c r="A29" s="55"/>
-      <c r="B29" s="58"/>
+      <c r="A29" s="58"/>
+      <c r="B29" s="59"/>
       <c r="C29" s="60"/>
       <c r="D29" s="60"/>
       <c r="E29" s="60"/>
@@ -9907,7 +9907,7 @@
       <c r="T34" s="22"/>
     </row>
     <row r="35" ht="27.75" customHeight="1">
-      <c r="A35" s="51"/>
+      <c r="A35" s="50"/>
       <c r="B35" s="71" t="s">
         <v>30</v>
       </c>
@@ -9917,10 +9917,10 @@
       <c r="D35" s="73" t="s">
         <v>32</v>
       </c>
-      <c r="E35" s="59" t="s">
+      <c r="E35" s="53" t="s">
         <v>52</v>
       </c>
-      <c r="F35" s="59" t="str">
+      <c r="F35" s="53" t="str">
         <f t="shared" ref="F35:I35" si="3">F21</f>
         <v>Faixa etária: 18 a 39 anos (Millennials e Gen Z adultos)
 Gênero: Maioria masculina (~65%), com presença feminina expressiva e em expansão (~35%)
@@ -9928,7 +9928,7 @@
 Perfil profissional: Executivos, profissionais liberais, gestores e especialistas (TI, finanças, negócios)
 Estilo de vida: Urbano, altamente digitalized, social e consumidor de cultura global.</v>
       </c>
-      <c r="G35" s="59" t="str">
+      <c r="G35" s="53" t="str">
         <f t="shared" si="3"/>
         <v>Esportes americanos (futebol americano / NFL, NBA) e Fantasy Football
 Jogos virtuais e eSports (destaque para o game Madden NFL)
@@ -9936,26 +9936,26 @@
 Consumo via streaming, mídias digitais e redes sociais em tempo real
 Produtos oficiais, colecionáveis esportivos e moda streetwear.</v>
       </c>
-      <c r="H35" s="59" t="str">
+      <c r="H35" s="53" t="str">
         <f t="shared" si="3"/>
         <v>Brasil</v>
       </c>
-      <c r="I35" s="59">
+      <c r="I35" s="53">
         <f t="shared" si="3"/>
         <v>4</v>
       </c>
       <c r="J35" s="54"/>
-      <c r="K35" s="80" t="s">
+      <c r="K35" s="78" t="s">
         <v>37</v>
       </c>
-      <c r="L35" s="75">
+      <c r="L35" s="77">
         <v>40.0</v>
       </c>
-      <c r="M35" s="78">
+      <c r="M35" s="80">
         <f t="shared" ref="M35:M36" si="4">N35/80%</f>
         <v>0</v>
       </c>
-      <c r="N35" s="78">
+      <c r="N35" s="80">
         <v>0.0</v>
       </c>
       <c r="O35" s="57"/>
@@ -9970,19 +9970,19 @@
         <f t="shared" ref="R35:R36" si="6">P35*Q35</f>
         <v>0</v>
       </c>
-      <c r="S35" s="84">
+      <c r="S35" s="83">
         <v>0.7</v>
       </c>
       <c r="T35" s="57"/>
     </row>
     <row r="36" ht="27.75" customHeight="1">
-      <c r="A36" s="51"/>
+      <c r="A36" s="50"/>
       <c r="B36" s="44"/>
       <c r="C36" s="70" t="s">
         <v>31</v>
       </c>
       <c r="D36" s="44"/>
-      <c r="E36" s="59" t="s">
+      <c r="E36" s="53" t="s">
         <v>53</v>
       </c>
       <c r="F36" s="44"/>
@@ -9991,14 +9991,14 @@
       <c r="I36" s="44"/>
       <c r="J36" s="54"/>
       <c r="K36" s="46"/>
-      <c r="L36" s="75">
+      <c r="L36" s="77">
         <v>24.0</v>
       </c>
-      <c r="M36" s="78">
+      <c r="M36" s="80">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="N36" s="78">
+      <c r="N36" s="80">
         <v>0.0</v>
       </c>
       <c r="O36" s="57"/>
@@ -10006,7 +10006,7 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="Q36" s="84">
+      <c r="Q36" s="83">
         <v>0.4</v>
       </c>
       <c r="R36" s="81">
@@ -10017,9 +10017,9 @@
       <c r="T36" s="57"/>
     </row>
     <row r="37" ht="27.75" customHeight="1">
-      <c r="A37" s="51"/>
+      <c r="A37" s="50"/>
       <c r="B37" s="44"/>
-      <c r="C37" s="56" t="s">
+      <c r="C37" s="52" t="s">
         <v>38</v>
       </c>
       <c r="D37" s="44"/>
@@ -10031,8 +10031,8 @@
       <c r="J37" s="54"/>
       <c r="K37" s="46"/>
       <c r="L37" s="47"/>
-      <c r="M37" s="83"/>
-      <c r="N37" s="83"/>
+      <c r="M37" s="84"/>
+      <c r="N37" s="84"/>
       <c r="P37" s="46"/>
       <c r="Q37" s="48"/>
       <c r="R37" s="46"/>
@@ -10040,9 +10040,9 @@
       <c r="T37" s="57"/>
     </row>
     <row r="38" ht="27.75" customHeight="1">
-      <c r="A38" s="51"/>
+      <c r="A38" s="50"/>
       <c r="B38" s="44"/>
-      <c r="C38" s="56" t="s">
+      <c r="C38" s="52" t="s">
         <v>39</v>
       </c>
       <c r="D38" s="44"/>
@@ -10054,8 +10054,8 @@
       <c r="J38" s="54"/>
       <c r="K38" s="46"/>
       <c r="L38" s="47"/>
-      <c r="M38" s="83"/>
-      <c r="N38" s="83"/>
+      <c r="M38" s="84"/>
+      <c r="N38" s="84"/>
       <c r="P38" s="46"/>
       <c r="Q38" s="48"/>
       <c r="R38" s="46"/>
@@ -10063,9 +10063,9 @@
       <c r="T38" s="57"/>
     </row>
     <row r="39" ht="27.75" customHeight="1">
-      <c r="A39" s="51"/>
+      <c r="A39" s="50"/>
       <c r="B39" s="44"/>
-      <c r="C39" s="56" t="s">
+      <c r="C39" s="52" t="s">
         <v>40</v>
       </c>
       <c r="D39" s="44"/>
@@ -10077,8 +10077,8 @@
       <c r="J39" s="54"/>
       <c r="K39" s="46"/>
       <c r="L39" s="47"/>
-      <c r="M39" s="83"/>
-      <c r="N39" s="83"/>
+      <c r="M39" s="84"/>
+      <c r="N39" s="84"/>
       <c r="P39" s="46"/>
       <c r="Q39" s="48"/>
       <c r="R39" s="46"/>
@@ -10086,9 +10086,9 @@
       <c r="T39" s="57"/>
     </row>
     <row r="40" ht="27.75" customHeight="1">
-      <c r="A40" s="51"/>
+      <c r="A40" s="50"/>
       <c r="B40" s="44"/>
-      <c r="C40" s="56" t="s">
+      <c r="C40" s="52" t="s">
         <v>41</v>
       </c>
       <c r="D40" s="44"/>
@@ -10100,8 +10100,8 @@
       <c r="J40" s="54"/>
       <c r="K40" s="46"/>
       <c r="L40" s="47"/>
-      <c r="M40" s="83"/>
-      <c r="N40" s="83"/>
+      <c r="M40" s="84"/>
+      <c r="N40" s="84"/>
       <c r="P40" s="46"/>
       <c r="Q40" s="48"/>
       <c r="R40" s="46"/>
@@ -10109,22 +10109,22 @@
       <c r="T40" s="57"/>
     </row>
     <row r="41" ht="27.75" customHeight="1">
-      <c r="A41" s="51"/>
-      <c r="B41" s="50"/>
-      <c r="C41" s="56" t="s">
+      <c r="A41" s="50"/>
+      <c r="B41" s="51"/>
+      <c r="C41" s="52" t="s">
         <v>42</v>
       </c>
-      <c r="D41" s="50"/>
-      <c r="E41" s="50"/>
-      <c r="F41" s="50"/>
-      <c r="G41" s="50"/>
-      <c r="H41" s="50"/>
-      <c r="I41" s="50"/>
+      <c r="D41" s="51"/>
+      <c r="E41" s="51"/>
+      <c r="F41" s="51"/>
+      <c r="G41" s="51"/>
+      <c r="H41" s="51"/>
+      <c r="I41" s="51"/>
       <c r="J41" s="54"/>
-      <c r="K41" s="52"/>
-      <c r="L41" s="53"/>
-      <c r="M41" s="83"/>
-      <c r="N41" s="83"/>
+      <c r="K41" s="55"/>
+      <c r="L41" s="56"/>
+      <c r="M41" s="84"/>
+      <c r="N41" s="84"/>
       <c r="P41" s="46"/>
       <c r="Q41" s="85"/>
       <c r="R41" s="46"/>
@@ -10132,8 +10132,8 @@
       <c r="T41" s="57"/>
     </row>
     <row r="42" ht="15.75" customHeight="1">
-      <c r="A42" s="55"/>
-      <c r="B42" s="58"/>
+      <c r="A42" s="58"/>
+      <c r="B42" s="59"/>
       <c r="C42" s="60"/>
       <c r="D42" s="60"/>
       <c r="E42" s="60"/>
@@ -10381,7 +10381,7 @@
         <f t="shared" ref="R48:R52" si="11">P48*Q48</f>
         <v>0</v>
       </c>
-      <c r="S48" s="77">
+      <c r="S48" s="76">
         <v>0.98</v>
       </c>
       <c r="T48" s="39"/>
@@ -10392,10 +10392,10 @@
       <c r="C49" s="98" t="s">
         <v>58</v>
       </c>
-      <c r="D49" s="59" t="s">
+      <c r="D49" s="53" t="s">
         <v>56</v>
       </c>
-      <c r="E49" s="100" t="s">
+      <c r="E49" s="99" t="s">
         <v>57</v>
       </c>
       <c r="F49" s="44"/>
@@ -10404,25 +10404,25 @@
       <c r="I49" s="44"/>
       <c r="J49" s="35"/>
       <c r="K49" s="46"/>
-      <c r="L49" s="101">
+      <c r="L49" s="100">
         <v>155.0</v>
       </c>
-      <c r="M49" s="102">
+      <c r="M49" s="101">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="N49" s="102">
+      <c r="N49" s="101">
         <v>0.0</v>
       </c>
       <c r="O49" s="57"/>
-      <c r="P49" s="103">
+      <c r="P49" s="102">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="Q49" s="104">
+      <c r="Q49" s="103">
         <v>0.0</v>
       </c>
-      <c r="R49" s="105">
+      <c r="R49" s="104">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
@@ -10437,10 +10437,10 @@
       <c r="C50" s="98" t="s">
         <v>59</v>
       </c>
-      <c r="D50" s="59" t="s">
+      <c r="D50" s="53" t="s">
         <v>56</v>
       </c>
-      <c r="E50" s="100" t="s">
+      <c r="E50" s="99" t="s">
         <v>57</v>
       </c>
       <c r="F50" s="44"/>
@@ -10449,25 +10449,25 @@
       <c r="I50" s="44"/>
       <c r="J50" s="35"/>
       <c r="K50" s="46"/>
-      <c r="L50" s="101">
+      <c r="L50" s="100">
         <v>177.0</v>
       </c>
-      <c r="M50" s="102">
+      <c r="M50" s="101">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="N50" s="102">
+      <c r="N50" s="101">
         <v>0.0</v>
       </c>
       <c r="O50" s="57"/>
-      <c r="P50" s="103">
+      <c r="P50" s="102">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="Q50" s="104">
+      <c r="Q50" s="103">
         <v>0.0</v>
       </c>
-      <c r="R50" s="105">
+      <c r="R50" s="104">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
@@ -10516,48 +10516,48 @@
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="S51" s="77">
+      <c r="S51" s="76">
         <v>0.98</v>
       </c>
       <c r="T51" s="39"/>
     </row>
     <row r="52" ht="25.5" customHeight="1">
-      <c r="A52" s="51"/>
-      <c r="B52" s="50"/>
+      <c r="A52" s="50"/>
+      <c r="B52" s="51"/>
       <c r="C52" s="98" t="s">
         <v>61</v>
       </c>
       <c r="D52" s="73" t="s">
         <v>32</v>
       </c>
-      <c r="E52" s="100" t="s">
+      <c r="E52" s="99" t="s">
         <v>62</v>
       </c>
-      <c r="F52" s="50"/>
-      <c r="G52" s="50"/>
-      <c r="H52" s="50"/>
-      <c r="I52" s="50"/>
+      <c r="F52" s="51"/>
+      <c r="G52" s="51"/>
+      <c r="H52" s="51"/>
+      <c r="I52" s="51"/>
       <c r="J52" s="54"/>
-      <c r="K52" s="52"/>
-      <c r="L52" s="101">
+      <c r="K52" s="55"/>
+      <c r="L52" s="100">
         <v>25.0</v>
       </c>
-      <c r="M52" s="102">
+      <c r="M52" s="101">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="N52" s="102">
+      <c r="N52" s="101">
         <v>0.0</v>
       </c>
       <c r="O52" s="57"/>
-      <c r="P52" s="103">
+      <c r="P52" s="102">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="Q52" s="108">
+      <c r="Q52" s="105">
         <v>0.01</v>
       </c>
-      <c r="R52" s="105">
+      <c r="R52" s="104">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
@@ -10567,8 +10567,8 @@
       <c r="T52" s="57"/>
     </row>
     <row r="53" ht="15.75" customHeight="1">
-      <c r="A53" s="55"/>
-      <c r="B53" s="58"/>
+      <c r="A53" s="58"/>
+      <c r="B53" s="59"/>
       <c r="C53" s="60"/>
       <c r="D53" s="60"/>
       <c r="E53" s="60"/>
@@ -10595,14 +10595,14 @@
         <f>SUM(P48:P52)</f>
         <v>3005423.695</v>
       </c>
-      <c r="Q53" s="106" t="s">
+      <c r="Q53" s="107" t="s">
         <v>63</v>
       </c>
       <c r="R53" s="63">
         <f>SUM(R48:R52)</f>
         <v>0</v>
       </c>
-      <c r="S53" s="107" t="s">
+      <c r="S53" s="108" t="s">
         <v>63</v>
       </c>
       <c r="T53" s="62"/>
@@ -10751,20 +10751,20 @@
       <c r="T58" s="22"/>
     </row>
     <row r="59" ht="55.5" customHeight="1">
-      <c r="A59" s="51"/>
-      <c r="B59" s="116" t="s">
+      <c r="A59" s="50"/>
+      <c r="B59" s="110" t="s">
         <v>30</v>
       </c>
-      <c r="C59" s="56" t="s">
+      <c r="C59" s="52" t="s">
         <v>65</v>
       </c>
-      <c r="D59" s="117" t="s">
+      <c r="D59" s="111" t="s">
         <v>32</v>
       </c>
-      <c r="E59" s="56" t="s">
+      <c r="E59" s="52" t="s">
         <v>66</v>
       </c>
-      <c r="F59" s="118" t="str">
+      <c r="F59" s="112" t="str">
         <f t="shared" ref="F59:I59" si="13">F21</f>
         <v>Faixa etária: 18 a 39 anos (Millennials e Gen Z adultos)
 Gênero: Maioria masculina (~65%), com presença feminina expressiva e em expansão (~35%)
@@ -10772,7 +10772,7 @@
 Perfil profissional: Executivos, profissionais liberais, gestores e especialistas (TI, finanças, negócios)
 Estilo de vida: Urbano, altamente digitalized, social e consumidor de cultura global.</v>
       </c>
-      <c r="G59" s="118" t="str">
+      <c r="G59" s="112" t="str">
         <f t="shared" si="13"/>
         <v>Esportes americanos (futebol americano / NFL, NBA) e Fantasy Football
 Jogos virtuais e eSports (destaque para o game Madden NFL)
@@ -10780,26 +10780,26 @@
 Consumo via streaming, mídias digitais e redes sociais em tempo real
 Produtos oficiais, colecionáveis esportivos e moda streetwear.</v>
       </c>
-      <c r="H59" s="118" t="str">
+      <c r="H59" s="112" t="str">
         <f t="shared" si="13"/>
         <v>Brasil</v>
       </c>
-      <c r="I59" s="118">
+      <c r="I59" s="112">
         <f t="shared" si="13"/>
         <v>4</v>
       </c>
       <c r="J59" s="54"/>
-      <c r="K59" s="119" t="s">
+      <c r="K59" s="113" t="s">
         <v>67</v>
       </c>
-      <c r="L59" s="120">
+      <c r="L59" s="114">
         <v>0.9</v>
       </c>
-      <c r="M59" s="102">
+      <c r="M59" s="101">
         <f>N59/80%</f>
         <v>0</v>
       </c>
-      <c r="N59" s="102">
+      <c r="N59" s="101">
         <v>0.0</v>
       </c>
       <c r="O59" s="57"/>
@@ -10807,10 +10807,10 @@
         <f>R59/Q59</f>
         <v>0</v>
       </c>
-      <c r="Q59" s="104">
+      <c r="Q59" s="103">
         <v>0.01</v>
       </c>
-      <c r="R59" s="105">
+      <c r="R59" s="104">
         <f>N59/L59</f>
         <v>0</v>
       </c>
@@ -10820,8 +10820,8 @@
       <c r="T59" s="57"/>
     </row>
     <row r="60" ht="15.75" customHeight="1">
-      <c r="A60" s="55"/>
-      <c r="B60" s="58"/>
+      <c r="A60" s="58"/>
+      <c r="B60" s="59"/>
       <c r="C60" s="60"/>
       <c r="D60" s="60"/>
       <c r="E60" s="60"/>
@@ -11006,20 +11006,20 @@
       <c r="T65" s="22"/>
     </row>
     <row r="66" ht="36.75" customHeight="1">
-      <c r="A66" s="51"/>
+      <c r="A66" s="50"/>
       <c r="B66" s="71" t="s">
         <v>30</v>
       </c>
-      <c r="C66" s="56" t="s">
+      <c r="C66" s="52" t="s">
         <v>69</v>
       </c>
-      <c r="D66" s="80" t="s">
+      <c r="D66" s="78" t="s">
         <v>70</v>
       </c>
-      <c r="E66" s="56" t="s">
+      <c r="E66" s="52" t="s">
         <v>71</v>
       </c>
-      <c r="F66" s="123" t="str">
+      <c r="F66" s="121" t="str">
         <f t="shared" ref="F66:H66" si="15">F21</f>
         <v>Faixa etária: 18 a 39 anos (Millennials e Gen Z adultos)
 Gênero: Maioria masculina (~65%), com presença feminina expressiva e em expansão (~35%)
@@ -11027,7 +11027,7 @@
 Perfil profissional: Executivos, profissionais liberais, gestores e especialistas (TI, finanças, negócios)
 Estilo de vida: Urbano, altamente digitalized, social e consumidor de cultura global.</v>
       </c>
-      <c r="G66" s="123" t="str">
+      <c r="G66" s="121" t="str">
         <f t="shared" si="15"/>
         <v>Esportes americanos (futebol americano / NFL, NBA) e Fantasy Football
 Jogos virtuais e eSports (destaque para o game Madden NFL)
@@ -11035,25 +11035,25 @@
 Consumo via streaming, mídias digitais e redes sociais em tempo real
 Produtos oficiais, colecionáveis esportivos e moda streetwear.</v>
       </c>
-      <c r="H66" s="123" t="str">
+      <c r="H66" s="121" t="str">
         <f t="shared" si="15"/>
         <v>Brasil</v>
       </c>
-      <c r="I66" s="123">
+      <c r="I66" s="121">
         <v>2.0</v>
       </c>
       <c r="J66" s="54"/>
-      <c r="K66" s="80" t="s">
+      <c r="K66" s="78" t="s">
         <v>72</v>
       </c>
-      <c r="L66" s="120">
+      <c r="L66" s="114">
         <v>0.7</v>
       </c>
-      <c r="M66" s="102">
+      <c r="M66" s="101">
         <f t="shared" ref="M66:M67" si="16">N66/80%</f>
         <v>0</v>
       </c>
-      <c r="N66" s="102">
+      <c r="N66" s="101">
         <v>0.0</v>
       </c>
       <c r="O66" s="57"/>
@@ -11061,46 +11061,46 @@
         <f t="shared" ref="P66:P67" si="17">N66/L66</f>
         <v>0</v>
       </c>
-      <c r="Q66" s="104">
+      <c r="Q66" s="103">
         <v>0.02</v>
       </c>
-      <c r="R66" s="105">
+      <c r="R66" s="104">
         <f t="shared" ref="R66:R67" si="18">P66*Q66</f>
         <v>0</v>
       </c>
-      <c r="S66" s="84">
+      <c r="S66" s="83">
         <v>0.9</v>
       </c>
       <c r="T66" s="57"/>
     </row>
     <row r="67" ht="36.75" customHeight="1">
-      <c r="A67" s="51"/>
-      <c r="B67" s="50"/>
-      <c r="C67" s="56" t="s">
+      <c r="A67" s="50"/>
+      <c r="B67" s="51"/>
+      <c r="C67" s="52" t="s">
         <v>73</v>
       </c>
-      <c r="D67" s="52"/>
-      <c r="E67" s="56" t="s">
+      <c r="D67" s="55"/>
+      <c r="E67" s="52" t="s">
         <v>71</v>
       </c>
       <c r="F67" s="122"/>
       <c r="G67" s="122"/>
       <c r="H67" s="122"/>
-      <c r="I67" s="123">
+      <c r="I67" s="121">
         <v>1.0</v>
       </c>
       <c r="J67" s="54"/>
-      <c r="K67" s="80" t="s">
+      <c r="K67" s="78" t="s">
         <v>72</v>
       </c>
-      <c r="L67" s="120">
+      <c r="L67" s="114">
         <v>0.7</v>
       </c>
-      <c r="M67" s="102">
+      <c r="M67" s="101">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="N67" s="102">
+      <c r="N67" s="101">
         <v>0.0</v>
       </c>
       <c r="O67" s="57"/>
@@ -11108,10 +11108,10 @@
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="Q67" s="104">
+      <c r="Q67" s="103">
         <v>0.02</v>
       </c>
-      <c r="R67" s="105">
+      <c r="R67" s="104">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
@@ -11119,8 +11119,8 @@
       <c r="T67" s="57"/>
     </row>
     <row r="68" ht="15.75" customHeight="1">
-      <c r="A68" s="55"/>
-      <c r="B68" s="58"/>
+      <c r="A68" s="58"/>
+      <c r="B68" s="59"/>
       <c r="C68" s="60"/>
       <c r="D68" s="60"/>
       <c r="E68" s="60"/>
@@ -11570,7 +11570,7 @@
         <v>93</v>
       </c>
       <c r="D82" s="159" t="s">
-        <v>115</v>
+        <v>94</v>
       </c>
       <c r="G82" s="139"/>
       <c r="H82" s="139"/>
@@ -11594,7 +11594,7 @@
       </c>
       <c r="C83" s="161"/>
       <c r="D83" s="162" t="s">
-        <v>112</v>
+        <v>96</v>
       </c>
       <c r="F83" s="163"/>
       <c r="H83" s="139"/>
@@ -11639,11 +11639,11 @@
     <row r="85" ht="15.75" customHeight="1">
       <c r="A85" s="6"/>
       <c r="B85" s="160" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C85" s="161"/>
       <c r="D85" s="162" t="s">
-        <v>111</v>
+        <v>99</v>
       </c>
       <c r="F85" s="163"/>
       <c r="H85" s="139"/>
@@ -11663,11 +11663,11 @@
     <row r="86" ht="15.75" customHeight="1">
       <c r="A86" s="6"/>
       <c r="B86" s="160" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C86" s="161"/>
       <c r="D86" s="162" t="s">
-        <v>116</v>
+        <v>101</v>
       </c>
       <c r="F86" s="163"/>
       <c r="G86" s="139"/>
@@ -11688,11 +11688,11 @@
     <row r="87" ht="15.75" customHeight="1">
       <c r="A87" s="6"/>
       <c r="B87" s="160" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C87" s="161"/>
       <c r="D87" s="162" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F87" s="163"/>
       <c r="H87" s="139"/>
@@ -11712,11 +11712,11 @@
     <row r="88" ht="15.75" customHeight="1">
       <c r="A88" s="6"/>
       <c r="B88" s="160" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C88" s="161"/>
       <c r="D88" s="162" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F88" s="163"/>
       <c r="G88" s="139"/>
@@ -11737,11 +11737,11 @@
     <row r="89" ht="15.75" customHeight="1">
       <c r="A89" s="6"/>
       <c r="B89" s="164" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C89" s="165"/>
       <c r="D89" s="166" t="s">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="E89" s="167"/>
       <c r="F89" s="168"/>
@@ -12113,7 +12113,7 @@
     <row r="9">
       <c r="A9" s="1"/>
       <c r="B9" s="8" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C9" s="12">
         <f t="shared" ref="C9:C10" si="1">N69</f>
@@ -12140,7 +12140,7 @@
     <row r="10">
       <c r="A10" s="1"/>
       <c r="B10" s="8" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C10" s="12">
         <f t="shared" si="1"/>
@@ -12189,7 +12189,7 @@
     <row r="12" ht="15.75" customHeight="1">
       <c r="A12" s="1"/>
       <c r="B12" s="15" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13" ht="15.75" customHeight="1">
@@ -12551,24 +12551,24 @@
       <c r="T25" s="39"/>
     </row>
     <row r="26" ht="32.25" customHeight="1">
-      <c r="A26" s="51"/>
-      <c r="B26" s="50"/>
-      <c r="C26" s="56" t="s">
+      <c r="A26" s="50"/>
+      <c r="B26" s="51"/>
+      <c r="C26" s="52" t="s">
         <v>46</v>
       </c>
-      <c r="D26" s="50"/>
-      <c r="E26" s="50"/>
-      <c r="F26" s="59" t="s">
+      <c r="D26" s="51"/>
+      <c r="E26" s="51"/>
+      <c r="F26" s="53" t="s">
         <v>47</v>
       </c>
-      <c r="G26" s="50"/>
-      <c r="H26" s="59" t="s">
+      <c r="G26" s="51"/>
+      <c r="H26" s="53" t="s">
         <v>45</v>
       </c>
-      <c r="I26" s="50"/>
+      <c r="I26" s="51"/>
       <c r="J26" s="54"/>
-      <c r="K26" s="52"/>
-      <c r="L26" s="53"/>
+      <c r="K26" s="55"/>
+      <c r="L26" s="56"/>
       <c r="M26" s="48"/>
       <c r="N26" s="48"/>
       <c r="P26" s="44"/>
@@ -12577,8 +12577,8 @@
       <c r="T26" s="57"/>
     </row>
     <row r="27" ht="15.75" customHeight="1">
-      <c r="A27" s="55"/>
-      <c r="B27" s="58"/>
+      <c r="A27" s="58"/>
+      <c r="B27" s="59"/>
       <c r="C27" s="60"/>
       <c r="D27" s="60"/>
       <c r="E27" s="60"/>
@@ -12763,7 +12763,7 @@
       <c r="T32" s="22"/>
     </row>
     <row r="33" ht="27.75" customHeight="1">
-      <c r="A33" s="51"/>
+      <c r="A33" s="50"/>
       <c r="B33" s="71" t="s">
         <v>30</v>
       </c>
@@ -12773,10 +12773,10 @@
       <c r="D33" s="73" t="s">
         <v>32</v>
       </c>
-      <c r="E33" s="59" t="s">
+      <c r="E33" s="53" t="s">
         <v>52</v>
       </c>
-      <c r="F33" s="59" t="str">
+      <c r="F33" s="53" t="str">
         <f t="shared" ref="F33:I33" si="4">F19</f>
         <v>Faixa etária: 18 a 39 anos (Millennials e Gen Z adultos)
 Gênero: Maioria masculina (~65%), com presença feminina expressiva e em expansão (~35%)
@@ -12784,7 +12784,7 @@
 Perfil profissional: Executivos, profissionais liberais, gestores e especialistas (TI, finanças, negócios)
 Estilo de vida: Urbano, altamente digitalized, social e consumidor de cultura global.</v>
       </c>
-      <c r="G33" s="59" t="str">
+      <c r="G33" s="53" t="str">
         <f t="shared" si="4"/>
         <v>Esportes americanos (futebol americano / NFL, NBA) e Fantasy Football
 Jogos virtuais e eSports (destaque para o game Madden NFL)
@@ -12792,26 +12792,26 @@
 Consumo via streaming, mídias digitais e redes sociais em tempo real
 Produtos oficiais, colecionáveis esportivos e moda streetwear.</v>
       </c>
-      <c r="H33" s="59" t="str">
+      <c r="H33" s="53" t="str">
         <f t="shared" si="4"/>
         <v>Brasil</v>
       </c>
-      <c r="I33" s="59">
+      <c r="I33" s="53">
         <f t="shared" si="4"/>
         <v>4</v>
       </c>
       <c r="J33" s="54"/>
-      <c r="K33" s="80" t="s">
+      <c r="K33" s="78" t="s">
         <v>37</v>
       </c>
-      <c r="L33" s="75">
+      <c r="L33" s="77">
         <v>40.0</v>
       </c>
-      <c r="M33" s="78">
+      <c r="M33" s="80">
         <f t="shared" ref="M33:M34" si="5">N33/80%</f>
         <v>0</v>
       </c>
-      <c r="N33" s="78">
+      <c r="N33" s="80">
         <v>0.0</v>
       </c>
       <c r="O33" s="57"/>
@@ -12826,19 +12826,19 @@
         <f t="shared" ref="R33:R34" si="7">P33*Q33</f>
         <v>0</v>
       </c>
-      <c r="S33" s="84">
+      <c r="S33" s="83">
         <v>0.7</v>
       </c>
       <c r="T33" s="57"/>
     </row>
     <row r="34" ht="27.75" customHeight="1">
-      <c r="A34" s="51"/>
+      <c r="A34" s="50"/>
       <c r="B34" s="44"/>
       <c r="C34" s="70" t="s">
         <v>31</v>
       </c>
       <c r="D34" s="44"/>
-      <c r="E34" s="59" t="s">
+      <c r="E34" s="53" t="s">
         <v>53</v>
       </c>
       <c r="F34" s="44"/>
@@ -12847,14 +12847,14 @@
       <c r="I34" s="44"/>
       <c r="J34" s="54"/>
       <c r="K34" s="46"/>
-      <c r="L34" s="75">
+      <c r="L34" s="77">
         <v>24.0</v>
       </c>
-      <c r="M34" s="78">
+      <c r="M34" s="80">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="N34" s="78">
+      <c r="N34" s="80">
         <v>0.0</v>
       </c>
       <c r="O34" s="57"/>
@@ -12862,7 +12862,7 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="Q34" s="84">
+      <c r="Q34" s="83">
         <v>0.4</v>
       </c>
       <c r="R34" s="81">
@@ -12873,9 +12873,9 @@
       <c r="T34" s="57"/>
     </row>
     <row r="35" ht="27.75" customHeight="1">
-      <c r="A35" s="51"/>
+      <c r="A35" s="50"/>
       <c r="B35" s="44"/>
-      <c r="C35" s="56" t="s">
+      <c r="C35" s="52" t="s">
         <v>38</v>
       </c>
       <c r="D35" s="44"/>
@@ -12887,8 +12887,8 @@
       <c r="J35" s="54"/>
       <c r="K35" s="46"/>
       <c r="L35" s="47"/>
-      <c r="M35" s="83"/>
-      <c r="N35" s="83"/>
+      <c r="M35" s="84"/>
+      <c r="N35" s="84"/>
       <c r="P35" s="46"/>
       <c r="Q35" s="48"/>
       <c r="R35" s="46"/>
@@ -12896,9 +12896,9 @@
       <c r="T35" s="57"/>
     </row>
     <row r="36" ht="27.75" customHeight="1">
-      <c r="A36" s="51"/>
+      <c r="A36" s="50"/>
       <c r="B36" s="44"/>
-      <c r="C36" s="56" t="s">
+      <c r="C36" s="52" t="s">
         <v>39</v>
       </c>
       <c r="D36" s="44"/>
@@ -12910,8 +12910,8 @@
       <c r="J36" s="54"/>
       <c r="K36" s="46"/>
       <c r="L36" s="47"/>
-      <c r="M36" s="83"/>
-      <c r="N36" s="83"/>
+      <c r="M36" s="84"/>
+      <c r="N36" s="84"/>
       <c r="P36" s="46"/>
       <c r="Q36" s="48"/>
       <c r="R36" s="46"/>
@@ -12919,9 +12919,9 @@
       <c r="T36" s="57"/>
     </row>
     <row r="37" ht="27.75" customHeight="1">
-      <c r="A37" s="51"/>
+      <c r="A37" s="50"/>
       <c r="B37" s="44"/>
-      <c r="C37" s="56" t="s">
+      <c r="C37" s="52" t="s">
         <v>40</v>
       </c>
       <c r="D37" s="44"/>
@@ -12933,8 +12933,8 @@
       <c r="J37" s="54"/>
       <c r="K37" s="46"/>
       <c r="L37" s="47"/>
-      <c r="M37" s="83"/>
-      <c r="N37" s="83"/>
+      <c r="M37" s="84"/>
+      <c r="N37" s="84"/>
       <c r="P37" s="46"/>
       <c r="Q37" s="48"/>
       <c r="R37" s="46"/>
@@ -12942,9 +12942,9 @@
       <c r="T37" s="57"/>
     </row>
     <row r="38" ht="27.75" customHeight="1">
-      <c r="A38" s="51"/>
+      <c r="A38" s="50"/>
       <c r="B38" s="44"/>
-      <c r="C38" s="56" t="s">
+      <c r="C38" s="52" t="s">
         <v>41</v>
       </c>
       <c r="D38" s="44"/>
@@ -12956,8 +12956,8 @@
       <c r="J38" s="54"/>
       <c r="K38" s="46"/>
       <c r="L38" s="47"/>
-      <c r="M38" s="83"/>
-      <c r="N38" s="83"/>
+      <c r="M38" s="84"/>
+      <c r="N38" s="84"/>
       <c r="P38" s="46"/>
       <c r="Q38" s="48"/>
       <c r="R38" s="46"/>
@@ -12965,22 +12965,22 @@
       <c r="T38" s="57"/>
     </row>
     <row r="39" ht="27.75" customHeight="1">
-      <c r="A39" s="51"/>
-      <c r="B39" s="50"/>
-      <c r="C39" s="56" t="s">
+      <c r="A39" s="50"/>
+      <c r="B39" s="51"/>
+      <c r="C39" s="52" t="s">
         <v>42</v>
       </c>
-      <c r="D39" s="50"/>
-      <c r="E39" s="50"/>
-      <c r="F39" s="50"/>
-      <c r="G39" s="50"/>
-      <c r="H39" s="50"/>
-      <c r="I39" s="50"/>
+      <c r="D39" s="51"/>
+      <c r="E39" s="51"/>
+      <c r="F39" s="51"/>
+      <c r="G39" s="51"/>
+      <c r="H39" s="51"/>
+      <c r="I39" s="51"/>
       <c r="J39" s="54"/>
-      <c r="K39" s="52"/>
-      <c r="L39" s="53"/>
-      <c r="M39" s="83"/>
-      <c r="N39" s="83"/>
+      <c r="K39" s="55"/>
+      <c r="L39" s="56"/>
+      <c r="M39" s="84"/>
+      <c r="N39" s="84"/>
       <c r="P39" s="46"/>
       <c r="Q39" s="85"/>
       <c r="R39" s="46"/>
@@ -12988,8 +12988,8 @@
       <c r="T39" s="57"/>
     </row>
     <row r="40" ht="15.75" customHeight="1">
-      <c r="A40" s="55"/>
-      <c r="B40" s="58"/>
+      <c r="A40" s="58"/>
+      <c r="B40" s="59"/>
       <c r="C40" s="60"/>
       <c r="D40" s="60"/>
       <c r="E40" s="60"/>
@@ -13174,20 +13174,20 @@
       <c r="T45" s="22"/>
     </row>
     <row r="46" ht="25.5" customHeight="1">
-      <c r="A46" s="51"/>
+      <c r="A46" s="50"/>
       <c r="B46" s="71" t="s">
         <v>30</v>
       </c>
       <c r="C46" s="98" t="s">
         <v>55</v>
       </c>
-      <c r="D46" s="59" t="s">
+      <c r="D46" s="53" t="s">
         <v>56</v>
       </c>
-      <c r="E46" s="100" t="s">
+      <c r="E46" s="99" t="s">
         <v>57</v>
       </c>
-      <c r="F46" s="59" t="str">
+      <c r="F46" s="53" t="str">
         <f t="shared" ref="F46:I46" si="9">F19</f>
         <v>Faixa etária: 18 a 39 anos (Millennials e Gen Z adultos)
 Gênero: Maioria masculina (~65%), com presença feminina expressiva e em expansão (~35%)
@@ -13195,7 +13195,7 @@
 Perfil profissional: Executivos, profissionais liberais, gestores e especialistas (TI, finanças, negócios)
 Estilo de vida: Urbano, altamente digitalized, social e consumidor de cultura global.</v>
       </c>
-      <c r="G46" s="59" t="str">
+      <c r="G46" s="53" t="str">
         <f t="shared" si="9"/>
         <v>Esportes americanos (futebol americano / NFL, NBA) e Fantasy Football
 Jogos virtuais e eSports (destaque para o game Madden NFL)
@@ -13203,37 +13203,37 @@
 Consumo via streaming, mídias digitais e redes sociais em tempo real
 Produtos oficiais, colecionáveis esportivos e moda streetwear.</v>
       </c>
-      <c r="H46" s="59" t="str">
+      <c r="H46" s="53" t="str">
         <f t="shared" si="9"/>
         <v>Brasil</v>
       </c>
-      <c r="I46" s="59">
+      <c r="I46" s="53">
         <f t="shared" si="9"/>
         <v>4</v>
       </c>
       <c r="J46" s="54"/>
-      <c r="K46" s="80" t="s">
+      <c r="K46" s="78" t="s">
         <v>37</v>
       </c>
-      <c r="L46" s="101">
+      <c r="L46" s="100">
         <v>203.0</v>
       </c>
-      <c r="M46" s="102">
+      <c r="M46" s="101">
         <f t="shared" ref="M46:M50" si="10">N46/80%</f>
         <v>0</v>
       </c>
-      <c r="N46" s="102">
+      <c r="N46" s="101">
         <v>0.0</v>
       </c>
       <c r="O46" s="57"/>
-      <c r="P46" s="103">
+      <c r="P46" s="102">
         <f t="shared" ref="P46:P50" si="11">N46/L46*1000</f>
         <v>0</v>
       </c>
-      <c r="Q46" s="104">
+      <c r="Q46" s="103">
         <v>0.0</v>
       </c>
-      <c r="R46" s="105">
+      <c r="R46" s="104">
         <f t="shared" ref="R46:R50" si="12">P46*Q46</f>
         <v>0</v>
       </c>
@@ -13243,15 +13243,15 @@
       <c r="T46" s="57"/>
     </row>
     <row r="47" ht="25.5" customHeight="1">
-      <c r="A47" s="51"/>
+      <c r="A47" s="50"/>
       <c r="B47" s="44"/>
       <c r="C47" s="98" t="s">
         <v>58</v>
       </c>
-      <c r="D47" s="59" t="s">
+      <c r="D47" s="53" t="s">
         <v>56</v>
       </c>
-      <c r="E47" s="100" t="s">
+      <c r="E47" s="99" t="s">
         <v>57</v>
       </c>
       <c r="F47" s="44"/>
@@ -13260,25 +13260,25 @@
       <c r="I47" s="44"/>
       <c r="J47" s="54"/>
       <c r="K47" s="46"/>
-      <c r="L47" s="101">
+      <c r="L47" s="100">
         <v>155.0</v>
       </c>
-      <c r="M47" s="102">
+      <c r="M47" s="101">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="N47" s="102">
+      <c r="N47" s="101">
         <v>0.0</v>
       </c>
       <c r="O47" s="57"/>
-      <c r="P47" s="103">
+      <c r="P47" s="102">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="Q47" s="104">
+      <c r="Q47" s="103">
         <v>0.0</v>
       </c>
-      <c r="R47" s="105">
+      <c r="R47" s="104">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
@@ -13288,15 +13288,15 @@
       <c r="T47" s="57"/>
     </row>
     <row r="48" ht="25.5" customHeight="1">
-      <c r="A48" s="51"/>
+      <c r="A48" s="50"/>
       <c r="B48" s="44"/>
       <c r="C48" s="98" t="s">
         <v>59</v>
       </c>
-      <c r="D48" s="59" t="s">
+      <c r="D48" s="53" t="s">
         <v>56</v>
       </c>
-      <c r="E48" s="100" t="s">
+      <c r="E48" s="99" t="s">
         <v>57</v>
       </c>
       <c r="F48" s="44"/>
@@ -13305,25 +13305,25 @@
       <c r="I48" s="44"/>
       <c r="J48" s="54"/>
       <c r="K48" s="46"/>
-      <c r="L48" s="101">
+      <c r="L48" s="100">
         <v>177.0</v>
       </c>
-      <c r="M48" s="102">
+      <c r="M48" s="101">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="N48" s="102">
+      <c r="N48" s="101">
         <v>0.0</v>
       </c>
       <c r="O48" s="57"/>
-      <c r="P48" s="103">
+      <c r="P48" s="102">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="Q48" s="104">
+      <c r="Q48" s="103">
         <v>0.0</v>
       </c>
-      <c r="R48" s="105">
+      <c r="R48" s="104">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
@@ -13333,15 +13333,15 @@
       <c r="T48" s="57"/>
     </row>
     <row r="49" ht="25.5" customHeight="1">
-      <c r="A49" s="51"/>
+      <c r="A49" s="50"/>
       <c r="B49" s="44"/>
       <c r="C49" s="98" t="s">
         <v>60</v>
       </c>
-      <c r="D49" s="59" t="s">
+      <c r="D49" s="53" t="s">
         <v>56</v>
       </c>
-      <c r="E49" s="100" t="s">
+      <c r="E49" s="99" t="s">
         <v>57</v>
       </c>
       <c r="F49" s="44"/>
@@ -13350,25 +13350,25 @@
       <c r="I49" s="44"/>
       <c r="J49" s="54"/>
       <c r="K49" s="46"/>
-      <c r="L49" s="101">
+      <c r="L49" s="100">
         <v>198.0</v>
       </c>
-      <c r="M49" s="102">
+      <c r="M49" s="101">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="N49" s="102">
+      <c r="N49" s="101">
         <v>0.0</v>
       </c>
       <c r="O49" s="57"/>
-      <c r="P49" s="103">
+      <c r="P49" s="102">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="Q49" s="104">
+      <c r="Q49" s="103">
         <v>0.0</v>
       </c>
-      <c r="R49" s="105">
+      <c r="R49" s="104">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
@@ -13378,42 +13378,42 @@
       <c r="T49" s="57"/>
     </row>
     <row r="50" ht="25.5" customHeight="1">
-      <c r="A50" s="51"/>
-      <c r="B50" s="50"/>
+      <c r="A50" s="50"/>
+      <c r="B50" s="51"/>
       <c r="C50" s="98" t="s">
         <v>61</v>
       </c>
       <c r="D50" s="73" t="s">
         <v>32</v>
       </c>
-      <c r="E50" s="100" t="s">
+      <c r="E50" s="99" t="s">
         <v>62</v>
       </c>
-      <c r="F50" s="50"/>
-      <c r="G50" s="50"/>
-      <c r="H50" s="50"/>
-      <c r="I50" s="50"/>
+      <c r="F50" s="51"/>
+      <c r="G50" s="51"/>
+      <c r="H50" s="51"/>
+      <c r="I50" s="51"/>
       <c r="J50" s="54"/>
-      <c r="K50" s="52"/>
-      <c r="L50" s="101">
+      <c r="K50" s="55"/>
+      <c r="L50" s="100">
         <v>25.0</v>
       </c>
-      <c r="M50" s="102">
+      <c r="M50" s="101">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="N50" s="102">
+      <c r="N50" s="101">
         <v>0.0</v>
       </c>
       <c r="O50" s="57"/>
-      <c r="P50" s="103">
+      <c r="P50" s="102">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="Q50" s="108">
+      <c r="Q50" s="105">
         <v>0.01</v>
       </c>
-      <c r="R50" s="105">
+      <c r="R50" s="104">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
@@ -13423,8 +13423,8 @@
       <c r="T50" s="57"/>
     </row>
     <row r="51" ht="15.75" customHeight="1">
-      <c r="A51" s="55"/>
-      <c r="B51" s="58"/>
+      <c r="A51" s="58"/>
+      <c r="B51" s="59"/>
       <c r="C51" s="60"/>
       <c r="D51" s="60"/>
       <c r="E51" s="60"/>
@@ -13451,14 +13451,14 @@
         <f>SUM(P46:P50)</f>
         <v>0</v>
       </c>
-      <c r="Q51" s="106" t="s">
+      <c r="Q51" s="107" t="s">
         <v>63</v>
       </c>
       <c r="R51" s="63">
         <f>SUM(R46:R50)</f>
         <v>0</v>
       </c>
-      <c r="S51" s="107" t="s">
+      <c r="S51" s="108" t="s">
         <v>63</v>
       </c>
       <c r="T51" s="62"/>
@@ -13607,20 +13607,20 @@
       <c r="T56" s="22"/>
     </row>
     <row r="57" ht="55.5" customHeight="1">
-      <c r="A57" s="51"/>
-      <c r="B57" s="116" t="s">
+      <c r="A57" s="50"/>
+      <c r="B57" s="110" t="s">
         <v>30</v>
       </c>
-      <c r="C57" s="56" t="s">
+      <c r="C57" s="52" t="s">
         <v>65</v>
       </c>
-      <c r="D57" s="117" t="s">
+      <c r="D57" s="111" t="s">
         <v>32</v>
       </c>
-      <c r="E57" s="56" t="s">
+      <c r="E57" s="52" t="s">
         <v>66</v>
       </c>
-      <c r="F57" s="118" t="str">
+      <c r="F57" s="112" t="str">
         <f t="shared" ref="F57:I57" si="14">F19</f>
         <v>Faixa etária: 18 a 39 anos (Millennials e Gen Z adultos)
 Gênero: Maioria masculina (~65%), com presença feminina expressiva e em expansão (~35%)
@@ -13628,7 +13628,7 @@
 Perfil profissional: Executivos, profissionais liberais, gestores e especialistas (TI, finanças, negócios)
 Estilo de vida: Urbano, altamente digitalized, social e consumidor de cultura global.</v>
       </c>
-      <c r="G57" s="118" t="str">
+      <c r="G57" s="112" t="str">
         <f t="shared" si="14"/>
         <v>Esportes americanos (futebol americano / NFL, NBA) e Fantasy Football
 Jogos virtuais e eSports (destaque para o game Madden NFL)
@@ -13636,26 +13636,26 @@
 Consumo via streaming, mídias digitais e redes sociais em tempo real
 Produtos oficiais, colecionáveis esportivos e moda streetwear.</v>
       </c>
-      <c r="H57" s="118" t="str">
+      <c r="H57" s="112" t="str">
         <f t="shared" si="14"/>
         <v>Brasil</v>
       </c>
-      <c r="I57" s="118">
+      <c r="I57" s="112">
         <f t="shared" si="14"/>
         <v>4</v>
       </c>
       <c r="J57" s="54"/>
-      <c r="K57" s="119" t="s">
+      <c r="K57" s="113" t="s">
         <v>67</v>
       </c>
-      <c r="L57" s="120">
+      <c r="L57" s="114">
         <v>0.9</v>
       </c>
-      <c r="M57" s="102">
+      <c r="M57" s="101">
         <f>N57/80%</f>
         <v>0</v>
       </c>
-      <c r="N57" s="102">
+      <c r="N57" s="101">
         <v>0.0</v>
       </c>
       <c r="O57" s="57"/>
@@ -13663,10 +13663,10 @@
         <f>R57/Q57</f>
         <v>0</v>
       </c>
-      <c r="Q57" s="104">
+      <c r="Q57" s="103">
         <v>0.01</v>
       </c>
-      <c r="R57" s="105">
+      <c r="R57" s="104">
         <f>N57/L57</f>
         <v>0</v>
       </c>
@@ -13676,8 +13676,8 @@
       <c r="T57" s="57"/>
     </row>
     <row r="58" ht="15.75" customHeight="1">
-      <c r="A58" s="55"/>
-      <c r="B58" s="58"/>
+      <c r="A58" s="58"/>
+      <c r="B58" s="59"/>
       <c r="C58" s="60"/>
       <c r="D58" s="60"/>
       <c r="E58" s="60"/>
@@ -13862,20 +13862,20 @@
       <c r="T63" s="22"/>
     </row>
     <row r="64" ht="36.75" customHeight="1">
-      <c r="A64" s="51"/>
+      <c r="A64" s="50"/>
       <c r="B64" s="71" t="s">
         <v>30</v>
       </c>
-      <c r="C64" s="56" t="s">
+      <c r="C64" s="52" t="s">
         <v>69</v>
       </c>
-      <c r="D64" s="80" t="s">
+      <c r="D64" s="78" t="s">
         <v>70</v>
       </c>
-      <c r="E64" s="56" t="s">
+      <c r="E64" s="52" t="s">
         <v>71</v>
       </c>
-      <c r="F64" s="123" t="str">
+      <c r="F64" s="121" t="str">
         <f t="shared" ref="F64:H64" si="16">F19</f>
         <v>Faixa etária: 18 a 39 anos (Millennials e Gen Z adultos)
 Gênero: Maioria masculina (~65%), com presença feminina expressiva e em expansão (~35%)
@@ -13883,7 +13883,7 @@
 Perfil profissional: Executivos, profissionais liberais, gestores e especialistas (TI, finanças, negócios)
 Estilo de vida: Urbano, altamente digitalized, social e consumidor de cultura global.</v>
       </c>
-      <c r="G64" s="123" t="str">
+      <c r="G64" s="121" t="str">
         <f t="shared" si="16"/>
         <v>Esportes americanos (futebol americano / NFL, NBA) e Fantasy Football
 Jogos virtuais e eSports (destaque para o game Madden NFL)
@@ -13891,25 +13891,25 @@
 Consumo via streaming, mídias digitais e redes sociais em tempo real
 Produtos oficiais, colecionáveis esportivos e moda streetwear.</v>
       </c>
-      <c r="H64" s="123" t="str">
+      <c r="H64" s="121" t="str">
         <f t="shared" si="16"/>
         <v>Brasil</v>
       </c>
-      <c r="I64" s="123">
+      <c r="I64" s="121">
         <v>2.0</v>
       </c>
       <c r="J64" s="54"/>
-      <c r="K64" s="80" t="s">
+      <c r="K64" s="78" t="s">
         <v>72</v>
       </c>
-      <c r="L64" s="120">
+      <c r="L64" s="114">
         <v>0.7</v>
       </c>
-      <c r="M64" s="102">
+      <c r="M64" s="101">
         <f t="shared" ref="M64:M65" si="17">N64/80%</f>
         <v>0</v>
       </c>
-      <c r="N64" s="102">
+      <c r="N64" s="101">
         <v>0.0</v>
       </c>
       <c r="O64" s="57"/>
@@ -13917,46 +13917,46 @@
         <f t="shared" ref="P64:P65" si="18">N64/L64</f>
         <v>0</v>
       </c>
-      <c r="Q64" s="104">
+      <c r="Q64" s="103">
         <v>0.02</v>
       </c>
-      <c r="R64" s="105">
+      <c r="R64" s="104">
         <f t="shared" ref="R64:R65" si="19">P64*Q64</f>
         <v>0</v>
       </c>
-      <c r="S64" s="84">
+      <c r="S64" s="83">
         <v>0.9</v>
       </c>
       <c r="T64" s="57"/>
     </row>
     <row r="65" ht="36.75" customHeight="1">
-      <c r="A65" s="51"/>
-      <c r="B65" s="50"/>
-      <c r="C65" s="56" t="s">
+      <c r="A65" s="50"/>
+      <c r="B65" s="51"/>
+      <c r="C65" s="52" t="s">
         <v>73</v>
       </c>
-      <c r="D65" s="52"/>
-      <c r="E65" s="56" t="s">
+      <c r="D65" s="55"/>
+      <c r="E65" s="52" t="s">
         <v>71</v>
       </c>
       <c r="F65" s="122"/>
       <c r="G65" s="122"/>
       <c r="H65" s="122"/>
-      <c r="I65" s="123">
+      <c r="I65" s="121">
         <v>1.0</v>
       </c>
       <c r="J65" s="54"/>
-      <c r="K65" s="80" t="s">
+      <c r="K65" s="78" t="s">
         <v>72</v>
       </c>
-      <c r="L65" s="120">
+      <c r="L65" s="114">
         <v>0.7</v>
       </c>
-      <c r="M65" s="102">
+      <c r="M65" s="101">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="N65" s="102">
+      <c r="N65" s="101">
         <v>0.0</v>
       </c>
       <c r="O65" s="57"/>
@@ -13964,10 +13964,10 @@
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="Q65" s="104">
+      <c r="Q65" s="103">
         <v>0.02</v>
       </c>
-      <c r="R65" s="105">
+      <c r="R65" s="104">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
@@ -13975,8 +13975,8 @@
       <c r="T65" s="57"/>
     </row>
     <row r="66" ht="15.75" customHeight="1">
-      <c r="A66" s="55"/>
-      <c r="B66" s="58"/>
+      <c r="A66" s="58"/>
+      <c r="B66" s="59"/>
       <c r="C66" s="60"/>
       <c r="D66" s="60"/>
       <c r="E66" s="60"/>
@@ -14426,7 +14426,7 @@
         <v>93</v>
       </c>
       <c r="D80" s="159" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="G80" s="139"/>
       <c r="H80" s="139"/>
@@ -14450,7 +14450,7 @@
       </c>
       <c r="C81" s="161"/>
       <c r="D81" s="162" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="F81" s="163"/>
       <c r="H81" s="139"/>
@@ -14495,11 +14495,11 @@
     <row r="83" ht="15.75" customHeight="1">
       <c r="A83" s="6"/>
       <c r="B83" s="160" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C83" s="161"/>
       <c r="D83" s="162" t="s">
-        <v>111</v>
+        <v>99</v>
       </c>
       <c r="F83" s="163"/>
       <c r="H83" s="139"/>
@@ -14519,11 +14519,11 @@
     <row r="84" ht="15.75" customHeight="1">
       <c r="A84" s="6"/>
       <c r="B84" s="160" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C84" s="161"/>
       <c r="D84" s="162" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="F84" s="163"/>
       <c r="G84" s="139"/>
@@ -14544,11 +14544,11 @@
     <row r="85" ht="15.75" customHeight="1">
       <c r="A85" s="6"/>
       <c r="B85" s="160" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C85" s="161"/>
       <c r="D85" s="162" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F85" s="163"/>
       <c r="H85" s="139"/>
@@ -14568,11 +14568,11 @@
     <row r="86" ht="15.75" customHeight="1">
       <c r="A86" s="6"/>
       <c r="B86" s="160" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C86" s="161"/>
       <c r="D86" s="162" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F86" s="163"/>
       <c r="G86" s="139"/>
@@ -14593,11 +14593,11 @@
     <row r="87" ht="15.75" customHeight="1">
       <c r="A87" s="6"/>
       <c r="B87" s="164" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C87" s="165"/>
       <c r="D87" s="166" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="E87" s="167"/>
       <c r="F87" s="168"/>
@@ -14795,7 +14795,7 @@
       <c r="B2" s="169"/>
       <c r="C2" s="169"/>
       <c r="D2" s="172" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E2" s="170"/>
       <c r="F2" s="169"/>
@@ -14812,18 +14812,18 @@
       <c r="A3" s="169"/>
       <c r="B3" s="169"/>
       <c r="C3" s="169"/>
-      <c r="D3" s="174" t="s">
-        <v>123</v>
+      <c r="D3" s="176" t="s">
+        <v>121</v>
       </c>
       <c r="E3" s="170"/>
       <c r="F3" s="169"/>
       <c r="G3" s="169"/>
       <c r="H3" s="171"/>
       <c r="I3" s="171"/>
-      <c r="J3" s="175"/>
-      <c r="K3" s="177" t="str">
+      <c r="J3" s="179"/>
+      <c r="K3" s="182" t="str">
         <f>RANDBETWEEN(10000,99999)&amp;"-"&amp;TEXT(TODAY(),"mmyy")</f>
-        <v>40136-0826</v>
+        <v>18527-0826</v>
       </c>
       <c r="M3" s="169"/>
     </row>
@@ -14831,34 +14831,34 @@
       <c r="A4" s="169"/>
       <c r="B4" s="169"/>
       <c r="C4" s="169"/>
-      <c r="D4" s="174" t="s">
-        <v>124</v>
+      <c r="D4" s="176" t="s">
+        <v>132</v>
       </c>
       <c r="E4" s="170"/>
       <c r="F4" s="169"/>
       <c r="G4" s="169"/>
       <c r="H4" s="171"/>
       <c r="I4" s="171"/>
-      <c r="J4" s="175"/>
+      <c r="J4" s="179"/>
       <c r="M4" s="169"/>
     </row>
     <row r="5" ht="15.75" customHeight="1">
       <c r="A5" s="169"/>
       <c r="B5" s="169"/>
       <c r="C5" s="169"/>
-      <c r="D5" s="174" t="s">
-        <v>125</v>
+      <c r="D5" s="176" t="s">
+        <v>134</v>
       </c>
       <c r="E5" s="170"/>
       <c r="F5" s="169"/>
       <c r="G5" s="169"/>
       <c r="H5" s="171"/>
       <c r="I5" s="171"/>
-      <c r="J5" s="178"/>
-      <c r="K5" s="178" t="s">
-        <v>126</v>
-      </c>
-      <c r="L5" s="180">
+      <c r="J5" s="185"/>
+      <c r="K5" s="185" t="s">
+        <v>138</v>
+      </c>
+      <c r="L5" s="188">
         <f>TODAY()</f>
         <v>46260</v>
       </c>
@@ -14881,24 +14881,24 @@
     </row>
     <row r="7" ht="15.75" customHeight="1">
       <c r="A7" s="169"/>
-      <c r="B7" s="181" t="s">
-        <v>127</v>
-      </c>
-      <c r="C7" s="185"/>
-      <c r="D7" s="185"/>
-      <c r="E7" s="185"/>
-      <c r="F7" s="185"/>
-      <c r="G7" s="185"/>
-      <c r="H7" s="185"/>
-      <c r="I7" s="185"/>
-      <c r="J7" s="185"/>
-      <c r="K7" s="185"/>
-      <c r="L7" s="190"/>
+      <c r="B7" s="192" t="s">
+        <v>147</v>
+      </c>
+      <c r="C7" s="193"/>
+      <c r="D7" s="193"/>
+      <c r="E7" s="193"/>
+      <c r="F7" s="193"/>
+      <c r="G7" s="193"/>
+      <c r="H7" s="193"/>
+      <c r="I7" s="193"/>
+      <c r="J7" s="193"/>
+      <c r="K7" s="193"/>
+      <c r="L7" s="195"/>
       <c r="M7" s="169"/>
     </row>
     <row r="8" ht="15.75" customHeight="1">
       <c r="A8" s="169"/>
-      <c r="B8" s="193"/>
+      <c r="B8" s="196"/>
       <c r="C8" s="167"/>
       <c r="D8" s="167"/>
       <c r="E8" s="167"/>
@@ -14920,7 +14920,7 @@
       <c r="F9" s="197"/>
       <c r="G9" s="197"/>
       <c r="H9" s="197"/>
-      <c r="I9" s="199"/>
+      <c r="I9" s="198"/>
       <c r="J9" s="197"/>
       <c r="K9" s="197"/>
       <c r="L9" s="197"/>
@@ -14929,19 +14929,19 @@
     <row r="10" ht="15.75" customHeight="1">
       <c r="A10" s="169"/>
       <c r="B10" s="200" t="s">
-        <v>230</v>
+        <v>200</v>
       </c>
       <c r="C10" s="141"/>
       <c r="D10" s="142"/>
       <c r="E10" s="201"/>
       <c r="F10" s="200" t="s">
-        <v>263</v>
+        <v>210</v>
       </c>
       <c r="G10" s="141"/>
       <c r="H10" s="142"/>
-      <c r="I10" s="199"/>
+      <c r="I10" s="198"/>
       <c r="J10" s="200" t="s">
-        <v>270</v>
+        <v>216</v>
       </c>
       <c r="K10" s="141"/>
       <c r="L10" s="142"/>
@@ -14950,19 +14950,19 @@
     <row r="11" ht="15.75" customHeight="1">
       <c r="A11" s="169"/>
       <c r="B11" s="203" t="s">
-        <v>284</v>
+        <v>221</v>
       </c>
       <c r="C11" s="204"/>
       <c r="D11" s="142"/>
       <c r="E11" s="201"/>
       <c r="F11" s="203" t="s">
-        <v>284</v>
+        <v>221</v>
       </c>
       <c r="G11" s="204"/>
       <c r="H11" s="142"/>
-      <c r="I11" s="199"/>
+      <c r="I11" s="198"/>
       <c r="J11" s="205" t="s">
-        <v>309</v>
+        <v>247</v>
       </c>
       <c r="K11" s="141"/>
       <c r="L11" s="142"/>
@@ -14971,64 +14971,64 @@
     <row r="12" ht="15.75" customHeight="1">
       <c r="A12" s="169"/>
       <c r="B12" s="203" t="s">
-        <v>318</v>
+        <v>255</v>
       </c>
       <c r="C12" s="204"/>
       <c r="D12" s="142"/>
       <c r="E12" s="201"/>
       <c r="F12" s="203" t="s">
-        <v>318</v>
+        <v>255</v>
       </c>
       <c r="G12" s="204"/>
       <c r="H12" s="142"/>
-      <c r="I12" s="199"/>
-      <c r="J12" s="209" t="s">
-        <v>329</v>
-      </c>
-      <c r="K12" s="211" t="s">
-        <v>334</v>
+      <c r="I12" s="198"/>
+      <c r="J12" s="206" t="s">
+        <v>263</v>
+      </c>
+      <c r="K12" s="207" t="s">
+        <v>272</v>
       </c>
       <c r="L12" s="142"/>
       <c r="M12" s="202"/>
     </row>
     <row r="13" ht="15.75" customHeight="1">
       <c r="A13" s="169"/>
-      <c r="B13" s="212" t="s">
-        <v>345</v>
+      <c r="B13" s="208" t="s">
+        <v>284</v>
       </c>
       <c r="C13" s="204"/>
       <c r="D13" s="142"/>
       <c r="E13" s="201"/>
-      <c r="F13" s="212" t="s">
-        <v>350</v>
+      <c r="F13" s="208" t="s">
+        <v>293</v>
       </c>
       <c r="G13" s="204"/>
       <c r="H13" s="142"/>
-      <c r="I13" s="199"/>
-      <c r="J13" s="209" t="s">
-        <v>354</v>
-      </c>
-      <c r="K13" s="211" t="s">
-        <v>355</v>
+      <c r="I13" s="198"/>
+      <c r="J13" s="206" t="s">
+        <v>294</v>
+      </c>
+      <c r="K13" s="207" t="s">
+        <v>296</v>
       </c>
       <c r="L13" s="142"/>
       <c r="M13" s="202"/>
     </row>
     <row r="14" ht="15.75" customHeight="1">
       <c r="A14" s="169"/>
-      <c r="B14" s="212" t="s">
-        <v>361</v>
+      <c r="B14" s="208" t="s">
+        <v>307</v>
       </c>
       <c r="C14" s="204"/>
       <c r="D14" s="142"/>
       <c r="E14" s="201"/>
-      <c r="F14" s="212" t="s">
-        <v>364</v>
+      <c r="F14" s="208" t="s">
+        <v>314</v>
       </c>
       <c r="G14" s="204"/>
       <c r="H14" s="142"/>
-      <c r="I14" s="199"/>
-      <c r="J14" s="215"/>
+      <c r="I14" s="198"/>
+      <c r="J14" s="209"/>
       <c r="K14" s="169"/>
       <c r="M14" s="202"/>
     </row>
@@ -15050,52 +15050,52 @@
     <row r="16" ht="15.75" customHeight="1">
       <c r="A16" s="170"/>
       <c r="B16" s="158" t="s">
-        <v>366</v>
+        <v>342</v>
       </c>
       <c r="C16" s="158" t="s">
         <v>22</v>
       </c>
       <c r="E16" s="158" t="s">
-        <v>367</v>
+        <v>350</v>
       </c>
       <c r="H16" s="158" t="s">
         <v>23</v>
       </c>
       <c r="I16" s="158"/>
       <c r="J16" s="158" t="s">
-        <v>368</v>
+        <v>357</v>
       </c>
       <c r="K16" s="158" t="s">
-        <v>369</v>
+        <v>359</v>
       </c>
       <c r="M16" s="170"/>
     </row>
     <row r="17" ht="15.75" customHeight="1">
       <c r="A17" s="170"/>
-      <c r="B17" s="216" t="s">
-        <v>370</v>
-      </c>
-      <c r="C17" s="217"/>
-      <c r="D17" s="218"/>
-      <c r="E17" s="217"/>
-      <c r="F17" s="219"/>
-      <c r="G17" s="218"/>
-      <c r="H17" s="220"/>
-      <c r="I17" s="221"/>
-      <c r="J17" s="83"/>
-      <c r="K17" s="222"/>
-      <c r="L17" s="83"/>
+      <c r="B17" s="210" t="s">
+        <v>363</v>
+      </c>
+      <c r="C17" s="212"/>
+      <c r="D17" s="214"/>
+      <c r="E17" s="212"/>
+      <c r="F17" s="215"/>
+      <c r="G17" s="214"/>
+      <c r="H17" s="217"/>
+      <c r="I17" s="218"/>
+      <c r="J17" s="84"/>
+      <c r="K17" s="220"/>
+      <c r="L17" s="84"/>
       <c r="M17" s="170"/>
     </row>
     <row r="18" ht="15.75" customHeight="1">
       <c r="A18" s="170"/>
-      <c r="B18" s="223"/>
-      <c r="C18" s="223"/>
-      <c r="D18" s="223"/>
-      <c r="E18" s="223"/>
-      <c r="F18" s="223"/>
-      <c r="G18" s="223"/>
-      <c r="H18" s="224"/>
+      <c r="B18" s="222"/>
+      <c r="C18" s="222"/>
+      <c r="D18" s="222"/>
+      <c r="E18" s="222"/>
+      <c r="F18" s="222"/>
+      <c r="G18" s="222"/>
+      <c r="H18" s="223"/>
       <c r="I18" s="225" t="s">
         <v>77</v>
       </c>
@@ -15130,7 +15130,7 @@
       <c r="G20" s="227"/>
       <c r="H20" s="227"/>
       <c r="I20" s="225" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="K20" s="226">
         <f>K18</f>
@@ -15281,16 +15281,16 @@
     <row r="30" ht="15.75" customHeight="1">
       <c r="A30" s="171"/>
       <c r="B30" s="239"/>
-      <c r="C30" s="185"/>
-      <c r="D30" s="185"/>
-      <c r="E30" s="185"/>
-      <c r="F30" s="185"/>
-      <c r="G30" s="185"/>
-      <c r="H30" s="185"/>
-      <c r="I30" s="185"/>
-      <c r="J30" s="185"/>
-      <c r="K30" s="185"/>
-      <c r="L30" s="190"/>
+      <c r="C30" s="193"/>
+      <c r="D30" s="193"/>
+      <c r="E30" s="193"/>
+      <c r="F30" s="193"/>
+      <c r="G30" s="193"/>
+      <c r="H30" s="193"/>
+      <c r="I30" s="193"/>
+      <c r="J30" s="193"/>
+      <c r="K30" s="193"/>
+      <c r="L30" s="195"/>
       <c r="M30" s="171"/>
     </row>
     <row r="31" ht="15.75" customHeight="1">
@@ -15307,7 +15307,7 @@
     </row>
     <row r="33" ht="15.75" customHeight="1">
       <c r="A33" s="171"/>
-      <c r="B33" s="193"/>
+      <c r="B33" s="196"/>
       <c r="C33" s="167"/>
       <c r="D33" s="167"/>
       <c r="E33" s="167"/>
@@ -15356,7 +15356,7 @@
         <v>93</v>
       </c>
       <c r="D36" s="159" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="I36" s="156"/>
       <c r="J36" s="241" t="str">
@@ -15377,12 +15377,12 @@
       </c>
       <c r="C37" s="161"/>
       <c r="D37" s="244" t="s">
-        <v>96</v>
+        <v>109</v>
       </c>
       <c r="H37" s="163"/>
       <c r="I37" s="156"/>
       <c r="J37" s="240"/>
-      <c r="K37" s="83"/>
+      <c r="K37" s="84"/>
       <c r="L37" s="245"/>
       <c r="M37" s="171"/>
     </row>
@@ -15393,7 +15393,7 @@
       </c>
       <c r="C38" s="161"/>
       <c r="D38" s="244" t="s">
-        <v>98</v>
+        <v>110</v>
       </c>
       <c r="H38" s="163"/>
       <c r="I38" s="156"/>
@@ -15409,11 +15409,11 @@
     <row r="39" ht="15.75" customHeight="1">
       <c r="A39" s="171"/>
       <c r="B39" s="160" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C39" s="161"/>
       <c r="D39" s="244" t="s">
-        <v>100</v>
+        <v>112</v>
       </c>
       <c r="H39" s="163"/>
       <c r="I39" s="156"/>
@@ -15425,11 +15425,11 @@
     <row r="40" ht="15.75" customHeight="1">
       <c r="A40" s="171"/>
       <c r="B40" s="160" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C40" s="161"/>
       <c r="D40" s="244" t="s">
-        <v>102</v>
+        <v>113</v>
       </c>
       <c r="H40" s="163"/>
       <c r="I40" s="156"/>
@@ -15441,11 +15441,11 @@
     <row r="41" ht="15.75" customHeight="1">
       <c r="A41" s="171"/>
       <c r="B41" s="160" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C41" s="161"/>
       <c r="D41" s="244" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="H41" s="163"/>
       <c r="I41" s="156"/>
@@ -15457,11 +15457,11 @@
     <row r="42" ht="15.75" customHeight="1">
       <c r="A42" s="171"/>
       <c r="B42" s="160" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C42" s="161"/>
       <c r="D42" s="244" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="H42" s="163"/>
       <c r="I42" s="156"/>
@@ -15473,11 +15473,11 @@
     <row r="43" ht="15.75" customHeight="1">
       <c r="A43" s="171"/>
       <c r="B43" s="164" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C43" s="165"/>
       <c r="D43" s="253" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E43" s="167"/>
       <c r="F43" s="167"/>
@@ -15591,1092 +15591,1092 @@
   </cols>
   <sheetData>
     <row r="1" ht="37.5" customHeight="1">
-      <c r="A1" s="176" t="s">
-        <v>121</v>
-      </c>
-      <c r="B1" s="179"/>
-      <c r="C1" s="179"/>
-      <c r="D1" s="179"/>
-      <c r="E1" s="179"/>
-      <c r="F1" s="182"/>
+      <c r="A1" s="174" t="s">
+        <v>119</v>
+      </c>
+      <c r="B1" s="175"/>
+      <c r="C1" s="175"/>
+      <c r="D1" s="175"/>
+      <c r="E1" s="175"/>
+      <c r="F1" s="177"/>
     </row>
     <row r="2" ht="15.75" customHeight="1">
-      <c r="A2" s="183" t="s">
+      <c r="A2" s="178" t="s">
+        <v>123</v>
+      </c>
+      <c r="B2" s="175"/>
+      <c r="C2" s="175"/>
+      <c r="D2" s="175"/>
+      <c r="E2" s="175"/>
+      <c r="F2" s="177"/>
+    </row>
+    <row r="3" ht="24.0" customHeight="1">
+      <c r="A3" s="180" t="s">
+        <v>124</v>
+      </c>
+      <c r="B3" s="180" t="s">
+        <v>125</v>
+      </c>
+      <c r="C3" s="180" t="s">
+        <v>126</v>
+      </c>
+      <c r="D3" s="180" t="s">
+        <v>127</v>
+      </c>
+      <c r="E3" s="180" t="s">
         <v>128</v>
       </c>
-      <c r="B2" s="179"/>
-      <c r="C2" s="179"/>
-      <c r="D2" s="179"/>
-      <c r="E2" s="179"/>
-      <c r="F2" s="182"/>
-    </row>
-    <row r="3" ht="24.0" customHeight="1">
-      <c r="A3" s="184" t="s">
+      <c r="F3" s="180" t="s">
         <v>129</v>
       </c>
-      <c r="B3" s="184" t="s">
-        <v>131</v>
-      </c>
-      <c r="C3" s="184" t="s">
-        <v>132</v>
-      </c>
-      <c r="D3" s="184" t="s">
+    </row>
+    <row r="4" ht="19.5" customHeight="1">
+      <c r="A4" s="181" t="s">
+        <v>130</v>
+      </c>
+      <c r="B4" s="175"/>
+      <c r="C4" s="175"/>
+      <c r="D4" s="175"/>
+      <c r="E4" s="175"/>
+      <c r="F4" s="177"/>
+    </row>
+    <row r="5" ht="42.0" customHeight="1">
+      <c r="A5" s="183">
+        <v>1.0</v>
+      </c>
+      <c r="B5" s="184" t="s">
         <v>133</v>
       </c>
-      <c r="E3" s="184" t="s">
-        <v>134</v>
-      </c>
-      <c r="F3" s="184" t="s">
+      <c r="C5" s="183" t="s">
         <v>135</v>
       </c>
-    </row>
-    <row r="4" ht="19.5" customHeight="1">
-      <c r="A4" s="186" t="s">
+      <c r="D5" s="183" t="s">
         <v>136</v>
       </c>
-      <c r="B4" s="179"/>
-      <c r="C4" s="179"/>
-      <c r="D4" s="179"/>
-      <c r="E4" s="179"/>
-      <c r="F4" s="182"/>
-    </row>
-    <row r="5" ht="42.0" customHeight="1">
-      <c r="A5" s="187">
-        <v>1.0</v>
-      </c>
-      <c r="B5" s="188" t="s">
-        <v>146</v>
-      </c>
-      <c r="C5" s="187" t="s">
-        <v>147</v>
-      </c>
-      <c r="D5" s="187" t="s">
+      <c r="E5" s="186" t="s">
+        <v>137</v>
+      </c>
+      <c r="F5" s="187" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="6" ht="42.0" customHeight="1">
+      <c r="A6" s="189">
+        <v>2.0</v>
+      </c>
+      <c r="B6" s="190" t="s">
+        <v>145</v>
+      </c>
+      <c r="C6" s="189" t="s">
+        <v>135</v>
+      </c>
+      <c r="D6" s="189" t="s">
         <v>148</v>
       </c>
-      <c r="E5" s="189" t="s">
+      <c r="E6" s="191" t="s">
         <v>149</v>
       </c>
-      <c r="F5" s="191" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="6" ht="42.0" customHeight="1">
-      <c r="A6" s="192">
-        <v>2.0</v>
-      </c>
-      <c r="B6" s="194" t="s">
-        <v>151</v>
-      </c>
-      <c r="C6" s="192" t="s">
-        <v>147</v>
-      </c>
-      <c r="D6" s="192" t="s">
-        <v>155</v>
-      </c>
-      <c r="E6" s="195" t="s">
-        <v>157</v>
-      </c>
-      <c r="F6" s="191" t="s">
-        <v>150</v>
+      <c r="F6" s="187" t="s">
+        <v>139</v>
       </c>
     </row>
     <row r="7" ht="42.0" customHeight="1">
-      <c r="A7" s="187">
+      <c r="A7" s="183">
         <v>3.0</v>
       </c>
-      <c r="B7" s="188" t="s">
-        <v>159</v>
-      </c>
-      <c r="C7" s="187" t="s">
-        <v>147</v>
-      </c>
-      <c r="D7" s="187" t="s">
-        <v>161</v>
-      </c>
-      <c r="E7" s="189" t="s">
-        <v>163</v>
-      </c>
-      <c r="F7" s="196" t="s">
-        <v>165</v>
+      <c r="B7" s="184" t="s">
+        <v>162</v>
+      </c>
+      <c r="C7" s="183" t="s">
+        <v>135</v>
+      </c>
+      <c r="D7" s="183" t="s">
+        <v>166</v>
+      </c>
+      <c r="E7" s="186" t="s">
+        <v>167</v>
+      </c>
+      <c r="F7" s="194" t="s">
+        <v>169</v>
       </c>
     </row>
     <row r="8" ht="42.0" customHeight="1">
-      <c r="A8" s="192">
+      <c r="A8" s="189">
         <v>4.0</v>
       </c>
-      <c r="B8" s="194" t="s">
+      <c r="B8" s="190" t="s">
         <v>173</v>
       </c>
-      <c r="C8" s="192" t="s">
-        <v>147</v>
-      </c>
-      <c r="D8" s="192" t="s">
+      <c r="C8" s="189" t="s">
+        <v>135</v>
+      </c>
+      <c r="D8" s="189" t="s">
         <v>174</v>
       </c>
-      <c r="E8" s="195" t="s">
-        <v>176</v>
-      </c>
-      <c r="F8" s="196" t="s">
-        <v>165</v>
+      <c r="E8" s="191" t="s">
+        <v>175</v>
+      </c>
+      <c r="F8" s="194" t="s">
+        <v>169</v>
       </c>
     </row>
     <row r="9" ht="19.5" customHeight="1">
-      <c r="A9" s="186" t="s">
-        <v>180</v>
-      </c>
-      <c r="B9" s="179"/>
-      <c r="C9" s="179"/>
-      <c r="D9" s="179"/>
-      <c r="E9" s="179"/>
-      <c r="F9" s="182"/>
+      <c r="A9" s="181" t="s">
+        <v>177</v>
+      </c>
+      <c r="B9" s="175"/>
+      <c r="C9" s="175"/>
+      <c r="D9" s="175"/>
+      <c r="E9" s="175"/>
+      <c r="F9" s="177"/>
     </row>
     <row r="10" ht="42.0" customHeight="1">
-      <c r="A10" s="187">
+      <c r="A10" s="183">
         <v>5.0</v>
       </c>
-      <c r="B10" s="188" t="s">
+      <c r="B10" s="184" t="s">
+        <v>181</v>
+      </c>
+      <c r="C10" s="183" t="s">
+        <v>183</v>
+      </c>
+      <c r="D10" s="183" t="s">
+        <v>184</v>
+      </c>
+      <c r="E10" s="186" t="s">
         <v>185</v>
       </c>
-      <c r="C10" s="187" t="s">
-        <v>186</v>
-      </c>
-      <c r="D10" s="187" t="s">
-        <v>188</v>
-      </c>
-      <c r="E10" s="189" t="s">
+      <c r="F10" s="187" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="11" ht="42.0" customHeight="1">
+      <c r="A11" s="189">
+        <v>6.0</v>
+      </c>
+      <c r="B11" s="190" t="s">
+        <v>187</v>
+      </c>
+      <c r="C11" s="189" t="s">
+        <v>183</v>
+      </c>
+      <c r="D11" s="189" t="s">
+        <v>184</v>
+      </c>
+      <c r="E11" s="191" t="s">
         <v>189</v>
       </c>
-      <c r="F10" s="191" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="11" ht="42.0" customHeight="1">
-      <c r="A11" s="192">
-        <v>6.0</v>
-      </c>
-      <c r="B11" s="194" t="s">
-        <v>191</v>
-      </c>
-      <c r="C11" s="192" t="s">
-        <v>186</v>
-      </c>
-      <c r="D11" s="192" t="s">
-        <v>188</v>
-      </c>
-      <c r="E11" s="195" t="s">
-        <v>193</v>
-      </c>
-      <c r="F11" s="191" t="s">
-        <v>150</v>
+      <c r="F11" s="187" t="s">
+        <v>139</v>
       </c>
     </row>
     <row r="12" ht="42.0" customHeight="1">
-      <c r="A12" s="187">
+      <c r="A12" s="183">
         <v>7.0</v>
       </c>
-      <c r="B12" s="188" t="s">
-        <v>195</v>
-      </c>
-      <c r="C12" s="187" t="s">
-        <v>186</v>
-      </c>
-      <c r="D12" s="187" t="s">
-        <v>188</v>
-      </c>
-      <c r="E12" s="189" t="s">
+      <c r="B12" s="184" t="s">
+        <v>192</v>
+      </c>
+      <c r="C12" s="183" t="s">
+        <v>183</v>
+      </c>
+      <c r="D12" s="183" t="s">
+        <v>184</v>
+      </c>
+      <c r="E12" s="186" t="s">
+        <v>196</v>
+      </c>
+      <c r="F12" s="194" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="13" ht="42.0" customHeight="1">
+      <c r="A13" s="189">
+        <v>8.0</v>
+      </c>
+      <c r="B13" s="190" t="s">
         <v>197</v>
       </c>
-      <c r="F12" s="196" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="13" ht="42.0" customHeight="1">
-      <c r="A13" s="192">
-        <v>8.0</v>
-      </c>
-      <c r="B13" s="194" t="s">
+      <c r="C13" s="189" t="s">
+        <v>183</v>
+      </c>
+      <c r="D13" s="189" t="s">
+        <v>184</v>
+      </c>
+      <c r="E13" s="191" t="s">
+        <v>199</v>
+      </c>
+      <c r="F13" s="199" t="s">
         <v>198</v>
       </c>
-      <c r="C13" s="192" t="s">
-        <v>186</v>
-      </c>
-      <c r="D13" s="192" t="s">
-        <v>188</v>
-      </c>
-      <c r="E13" s="195" t="s">
-        <v>199</v>
-      </c>
-      <c r="F13" s="198" t="s">
-        <v>196</v>
-      </c>
     </row>
     <row r="14" ht="19.5" customHeight="1">
-      <c r="A14" s="186" t="s">
+      <c r="A14" s="181" t="s">
+        <v>201</v>
+      </c>
+      <c r="B14" s="175"/>
+      <c r="C14" s="175"/>
+      <c r="D14" s="175"/>
+      <c r="E14" s="175"/>
+      <c r="F14" s="177"/>
+    </row>
+    <row r="15" ht="42.0" customHeight="1">
+      <c r="A15" s="183">
+        <v>9.0</v>
+      </c>
+      <c r="B15" s="184" t="s">
         <v>202</v>
       </c>
-      <c r="B14" s="179"/>
-      <c r="C14" s="179"/>
-      <c r="D14" s="179"/>
-      <c r="E14" s="179"/>
-      <c r="F14" s="182"/>
-    </row>
-    <row r="15" ht="42.0" customHeight="1">
-      <c r="A15" s="187">
-        <v>9.0</v>
-      </c>
-      <c r="B15" s="188" t="s">
+      <c r="C15" s="183" t="s">
+        <v>203</v>
+      </c>
+      <c r="D15" s="183" t="s">
         <v>204</v>
       </c>
-      <c r="C15" s="187" t="s">
+      <c r="E15" s="186" t="s">
         <v>205</v>
       </c>
-      <c r="D15" s="187" t="s">
+      <c r="F15" s="187" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="16" ht="42.0" customHeight="1">
+      <c r="A16" s="189">
+        <v>10.0</v>
+      </c>
+      <c r="B16" s="190" t="s">
         <v>206</v>
       </c>
-      <c r="E15" s="189" t="s">
+      <c r="C16" s="189" t="s">
+        <v>203</v>
+      </c>
+      <c r="D16" s="189" t="s">
+        <v>204</v>
+      </c>
+      <c r="E16" s="191" t="s">
         <v>207</v>
       </c>
-      <c r="F15" s="191" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="16" ht="42.0" customHeight="1">
-      <c r="A16" s="192">
-        <v>10.0</v>
-      </c>
-      <c r="B16" s="194" t="s">
+      <c r="F16" s="194" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="17" ht="42.0" customHeight="1">
+      <c r="A17" s="183">
+        <v>11.0</v>
+      </c>
+      <c r="B17" s="184" t="s">
         <v>209</v>
       </c>
-      <c r="C16" s="192" t="s">
-        <v>205</v>
-      </c>
-      <c r="D16" s="192" t="s">
-        <v>206</v>
-      </c>
-      <c r="E16" s="195" t="s">
+      <c r="C17" s="183" t="s">
+        <v>203</v>
+      </c>
+      <c r="D17" s="183" t="s">
+        <v>204</v>
+      </c>
+      <c r="E17" s="186" t="s">
+        <v>211</v>
+      </c>
+      <c r="F17" s="194" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="18" ht="42.0" customHeight="1">
+      <c r="A18" s="189">
+        <v>12.0</v>
+      </c>
+      <c r="B18" s="190" t="s">
         <v>213</v>
       </c>
-      <c r="F16" s="196" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="17" ht="42.0" customHeight="1">
-      <c r="A17" s="187">
-        <v>11.0</v>
-      </c>
-      <c r="B17" s="188" t="s">
+      <c r="C18" s="189" t="s">
+        <v>203</v>
+      </c>
+      <c r="D18" s="189" t="s">
+        <v>204</v>
+      </c>
+      <c r="E18" s="191" t="s">
         <v>215</v>
       </c>
-      <c r="C17" s="187" t="s">
-        <v>205</v>
-      </c>
-      <c r="D17" s="187" t="s">
-        <v>206</v>
-      </c>
-      <c r="E17" s="189" t="s">
+      <c r="F18" s="199" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="19" ht="19.5" customHeight="1">
+      <c r="A19" s="181" t="s">
         <v>217</v>
       </c>
-      <c r="F17" s="196" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="18" ht="42.0" customHeight="1">
-      <c r="A18" s="192">
-        <v>12.0</v>
-      </c>
-      <c r="B18" s="194" t="s">
+      <c r="B19" s="175"/>
+      <c r="C19" s="175"/>
+      <c r="D19" s="175"/>
+      <c r="E19" s="175"/>
+      <c r="F19" s="177"/>
+    </row>
+    <row r="20" ht="42.0" customHeight="1">
+      <c r="A20" s="183">
+        <v>13.0</v>
+      </c>
+      <c r="B20" s="184" t="s">
+        <v>218</v>
+      </c>
+      <c r="C20" s="183" t="s">
         <v>219</v>
       </c>
-      <c r="C18" s="192" t="s">
-        <v>205</v>
-      </c>
-      <c r="D18" s="192" t="s">
-        <v>206</v>
-      </c>
-      <c r="E18" s="195" t="s">
+      <c r="D20" s="183" t="s">
+        <v>204</v>
+      </c>
+      <c r="E20" s="186" t="s">
         <v>220</v>
       </c>
-      <c r="F18" s="198" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="19" ht="19.5" customHeight="1">
-      <c r="A19" s="186" t="s">
-        <v>222</v>
-      </c>
-      <c r="B19" s="179"/>
-      <c r="C19" s="179"/>
-      <c r="D19" s="179"/>
-      <c r="E19" s="179"/>
-      <c r="F19" s="182"/>
-    </row>
-    <row r="20" ht="42.0" customHeight="1">
-      <c r="A20" s="187">
-        <v>13.0</v>
-      </c>
-      <c r="B20" s="188" t="s">
+      <c r="F20" s="187" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="21" ht="42.0" customHeight="1">
+      <c r="A21" s="189">
+        <v>14.0</v>
+      </c>
+      <c r="B21" s="190" t="s">
+        <v>223</v>
+      </c>
+      <c r="C21" s="189" t="s">
+        <v>219</v>
+      </c>
+      <c r="D21" s="189" t="s">
+        <v>204</v>
+      </c>
+      <c r="E21" s="191" t="s">
+        <v>226</v>
+      </c>
+      <c r="F21" s="187" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="22" ht="42.0" customHeight="1">
+      <c r="A22" s="183">
+        <v>15.0</v>
+      </c>
+      <c r="B22" s="184" t="s">
         <v>228</v>
       </c>
-      <c r="C20" s="187" t="s">
+      <c r="C22" s="183" t="s">
+        <v>219</v>
+      </c>
+      <c r="D22" s="183" t="s">
+        <v>204</v>
+      </c>
+      <c r="E22" s="186" t="s">
         <v>229</v>
       </c>
-      <c r="D20" s="187" t="s">
-        <v>206</v>
-      </c>
-      <c r="E20" s="189" t="s">
-        <v>232</v>
-      </c>
-      <c r="F20" s="191" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="21" ht="42.0" customHeight="1">
-      <c r="A21" s="192">
-        <v>14.0</v>
-      </c>
-      <c r="B21" s="194" t="s">
+      <c r="F22" s="194" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="23" ht="42.0" customHeight="1">
+      <c r="A23" s="189">
+        <v>16.0</v>
+      </c>
+      <c r="B23" s="190" t="s">
+        <v>231</v>
+      </c>
+      <c r="C23" s="189" t="s">
+        <v>219</v>
+      </c>
+      <c r="D23" s="189" t="s">
+        <v>204</v>
+      </c>
+      <c r="E23" s="191" t="s">
         <v>233</v>
       </c>
-      <c r="C21" s="192" t="s">
-        <v>229</v>
-      </c>
-      <c r="D21" s="192" t="s">
-        <v>206</v>
-      </c>
-      <c r="E21" s="195" t="s">
-        <v>234</v>
-      </c>
-      <c r="F21" s="191" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="22" ht="42.0" customHeight="1">
-      <c r="A22" s="187">
-        <v>15.0</v>
-      </c>
-      <c r="B22" s="188" t="s">
+      <c r="F23" s="199" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="24" ht="19.5" customHeight="1">
+      <c r="A24" s="181" t="s">
         <v>235</v>
       </c>
-      <c r="C22" s="187" t="s">
-        <v>229</v>
-      </c>
-      <c r="D22" s="187" t="s">
-        <v>206</v>
-      </c>
-      <c r="E22" s="189" t="s">
-        <v>236</v>
-      </c>
-      <c r="F22" s="196" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="23" ht="42.0" customHeight="1">
-      <c r="A23" s="192">
-        <v>16.0</v>
-      </c>
-      <c r="B23" s="194" t="s">
+      <c r="B24" s="175"/>
+      <c r="C24" s="175"/>
+      <c r="D24" s="175"/>
+      <c r="E24" s="175"/>
+      <c r="F24" s="177"/>
+    </row>
+    <row r="25" ht="42.0" customHeight="1">
+      <c r="A25" s="183">
+        <v>17.0</v>
+      </c>
+      <c r="B25" s="184" t="s">
         <v>240</v>
       </c>
-      <c r="C23" s="192" t="s">
-        <v>229</v>
-      </c>
-      <c r="D23" s="192" t="s">
-        <v>206</v>
-      </c>
-      <c r="E23" s="195" t="s">
+      <c r="C25" s="183" t="s">
+        <v>241</v>
+      </c>
+      <c r="D25" s="183" t="s">
         <v>242</v>
       </c>
-      <c r="F23" s="198" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="24" ht="19.5" customHeight="1">
-      <c r="A24" s="186" t="s">
-        <v>243</v>
-      </c>
-      <c r="B24" s="179"/>
-      <c r="C24" s="179"/>
-      <c r="D24" s="179"/>
-      <c r="E24" s="179"/>
-      <c r="F24" s="182"/>
-    </row>
-    <row r="25" ht="42.0" customHeight="1">
-      <c r="A25" s="187">
-        <v>17.0</v>
-      </c>
-      <c r="B25" s="188" t="s">
+      <c r="E25" s="186" t="s">
+        <v>244</v>
+      </c>
+      <c r="F25" s="187" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="26" ht="42.0" customHeight="1">
+      <c r="A26" s="189">
+        <v>18.0</v>
+      </c>
+      <c r="B26" s="190" t="s">
+        <v>246</v>
+      </c>
+      <c r="C26" s="189" t="s">
+        <v>241</v>
+      </c>
+      <c r="D26" s="189" t="s">
+        <v>248</v>
+      </c>
+      <c r="E26" s="191" t="s">
+        <v>250</v>
+      </c>
+      <c r="F26" s="187" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="27" ht="42.0" customHeight="1">
+      <c r="A27" s="183">
+        <v>19.0</v>
+      </c>
+      <c r="B27" s="184" t="s">
+        <v>251</v>
+      </c>
+      <c r="C27" s="183" t="s">
+        <v>241</v>
+      </c>
+      <c r="D27" s="183" t="s">
+        <v>248</v>
+      </c>
+      <c r="E27" s="186" t="s">
         <v>252</v>
       </c>
-      <c r="C25" s="187" t="s">
+      <c r="F27" s="187" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="28" ht="42.0" customHeight="1">
+      <c r="A28" s="189">
+        <v>20.0</v>
+      </c>
+      <c r="B28" s="190" t="s">
         <v>253</v>
       </c>
-      <c r="D25" s="187" t="s">
+      <c r="C28" s="189" t="s">
+        <v>241</v>
+      </c>
+      <c r="D28" s="189" t="s">
+        <v>242</v>
+      </c>
+      <c r="E28" s="191" t="s">
         <v>254</v>
       </c>
-      <c r="E25" s="189" t="s">
+      <c r="F28" s="194" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="29" ht="42.0" customHeight="1">
+      <c r="A29" s="183">
+        <v>21.0</v>
+      </c>
+      <c r="B29" s="184" t="s">
         <v>256</v>
       </c>
-      <c r="F25" s="191" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="26" ht="42.0" customHeight="1">
-      <c r="A26" s="192">
-        <v>18.0</v>
-      </c>
-      <c r="B26" s="194" t="s">
+      <c r="C29" s="183" t="s">
+        <v>241</v>
+      </c>
+      <c r="D29" s="183" t="s">
+        <v>242</v>
+      </c>
+      <c r="E29" s="186" t="s">
+        <v>257</v>
+      </c>
+      <c r="F29" s="199" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="30" ht="19.5" customHeight="1">
+      <c r="A30" s="181" t="s">
         <v>259</v>
       </c>
-      <c r="C26" s="192" t="s">
-        <v>253</v>
-      </c>
-      <c r="D26" s="192" t="s">
-        <v>261</v>
-      </c>
-      <c r="E26" s="195" t="s">
-        <v>262</v>
-      </c>
-      <c r="F26" s="191" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="27" ht="42.0" customHeight="1">
-      <c r="A27" s="187">
-        <v>19.0</v>
-      </c>
-      <c r="B27" s="188" t="s">
-        <v>264</v>
-      </c>
-      <c r="C27" s="187" t="s">
-        <v>253</v>
-      </c>
-      <c r="D27" s="187" t="s">
-        <v>261</v>
-      </c>
-      <c r="E27" s="189" t="s">
+      <c r="B30" s="175"/>
+      <c r="C30" s="175"/>
+      <c r="D30" s="175"/>
+      <c r="E30" s="175"/>
+      <c r="F30" s="177"/>
+    </row>
+    <row r="31" ht="42.0" customHeight="1">
+      <c r="A31" s="189">
+        <v>22.0</v>
+      </c>
+      <c r="B31" s="190" t="s">
         <v>265</v>
       </c>
-      <c r="F27" s="191" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="28" ht="42.0" customHeight="1">
-      <c r="A28" s="192">
-        <v>20.0</v>
-      </c>
-      <c r="B28" s="194" t="s">
+      <c r="C31" s="189" t="s">
+        <v>267</v>
+      </c>
+      <c r="D31" s="189" t="s">
         <v>268</v>
       </c>
-      <c r="C28" s="192" t="s">
-        <v>253</v>
-      </c>
-      <c r="D28" s="192" t="s">
-        <v>254</v>
-      </c>
-      <c r="E28" s="195" t="s">
-        <v>272</v>
-      </c>
-      <c r="F28" s="196" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="29" ht="42.0" customHeight="1">
-      <c r="A29" s="187">
-        <v>21.0</v>
-      </c>
-      <c r="B29" s="188" t="s">
+      <c r="E31" s="191" t="s">
+        <v>269</v>
+      </c>
+      <c r="F31" s="187" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="32" ht="42.0" customHeight="1">
+      <c r="A32" s="183">
+        <v>23.0</v>
+      </c>
+      <c r="B32" s="184" t="s">
+        <v>273</v>
+      </c>
+      <c r="C32" s="183" t="s">
+        <v>267</v>
+      </c>
+      <c r="D32" s="183" t="s">
+        <v>268</v>
+      </c>
+      <c r="E32" s="186" t="s">
         <v>274</v>
       </c>
-      <c r="C29" s="187" t="s">
-        <v>253</v>
-      </c>
-      <c r="D29" s="187" t="s">
-        <v>254</v>
-      </c>
-      <c r="E29" s="189" t="s">
-        <v>277</v>
-      </c>
-      <c r="F29" s="198" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="30" ht="19.5" customHeight="1">
-      <c r="A30" s="186" t="s">
+      <c r="F32" s="187" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="33" ht="42.0" customHeight="1">
+      <c r="A33" s="189">
+        <v>24.0</v>
+      </c>
+      <c r="B33" s="190" t="s">
+        <v>276</v>
+      </c>
+      <c r="C33" s="189" t="s">
+        <v>278</v>
+      </c>
+      <c r="D33" s="189" t="s">
         <v>280</v>
       </c>
-      <c r="B30" s="179"/>
-      <c r="C30" s="179"/>
-      <c r="D30" s="179"/>
-      <c r="E30" s="179"/>
-      <c r="F30" s="182"/>
-    </row>
-    <row r="31" ht="42.0" customHeight="1">
-      <c r="A31" s="192">
-        <v>22.0</v>
-      </c>
-      <c r="B31" s="194" t="s">
-        <v>285</v>
-      </c>
-      <c r="C31" s="192" t="s">
+      <c r="E33" s="191" t="s">
+        <v>282</v>
+      </c>
+      <c r="F33" s="187" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="34" ht="42.0" customHeight="1">
+      <c r="A34" s="183">
+        <v>25.0</v>
+      </c>
+      <c r="B34" s="184" t="s">
+        <v>283</v>
+      </c>
+      <c r="C34" s="183" t="s">
+        <v>267</v>
+      </c>
+      <c r="D34" s="183" t="s">
+        <v>268</v>
+      </c>
+      <c r="E34" s="186" t="s">
         <v>286</v>
       </c>
-      <c r="D31" s="192" t="s">
-        <v>288</v>
-      </c>
-      <c r="E31" s="195" t="s">
+      <c r="F34" s="194" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="35" ht="42.0" customHeight="1">
+      <c r="A35" s="189">
+        <v>26.0</v>
+      </c>
+      <c r="B35" s="190" t="s">
+        <v>289</v>
+      </c>
+      <c r="C35" s="189" t="s">
+        <v>278</v>
+      </c>
+      <c r="D35" s="189" t="s">
+        <v>280</v>
+      </c>
+      <c r="E35" s="191" t="s">
         <v>290</v>
       </c>
-      <c r="F31" s="191" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="32" ht="42.0" customHeight="1">
-      <c r="A32" s="187">
-        <v>23.0</v>
-      </c>
-      <c r="B32" s="188" t="s">
-        <v>293</v>
-      </c>
-      <c r="C32" s="187" t="s">
-        <v>286</v>
-      </c>
-      <c r="D32" s="187" t="s">
-        <v>288</v>
-      </c>
-      <c r="E32" s="189" t="s">
+      <c r="F35" s="199" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="36" ht="19.5" customHeight="1">
+      <c r="A36" s="181" t="s">
+        <v>292</v>
+      </c>
+      <c r="B36" s="175"/>
+      <c r="C36" s="175"/>
+      <c r="D36" s="175"/>
+      <c r="E36" s="175"/>
+      <c r="F36" s="177"/>
+    </row>
+    <row r="37" ht="42.0" customHeight="1">
+      <c r="A37" s="183">
+        <v>27.0</v>
+      </c>
+      <c r="B37" s="184" t="s">
         <v>295</v>
       </c>
-      <c r="F32" s="191" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="33" ht="42.0" customHeight="1">
-      <c r="A33" s="192">
-        <v>24.0</v>
-      </c>
-      <c r="B33" s="194" t="s">
+      <c r="C37" s="183" t="s">
+        <v>297</v>
+      </c>
+      <c r="D37" s="183" t="s">
         <v>298</v>
       </c>
-      <c r="C33" s="192" t="s">
+      <c r="E37" s="186" t="s">
         <v>300</v>
       </c>
-      <c r="D33" s="192" t="s">
-        <v>301</v>
-      </c>
-      <c r="E33" s="195" t="s">
+      <c r="F37" s="187" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="38" ht="42.0" customHeight="1">
+      <c r="A38" s="189">
+        <v>28.0</v>
+      </c>
+      <c r="B38" s="190" t="s">
         <v>302</v>
       </c>
-      <c r="F33" s="191" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="34" ht="42.0" customHeight="1">
-      <c r="A34" s="187">
-        <v>25.0</v>
-      </c>
-      <c r="B34" s="188" t="s">
+      <c r="C38" s="189" t="s">
+        <v>297</v>
+      </c>
+      <c r="D38" s="189" t="s">
+        <v>304</v>
+      </c>
+      <c r="E38" s="191" t="s">
         <v>305</v>
       </c>
-      <c r="C34" s="187" t="s">
-        <v>286</v>
-      </c>
-      <c r="D34" s="187" t="s">
-        <v>288</v>
-      </c>
-      <c r="E34" s="189" t="s">
-        <v>307</v>
-      </c>
-      <c r="F34" s="196" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="35" ht="42.0" customHeight="1">
-      <c r="A35" s="192">
-        <v>26.0</v>
-      </c>
-      <c r="B35" s="194" t="s">
+      <c r="F38" s="187" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="39" ht="42.0" customHeight="1">
+      <c r="A39" s="183">
+        <v>29.0</v>
+      </c>
+      <c r="B39" s="184" t="s">
+        <v>308</v>
+      </c>
+      <c r="C39" s="183" t="s">
+        <v>297</v>
+      </c>
+      <c r="D39" s="183" t="s">
+        <v>298</v>
+      </c>
+      <c r="E39" s="186" t="s">
         <v>310</v>
       </c>
-      <c r="C35" s="192" t="s">
-        <v>300</v>
-      </c>
-      <c r="D35" s="192" t="s">
-        <v>301</v>
-      </c>
-      <c r="E35" s="195" t="s">
-        <v>311</v>
-      </c>
-      <c r="F35" s="198" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="36" ht="19.5" customHeight="1">
-      <c r="A36" s="186" t="s">
-        <v>313</v>
-      </c>
-      <c r="B36" s="179"/>
-      <c r="C36" s="179"/>
-      <c r="D36" s="179"/>
-      <c r="E36" s="179"/>
-      <c r="F36" s="182"/>
-    </row>
-    <row r="37" ht="42.0" customHeight="1">
-      <c r="A37" s="187">
-        <v>27.0</v>
-      </c>
-      <c r="B37" s="188" t="s">
-        <v>314</v>
-      </c>
-      <c r="C37" s="187" t="s">
+      <c r="F39" s="194" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="40" ht="42.0" customHeight="1">
+      <c r="A40" s="189">
+        <v>30.0</v>
+      </c>
+      <c r="B40" s="190" t="s">
+        <v>312</v>
+      </c>
+      <c r="C40" s="189" t="s">
+        <v>297</v>
+      </c>
+      <c r="D40" s="189" t="s">
+        <v>304</v>
+      </c>
+      <c r="E40" s="191" t="s">
         <v>315</v>
       </c>
-      <c r="D37" s="187" t="s">
-        <v>316</v>
-      </c>
-      <c r="E37" s="189" t="s">
+      <c r="F40" s="199" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="41" ht="19.5" customHeight="1">
+      <c r="A41" s="181" t="s">
         <v>317</v>
       </c>
-      <c r="F37" s="191" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="38" ht="42.0" customHeight="1">
-      <c r="A38" s="192">
-        <v>28.0</v>
-      </c>
-      <c r="B38" s="194" t="s">
-        <v>320</v>
-      </c>
-      <c r="C38" s="192" t="s">
-        <v>315</v>
-      </c>
-      <c r="D38" s="192" t="s">
-        <v>321</v>
-      </c>
-      <c r="E38" s="195" t="s">
+      <c r="B41" s="175"/>
+      <c r="C41" s="175"/>
+      <c r="D41" s="175"/>
+      <c r="E41" s="175"/>
+      <c r="F41" s="177"/>
+    </row>
+    <row r="42" ht="42.0" customHeight="1">
+      <c r="A42" s="183">
+        <v>31.0</v>
+      </c>
+      <c r="B42" s="184" t="s">
         <v>322</v>
       </c>
-      <c r="F38" s="191" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="39" ht="42.0" customHeight="1">
-      <c r="A39" s="187">
-        <v>29.0</v>
-      </c>
-      <c r="B39" s="188" t="s">
+      <c r="C42" s="183" t="s">
+        <v>323</v>
+      </c>
+      <c r="D42" s="183" t="s">
         <v>324</v>
       </c>
-      <c r="C39" s="187" t="s">
-        <v>315</v>
-      </c>
-      <c r="D39" s="187" t="s">
-        <v>316</v>
-      </c>
-      <c r="E39" s="189" t="s">
+      <c r="E42" s="186" t="s">
         <v>325</v>
       </c>
-      <c r="F39" s="196" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="40" ht="42.0" customHeight="1">
-      <c r="A40" s="192">
-        <v>30.0</v>
-      </c>
-      <c r="B40" s="194" t="s">
+      <c r="F42" s="187" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="43" ht="42.0" customHeight="1">
+      <c r="A43" s="189">
+        <v>32.0</v>
+      </c>
+      <c r="B43" s="190" t="s">
         <v>326</v>
       </c>
-      <c r="C40" s="192" t="s">
-        <v>315</v>
-      </c>
-      <c r="D40" s="192" t="s">
-        <v>321</v>
-      </c>
-      <c r="E40" s="195" t="s">
+      <c r="C43" s="189" t="s">
         <v>327</v>
       </c>
-      <c r="F40" s="198" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="41" ht="19.5" customHeight="1">
-      <c r="A41" s="186" t="s">
+      <c r="D43" s="189" t="s">
         <v>328</v>
       </c>
-      <c r="B41" s="179"/>
-      <c r="C41" s="179"/>
-      <c r="D41" s="179"/>
-      <c r="E41" s="179"/>
-      <c r="F41" s="182"/>
-    </row>
-    <row r="42" ht="42.0" customHeight="1">
-      <c r="A42" s="187">
-        <v>31.0</v>
-      </c>
-      <c r="B42" s="188" t="s">
-        <v>331</v>
-      </c>
-      <c r="C42" s="187" t="s">
+      <c r="E43" s="191" t="s">
+        <v>329</v>
+      </c>
+      <c r="F43" s="187" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="44" ht="42.0" customHeight="1">
+      <c r="A44" s="183">
+        <v>33.0</v>
+      </c>
+      <c r="B44" s="184" t="s">
+        <v>330</v>
+      </c>
+      <c r="C44" s="183" t="s">
+        <v>323</v>
+      </c>
+      <c r="D44" s="183" t="s">
         <v>332</v>
       </c>
-      <c r="D42" s="187" t="s">
+      <c r="E44" s="186" t="s">
         <v>333</v>
       </c>
-      <c r="E42" s="189" t="s">
-        <v>335</v>
-      </c>
-      <c r="F42" s="191" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="43" ht="42.0" customHeight="1">
-      <c r="A43" s="192">
-        <v>32.0</v>
-      </c>
-      <c r="B43" s="194" t="s">
+      <c r="F44" s="187" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="45" ht="42.0" customHeight="1">
+      <c r="A45" s="189">
+        <v>34.0</v>
+      </c>
+      <c r="B45" s="190" t="s">
         <v>336</v>
       </c>
-      <c r="C43" s="192" t="s">
-        <v>337</v>
-      </c>
-      <c r="D43" s="192" t="s">
+      <c r="C45" s="189" t="s">
+        <v>327</v>
+      </c>
+      <c r="D45" s="189" t="s">
+        <v>328</v>
+      </c>
+      <c r="E45" s="191" t="s">
         <v>338</v>
       </c>
-      <c r="E43" s="195" t="s">
+      <c r="F45" s="194" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="46" ht="19.5" customHeight="1">
+      <c r="A46" s="181" t="s">
         <v>339</v>
       </c>
-      <c r="F43" s="191" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="44" ht="42.0" customHeight="1">
-      <c r="A44" s="187">
-        <v>33.0</v>
-      </c>
-      <c r="B44" s="188" t="s">
-        <v>341</v>
-      </c>
-      <c r="C44" s="187" t="s">
+      <c r="B46" s="175"/>
+      <c r="C46" s="175"/>
+      <c r="D46" s="175"/>
+      <c r="E46" s="175"/>
+      <c r="F46" s="177"/>
+    </row>
+    <row r="47" ht="42.0" customHeight="1">
+      <c r="A47" s="183">
+        <v>35.0</v>
+      </c>
+      <c r="B47" s="184" t="s">
+        <v>344</v>
+      </c>
+      <c r="C47" s="183" t="s">
+        <v>346</v>
+      </c>
+      <c r="D47" s="183" t="s">
         <v>332</v>
       </c>
-      <c r="D44" s="187" t="s">
-        <v>342</v>
-      </c>
-      <c r="E44" s="189" t="s">
-        <v>343</v>
-      </c>
-      <c r="F44" s="191" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="45" ht="42.0" customHeight="1">
-      <c r="A45" s="192">
-        <v>34.0</v>
-      </c>
-      <c r="B45" s="194" t="s">
-        <v>344</v>
-      </c>
-      <c r="C45" s="192" t="s">
-        <v>337</v>
-      </c>
-      <c r="D45" s="192" t="s">
-        <v>338</v>
-      </c>
-      <c r="E45" s="195" t="s">
+      <c r="E47" s="186" t="s">
         <v>347</v>
       </c>
-      <c r="F45" s="196" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="46" ht="19.5" customHeight="1">
-      <c r="A46" s="186" t="s">
+      <c r="F47" s="187" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="48" ht="42.0" customHeight="1">
+      <c r="A48" s="189">
+        <v>36.0</v>
+      </c>
+      <c r="B48" s="190" t="s">
         <v>348</v>
       </c>
-      <c r="B46" s="179"/>
-      <c r="C46" s="179"/>
-      <c r="D46" s="179"/>
-      <c r="E46" s="179"/>
-      <c r="F46" s="182"/>
-    </row>
-    <row r="47" ht="42.0" customHeight="1">
-      <c r="A47" s="187">
-        <v>35.0</v>
-      </c>
-      <c r="B47" s="188" t="s">
-        <v>351</v>
-      </c>
-      <c r="C47" s="187" t="s">
+      <c r="C48" s="189" t="s">
+        <v>346</v>
+      </c>
+      <c r="D48" s="189" t="s">
+        <v>332</v>
+      </c>
+      <c r="E48" s="191" t="s">
         <v>352</v>
       </c>
-      <c r="D47" s="187" t="s">
-        <v>342</v>
-      </c>
-      <c r="E47" s="189" t="s">
-        <v>353</v>
-      </c>
-      <c r="F47" s="191" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="48" ht="42.0" customHeight="1">
-      <c r="A48" s="192">
-        <v>36.0</v>
-      </c>
-      <c r="B48" s="194" t="s">
+      <c r="F48" s="187" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="49" ht="42.0" customHeight="1">
+      <c r="A49" s="183">
+        <v>37.0</v>
+      </c>
+      <c r="B49" s="184" t="s">
+        <v>354</v>
+      </c>
+      <c r="C49" s="183" t="s">
+        <v>346</v>
+      </c>
+      <c r="D49" s="183" t="s">
+        <v>332</v>
+      </c>
+      <c r="E49" s="186" t="s">
         <v>356</v>
       </c>
-      <c r="C48" s="192" t="s">
-        <v>352</v>
-      </c>
-      <c r="D48" s="192" t="s">
-        <v>342</v>
-      </c>
-      <c r="E48" s="195" t="s">
+      <c r="F49" s="187" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="50" ht="42.0" customHeight="1">
+      <c r="A50" s="189">
+        <v>38.0</v>
+      </c>
+      <c r="B50" s="190" t="s">
         <v>358</v>
       </c>
-      <c r="F48" s="191" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="49" ht="42.0" customHeight="1">
-      <c r="A49" s="187">
-        <v>37.0</v>
-      </c>
-      <c r="B49" s="188" t="s">
-        <v>359</v>
-      </c>
-      <c r="C49" s="187" t="s">
-        <v>352</v>
-      </c>
-      <c r="D49" s="187" t="s">
-        <v>342</v>
-      </c>
-      <c r="E49" s="189" t="s">
+      <c r="C50" s="189" t="s">
+        <v>346</v>
+      </c>
+      <c r="D50" s="189" t="s">
+        <v>332</v>
+      </c>
+      <c r="E50" s="191" t="s">
         <v>360</v>
       </c>
-      <c r="F49" s="191" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="50" ht="42.0" customHeight="1">
-      <c r="A50" s="192">
-        <v>38.0</v>
-      </c>
-      <c r="B50" s="194" t="s">
+      <c r="F50" s="194" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="51" ht="19.5" customHeight="1">
+      <c r="A51" s="181" t="s">
         <v>362</v>
       </c>
-      <c r="C50" s="192" t="s">
-        <v>352</v>
-      </c>
-      <c r="D50" s="192" t="s">
-        <v>342</v>
-      </c>
-      <c r="E50" s="195" t="s">
-        <v>363</v>
-      </c>
-      <c r="F50" s="196" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="51" ht="19.5" customHeight="1">
-      <c r="A51" s="186" t="s">
+      <c r="B51" s="175"/>
+      <c r="C51" s="175"/>
+      <c r="D51" s="175"/>
+      <c r="E51" s="175"/>
+      <c r="F51" s="177"/>
+    </row>
+    <row r="52" ht="42.0" customHeight="1">
+      <c r="A52" s="183">
+        <v>39.0</v>
+      </c>
+      <c r="B52" s="184" t="s">
+        <v>364</v>
+      </c>
+      <c r="C52" s="183" t="s">
         <v>365</v>
       </c>
-      <c r="B51" s="179"/>
-      <c r="C51" s="179"/>
-      <c r="D51" s="179"/>
-      <c r="E51" s="179"/>
-      <c r="F51" s="182"/>
-    </row>
-    <row r="52" ht="42.0" customHeight="1">
-      <c r="A52" s="187">
-        <v>39.0</v>
-      </c>
-      <c r="B52" s="188" t="s">
+      <c r="D52" s="183" t="s">
+        <v>204</v>
+      </c>
+      <c r="E52" s="186" t="s">
+        <v>366</v>
+      </c>
+      <c r="F52" s="187" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="53" ht="42.0" customHeight="1">
+      <c r="A53" s="189">
+        <v>40.0</v>
+      </c>
+      <c r="B53" s="190" t="s">
+        <v>367</v>
+      </c>
+      <c r="C53" s="189" t="s">
+        <v>365</v>
+      </c>
+      <c r="D53" s="189" t="s">
+        <v>204</v>
+      </c>
+      <c r="E53" s="191" t="s">
+        <v>368</v>
+      </c>
+      <c r="F53" s="194" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="54" ht="42.0" customHeight="1">
+      <c r="A54" s="183">
+        <v>41.0</v>
+      </c>
+      <c r="B54" s="184" t="s">
+        <v>369</v>
+      </c>
+      <c r="C54" s="183" t="s">
+        <v>365</v>
+      </c>
+      <c r="D54" s="183" t="s">
+        <v>204</v>
+      </c>
+      <c r="E54" s="186" t="s">
+        <v>370</v>
+      </c>
+      <c r="F54" s="199" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="55" ht="19.5" customHeight="1">
+      <c r="A55" s="181" t="s">
         <v>371</v>
       </c>
-      <c r="C52" s="187" t="s">
+      <c r="B55" s="175"/>
+      <c r="C55" s="175"/>
+      <c r="D55" s="175"/>
+      <c r="E55" s="175"/>
+      <c r="F55" s="177"/>
+    </row>
+    <row r="56" ht="42.0" customHeight="1">
+      <c r="A56" s="189">
+        <v>42.0</v>
+      </c>
+      <c r="B56" s="190" t="s">
         <v>372</v>
       </c>
-      <c r="D52" s="187" t="s">
-        <v>206</v>
-      </c>
-      <c r="E52" s="189" t="s">
+      <c r="C56" s="189" t="s">
         <v>373</v>
       </c>
-      <c r="F52" s="191" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="53" ht="42.0" customHeight="1">
-      <c r="A53" s="192">
-        <v>40.0</v>
-      </c>
-      <c r="B53" s="194" t="s">
+      <c r="D56" s="189" t="s">
         <v>374</v>
       </c>
-      <c r="C53" s="192" t="s">
-        <v>372</v>
-      </c>
-      <c r="D53" s="192" t="s">
-        <v>206</v>
-      </c>
-      <c r="E53" s="195" t="s">
+      <c r="E56" s="191" t="s">
         <v>375</v>
       </c>
-      <c r="F53" s="196" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="54" ht="42.0" customHeight="1">
-      <c r="A54" s="187">
-        <v>41.0</v>
-      </c>
-      <c r="B54" s="188" t="s">
+      <c r="F56" s="187" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="57" ht="42.0" customHeight="1">
+      <c r="A57" s="183">
+        <v>43.0</v>
+      </c>
+      <c r="B57" s="184" t="s">
         <v>376</v>
       </c>
-      <c r="C54" s="187" t="s">
-        <v>372</v>
-      </c>
-      <c r="D54" s="187" t="s">
-        <v>206</v>
-      </c>
-      <c r="E54" s="189" t="s">
+      <c r="C57" s="183" t="s">
+        <v>373</v>
+      </c>
+      <c r="D57" s="183" t="s">
+        <v>374</v>
+      </c>
+      <c r="E57" s="186" t="s">
         <v>377</v>
       </c>
-      <c r="F54" s="198" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="55" ht="19.5" customHeight="1">
-      <c r="A55" s="186" t="s">
+      <c r="F57" s="187" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="58" ht="42.0" customHeight="1">
+      <c r="A58" s="189">
+        <v>44.0</v>
+      </c>
+      <c r="B58" s="190" t="s">
         <v>378</v>
       </c>
-      <c r="B55" s="179"/>
-      <c r="C55" s="179"/>
-      <c r="D55" s="179"/>
-      <c r="E55" s="179"/>
-      <c r="F55" s="182"/>
-    </row>
-    <row r="56" ht="42.0" customHeight="1">
-      <c r="A56" s="192">
-        <v>42.0</v>
-      </c>
-      <c r="B56" s="194" t="s">
+      <c r="C58" s="189" t="s">
+        <v>373</v>
+      </c>
+      <c r="D58" s="189" t="s">
+        <v>374</v>
+      </c>
+      <c r="E58" s="191" t="s">
         <v>379</v>
       </c>
-      <c r="C56" s="192" t="s">
-        <v>380</v>
-      </c>
-      <c r="D56" s="192" t="s">
-        <v>381</v>
-      </c>
-      <c r="E56" s="195" t="s">
-        <v>382</v>
-      </c>
-      <c r="F56" s="191" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="57" ht="42.0" customHeight="1">
-      <c r="A57" s="187">
-        <v>43.0</v>
-      </c>
-      <c r="B57" s="188" t="s">
-        <v>383</v>
-      </c>
-      <c r="C57" s="187" t="s">
-        <v>380</v>
-      </c>
-      <c r="D57" s="187" t="s">
-        <v>381</v>
-      </c>
-      <c r="E57" s="189" t="s">
-        <v>384</v>
-      </c>
-      <c r="F57" s="191" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="58" ht="42.0" customHeight="1">
-      <c r="A58" s="192">
-        <v>44.0</v>
-      </c>
-      <c r="B58" s="194" t="s">
-        <v>385</v>
-      </c>
-      <c r="C58" s="192" t="s">
-        <v>380</v>
-      </c>
-      <c r="D58" s="192" t="s">
-        <v>381</v>
-      </c>
-      <c r="E58" s="195" t="s">
-        <v>386</v>
-      </c>
-      <c r="F58" s="196" t="s">
-        <v>165</v>
+      <c r="F58" s="194" t="s">
+        <v>169</v>
       </c>
     </row>
     <row r="59"/>
     <row r="60" ht="18.0" customHeight="1">
-      <c r="A60" s="206" t="s">
-        <v>312</v>
-      </c>
-      <c r="B60" s="179"/>
-      <c r="C60" s="179"/>
-      <c r="D60" s="179"/>
-      <c r="E60" s="179"/>
-      <c r="F60" s="182"/>
+      <c r="A60" s="211" t="s">
+        <v>361</v>
+      </c>
+      <c r="B60" s="175"/>
+      <c r="C60" s="175"/>
+      <c r="D60" s="175"/>
+      <c r="E60" s="175"/>
+      <c r="F60" s="177"/>
     </row>
     <row r="61" ht="18.0" customHeight="1">
-      <c r="A61" s="207" t="s">
-        <v>319</v>
-      </c>
-      <c r="B61" s="208" t="s">
-        <v>323</v>
-      </c>
-      <c r="C61" s="179"/>
-      <c r="D61" s="179"/>
-      <c r="E61" s="179"/>
-      <c r="F61" s="182"/>
+      <c r="A61" s="213" t="s">
+        <v>380</v>
+      </c>
+      <c r="B61" s="216" t="s">
+        <v>381</v>
+      </c>
+      <c r="C61" s="175"/>
+      <c r="D61" s="175"/>
+      <c r="E61" s="175"/>
+      <c r="F61" s="177"/>
     </row>
     <row r="62" ht="18.0" customHeight="1">
-      <c r="A62" s="210" t="s">
-        <v>330</v>
-      </c>
-      <c r="B62" s="208" t="s">
-        <v>340</v>
-      </c>
-      <c r="C62" s="179"/>
-      <c r="D62" s="179"/>
-      <c r="E62" s="179"/>
-      <c r="F62" s="182"/>
+      <c r="A62" s="219" t="s">
+        <v>382</v>
+      </c>
+      <c r="B62" s="216" t="s">
+        <v>383</v>
+      </c>
+      <c r="C62" s="175"/>
+      <c r="D62" s="175"/>
+      <c r="E62" s="175"/>
+      <c r="F62" s="177"/>
     </row>
     <row r="63" ht="18.0" customHeight="1">
-      <c r="A63" s="213" t="s">
-        <v>346</v>
-      </c>
-      <c r="B63" s="208" t="s">
-        <v>349</v>
-      </c>
-      <c r="C63" s="179"/>
-      <c r="D63" s="179"/>
-      <c r="E63" s="179"/>
-      <c r="F63" s="182"/>
+      <c r="A63" s="221" t="s">
+        <v>384</v>
+      </c>
+      <c r="B63" s="216" t="s">
+        <v>385</v>
+      </c>
+      <c r="C63" s="175"/>
+      <c r="D63" s="175"/>
+      <c r="E63" s="175"/>
+      <c r="F63" s="177"/>
     </row>
     <row r="64"/>
     <row r="65" ht="39.75" customHeight="1">
-      <c r="A65" s="214" t="s">
-        <v>388</v>
-      </c>
-      <c r="B65" s="179"/>
-      <c r="C65" s="179"/>
-      <c r="D65" s="179"/>
-      <c r="E65" s="179"/>
-      <c r="F65" s="182"/>
+      <c r="A65" s="224" t="s">
+        <v>387</v>
+      </c>
+      <c r="B65" s="175"/>
+      <c r="C65" s="175"/>
+      <c r="D65" s="175"/>
+      <c r="E65" s="175"/>
+      <c r="F65" s="177"/>
     </row>
     <row r="66"/>
     <row r="67"/>
@@ -17658,642 +17658,642 @@
   </cols>
   <sheetData>
     <row r="1" ht="37.5" customHeight="1">
-      <c r="A1" s="176" t="s">
-        <v>122</v>
-      </c>
-      <c r="B1" s="179"/>
-      <c r="C1" s="179"/>
-      <c r="D1" s="179"/>
-      <c r="E1" s="179"/>
-      <c r="F1" s="182"/>
+      <c r="A1" s="174" t="s">
+        <v>131</v>
+      </c>
+      <c r="B1" s="175"/>
+      <c r="C1" s="175"/>
+      <c r="D1" s="175"/>
+      <c r="E1" s="175"/>
+      <c r="F1" s="177"/>
     </row>
     <row r="2" ht="15.75" customHeight="1">
-      <c r="A2" s="183" t="s">
-        <v>130</v>
-      </c>
-      <c r="B2" s="179"/>
-      <c r="C2" s="179"/>
-      <c r="D2" s="179"/>
-      <c r="E2" s="179"/>
-      <c r="F2" s="182"/>
+      <c r="A2" s="178" t="s">
+        <v>140</v>
+      </c>
+      <c r="B2" s="175"/>
+      <c r="C2" s="175"/>
+      <c r="D2" s="175"/>
+      <c r="E2" s="175"/>
+      <c r="F2" s="177"/>
     </row>
     <row r="3" ht="24.0" customHeight="1">
-      <c r="A3" s="184" t="s">
+      <c r="A3" s="180" t="s">
+        <v>124</v>
+      </c>
+      <c r="B3" s="180" t="s">
+        <v>141</v>
+      </c>
+      <c r="C3" s="180" t="s">
+        <v>142</v>
+      </c>
+      <c r="D3" s="180" t="s">
+        <v>143</v>
+      </c>
+      <c r="E3" s="180" t="s">
+        <v>144</v>
+      </c>
+      <c r="F3" s="180" t="s">
         <v>129</v>
       </c>
-      <c r="B3" s="184" t="s">
-        <v>137</v>
-      </c>
-      <c r="C3" s="184" t="s">
-        <v>138</v>
-      </c>
-      <c r="D3" s="184" t="s">
+    </row>
+    <row r="4" ht="19.5" customHeight="1">
+      <c r="A4" s="181" t="s">
+        <v>146</v>
+      </c>
+      <c r="B4" s="175"/>
+      <c r="C4" s="175"/>
+      <c r="D4" s="175"/>
+      <c r="E4" s="175"/>
+      <c r="F4" s="177"/>
+    </row>
+    <row r="5" ht="42.0" customHeight="1">
+      <c r="A5" s="183">
+        <v>1.0</v>
+      </c>
+      <c r="B5" s="184" t="s">
+        <v>150</v>
+      </c>
+      <c r="C5" s="183" t="s">
+        <v>151</v>
+      </c>
+      <c r="D5" s="183" t="s">
+        <v>152</v>
+      </c>
+      <c r="E5" s="186" t="s">
+        <v>153</v>
+      </c>
+      <c r="F5" s="187" t="s">
         <v>139</v>
       </c>
-      <c r="E3" s="184" t="s">
-        <v>140</v>
-      </c>
-      <c r="F3" s="184" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="4" ht="19.5" customHeight="1">
-      <c r="A4" s="186" t="s">
-        <v>141</v>
-      </c>
-      <c r="B4" s="179"/>
-      <c r="C4" s="179"/>
-      <c r="D4" s="179"/>
-      <c r="E4" s="179"/>
-      <c r="F4" s="182"/>
-    </row>
-    <row r="5" ht="42.0" customHeight="1">
-      <c r="A5" s="187">
-        <v>1.0</v>
-      </c>
-      <c r="B5" s="188" t="s">
-        <v>142</v>
-      </c>
-      <c r="C5" s="187" t="s">
-        <v>143</v>
-      </c>
-      <c r="D5" s="187" t="s">
-        <v>144</v>
-      </c>
-      <c r="E5" s="189" t="s">
-        <v>145</v>
-      </c>
-      <c r="F5" s="191" t="s">
-        <v>150</v>
-      </c>
     </row>
     <row r="6" ht="42.0" customHeight="1">
-      <c r="A6" s="192">
+      <c r="A6" s="189">
         <v>2.0</v>
       </c>
-      <c r="B6" s="194" t="s">
-        <v>152</v>
-      </c>
-      <c r="C6" s="192" t="s">
-        <v>153</v>
-      </c>
-      <c r="D6" s="192" t="s">
+      <c r="B6" s="190" t="s">
         <v>154</v>
       </c>
-      <c r="E6" s="195" t="s">
+      <c r="C6" s="189" t="s">
+        <v>155</v>
+      </c>
+      <c r="D6" s="189" t="s">
         <v>156</v>
       </c>
-      <c r="F6" s="191" t="s">
-        <v>150</v>
+      <c r="E6" s="191" t="s">
+        <v>157</v>
+      </c>
+      <c r="F6" s="187" t="s">
+        <v>139</v>
       </c>
     </row>
     <row r="7" ht="42.0" customHeight="1">
-      <c r="A7" s="187">
+      <c r="A7" s="183">
         <v>3.0</v>
       </c>
-      <c r="B7" s="188" t="s">
+      <c r="B7" s="184" t="s">
         <v>158</v>
       </c>
-      <c r="C7" s="187" t="s">
-        <v>153</v>
-      </c>
-      <c r="D7" s="187" t="s">
+      <c r="C7" s="183" t="s">
+        <v>155</v>
+      </c>
+      <c r="D7" s="183" t="s">
+        <v>159</v>
+      </c>
+      <c r="E7" s="186" t="s">
         <v>160</v>
       </c>
-      <c r="E7" s="189" t="s">
-        <v>162</v>
-      </c>
-      <c r="F7" s="191" t="s">
-        <v>150</v>
+      <c r="F7" s="187" t="s">
+        <v>139</v>
       </c>
     </row>
     <row r="8" ht="42.0" customHeight="1">
-      <c r="A8" s="192">
+      <c r="A8" s="189">
         <v>4.0</v>
       </c>
-      <c r="B8" s="194" t="s">
+      <c r="B8" s="190" t="s">
+        <v>161</v>
+      </c>
+      <c r="C8" s="189" t="s">
+        <v>163</v>
+      </c>
+      <c r="D8" s="189" t="s">
         <v>164</v>
       </c>
-      <c r="C8" s="192" t="s">
-        <v>166</v>
-      </c>
-      <c r="D8" s="192" t="s">
-        <v>167</v>
-      </c>
-      <c r="E8" s="195" t="s">
+      <c r="E8" s="191" t="s">
+        <v>165</v>
+      </c>
+      <c r="F8" s="187" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="9" ht="42.0" customHeight="1">
+      <c r="A9" s="183">
+        <v>5.0</v>
+      </c>
+      <c r="B9" s="184" t="s">
         <v>168</v>
       </c>
-      <c r="F8" s="191" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="9" ht="42.0" customHeight="1">
-      <c r="A9" s="187">
-        <v>5.0</v>
-      </c>
-      <c r="B9" s="188" t="s">
+      <c r="C9" s="183" t="s">
+        <v>163</v>
+      </c>
+      <c r="D9" s="183" t="s">
+        <v>170</v>
+      </c>
+      <c r="E9" s="186" t="s">
+        <v>171</v>
+      </c>
+      <c r="F9" s="194" t="s">
         <v>169</v>
       </c>
-      <c r="C9" s="187" t="s">
-        <v>166</v>
-      </c>
-      <c r="D9" s="187" t="s">
-        <v>170</v>
-      </c>
-      <c r="E9" s="189" t="s">
-        <v>171</v>
-      </c>
-      <c r="F9" s="196" t="s">
-        <v>165</v>
-      </c>
     </row>
     <row r="10" ht="19.5" customHeight="1">
-      <c r="A10" s="186" t="s">
+      <c r="A10" s="181" t="s">
         <v>172</v>
       </c>
-      <c r="B10" s="179"/>
-      <c r="C10" s="179"/>
-      <c r="D10" s="179"/>
-      <c r="E10" s="179"/>
-      <c r="F10" s="182"/>
+      <c r="B10" s="175"/>
+      <c r="C10" s="175"/>
+      <c r="D10" s="175"/>
+      <c r="E10" s="175"/>
+      <c r="F10" s="177"/>
     </row>
     <row r="11" ht="42.0" customHeight="1">
-      <c r="A11" s="192">
+      <c r="A11" s="189">
         <v>6.0</v>
       </c>
-      <c r="B11" s="194" t="s">
-        <v>175</v>
-      </c>
-      <c r="C11" s="192" t="s">
-        <v>177</v>
-      </c>
-      <c r="D11" s="192" t="s">
+      <c r="B11" s="190" t="s">
+        <v>176</v>
+      </c>
+      <c r="C11" s="189" t="s">
         <v>178</v>
       </c>
-      <c r="E11" s="195" t="s">
+      <c r="D11" s="189" t="s">
         <v>179</v>
       </c>
-      <c r="F11" s="191" t="s">
-        <v>150</v>
+      <c r="E11" s="191" t="s">
+        <v>180</v>
+      </c>
+      <c r="F11" s="187" t="s">
+        <v>139</v>
       </c>
     </row>
     <row r="12" ht="42.0" customHeight="1">
-      <c r="A12" s="187">
+      <c r="A12" s="183">
         <v>7.0</v>
       </c>
-      <c r="B12" s="188" t="s">
-        <v>181</v>
-      </c>
-      <c r="C12" s="187" t="s">
-        <v>177</v>
-      </c>
-      <c r="D12" s="187" t="s">
+      <c r="B12" s="184" t="s">
+        <v>182</v>
+      </c>
+      <c r="C12" s="183" t="s">
         <v>178</v>
       </c>
-      <c r="E12" s="189" t="s">
-        <v>182</v>
-      </c>
-      <c r="F12" s="191" t="s">
-        <v>150</v>
+      <c r="D12" s="183" t="s">
+        <v>179</v>
+      </c>
+      <c r="E12" s="186" t="s">
+        <v>186</v>
+      </c>
+      <c r="F12" s="187" t="s">
+        <v>139</v>
       </c>
     </row>
     <row r="13" ht="42.0" customHeight="1">
-      <c r="A13" s="192">
+      <c r="A13" s="189">
         <v>8.0</v>
       </c>
-      <c r="B13" s="194" t="s">
-        <v>183</v>
-      </c>
-      <c r="C13" s="192" t="s">
-        <v>177</v>
-      </c>
-      <c r="D13" s="192" t="s">
-        <v>184</v>
-      </c>
-      <c r="E13" s="195" t="s">
-        <v>187</v>
-      </c>
-      <c r="F13" s="196" t="s">
-        <v>165</v>
+      <c r="B13" s="190" t="s">
+        <v>188</v>
+      </c>
+      <c r="C13" s="189" t="s">
+        <v>178</v>
+      </c>
+      <c r="D13" s="189" t="s">
+        <v>190</v>
+      </c>
+      <c r="E13" s="191" t="s">
+        <v>191</v>
+      </c>
+      <c r="F13" s="194" t="s">
+        <v>169</v>
       </c>
     </row>
     <row r="14" ht="42.0" customHeight="1">
-      <c r="A14" s="187">
+      <c r="A14" s="183">
         <v>9.0</v>
       </c>
-      <c r="B14" s="188" t="s">
-        <v>190</v>
-      </c>
-      <c r="C14" s="187" t="s">
-        <v>177</v>
-      </c>
-      <c r="D14" s="187" t="s">
-        <v>192</v>
-      </c>
-      <c r="E14" s="189" t="s">
+      <c r="B14" s="184" t="s">
+        <v>193</v>
+      </c>
+      <c r="C14" s="183" t="s">
+        <v>178</v>
+      </c>
+      <c r="D14" s="183" t="s">
         <v>194</v>
       </c>
-      <c r="F14" s="198" t="s">
-        <v>196</v>
+      <c r="E14" s="186" t="s">
+        <v>195</v>
+      </c>
+      <c r="F14" s="199" t="s">
+        <v>198</v>
       </c>
     </row>
     <row r="15" ht="42.0" customHeight="1">
-      <c r="A15" s="192">
+      <c r="A15" s="189">
         <v>10.0</v>
       </c>
-      <c r="B15" s="194" t="s">
-        <v>200</v>
-      </c>
-      <c r="C15" s="192" t="s">
-        <v>177</v>
-      </c>
-      <c r="D15" s="192" t="s">
-        <v>192</v>
-      </c>
-      <c r="E15" s="195" t="s">
-        <v>201</v>
-      </c>
-      <c r="F15" s="198" t="s">
-        <v>196</v>
+      <c r="B15" s="190" t="s">
+        <v>208</v>
+      </c>
+      <c r="C15" s="189" t="s">
+        <v>178</v>
+      </c>
+      <c r="D15" s="189" t="s">
+        <v>194</v>
+      </c>
+      <c r="E15" s="191" t="s">
+        <v>212</v>
+      </c>
+      <c r="F15" s="199" t="s">
+        <v>198</v>
       </c>
     </row>
     <row r="16" ht="19.5" customHeight="1">
-      <c r="A16" s="186" t="s">
-        <v>203</v>
-      </c>
-      <c r="B16" s="179"/>
-      <c r="C16" s="179"/>
-      <c r="D16" s="179"/>
-      <c r="E16" s="179"/>
-      <c r="F16" s="182"/>
+      <c r="A16" s="181" t="s">
+        <v>214</v>
+      </c>
+      <c r="B16" s="175"/>
+      <c r="C16" s="175"/>
+      <c r="D16" s="175"/>
+      <c r="E16" s="175"/>
+      <c r="F16" s="177"/>
     </row>
     <row r="17" ht="42.0" customHeight="1">
-      <c r="A17" s="187">
+      <c r="A17" s="183">
         <v>11.0</v>
       </c>
-      <c r="B17" s="188" t="s">
-        <v>208</v>
-      </c>
-      <c r="C17" s="187" t="s">
-        <v>210</v>
-      </c>
-      <c r="D17" s="187" t="s">
-        <v>211</v>
-      </c>
-      <c r="E17" s="189" t="s">
-        <v>212</v>
-      </c>
-      <c r="F17" s="191" t="s">
-        <v>150</v>
+      <c r="B17" s="184" t="s">
+        <v>222</v>
+      </c>
+      <c r="C17" s="183" t="s">
+        <v>224</v>
+      </c>
+      <c r="D17" s="183" t="s">
+        <v>225</v>
+      </c>
+      <c r="E17" s="186" t="s">
+        <v>227</v>
+      </c>
+      <c r="F17" s="187" t="s">
+        <v>139</v>
       </c>
     </row>
     <row r="18" ht="42.0" customHeight="1">
-      <c r="A18" s="192">
+      <c r="A18" s="189">
         <v>12.0</v>
       </c>
-      <c r="B18" s="194" t="s">
-        <v>214</v>
-      </c>
-      <c r="C18" s="192" t="s">
-        <v>210</v>
-      </c>
-      <c r="D18" s="192" t="s">
-        <v>216</v>
-      </c>
-      <c r="E18" s="195" t="s">
-        <v>218</v>
-      </c>
-      <c r="F18" s="196" t="s">
-        <v>165</v>
+      <c r="B18" s="190" t="s">
+        <v>230</v>
+      </c>
+      <c r="C18" s="189" t="s">
+        <v>224</v>
+      </c>
+      <c r="D18" s="189" t="s">
+        <v>232</v>
+      </c>
+      <c r="E18" s="191" t="s">
+        <v>234</v>
+      </c>
+      <c r="F18" s="194" t="s">
+        <v>169</v>
       </c>
     </row>
     <row r="19" ht="42.0" customHeight="1">
-      <c r="A19" s="187">
+      <c r="A19" s="183">
         <v>13.0</v>
       </c>
-      <c r="B19" s="188" t="s">
-        <v>221</v>
-      </c>
-      <c r="C19" s="187" t="s">
-        <v>210</v>
-      </c>
-      <c r="D19" s="187" t="s">
-        <v>223</v>
-      </c>
-      <c r="E19" s="189" t="s">
+      <c r="B19" s="184" t="s">
+        <v>236</v>
+      </c>
+      <c r="C19" s="183" t="s">
         <v>224</v>
       </c>
-      <c r="F19" s="196" t="s">
-        <v>165</v>
+      <c r="D19" s="183" t="s">
+        <v>237</v>
+      </c>
+      <c r="E19" s="186" t="s">
+        <v>238</v>
+      </c>
+      <c r="F19" s="194" t="s">
+        <v>169</v>
       </c>
     </row>
     <row r="20" ht="42.0" customHeight="1">
-      <c r="A20" s="192">
+      <c r="A20" s="189">
         <v>14.0</v>
       </c>
-      <c r="B20" s="194" t="s">
-        <v>225</v>
-      </c>
-      <c r="C20" s="192" t="s">
-        <v>210</v>
-      </c>
-      <c r="D20" s="192" t="s">
-        <v>226</v>
-      </c>
-      <c r="E20" s="195" t="s">
-        <v>227</v>
-      </c>
-      <c r="F20" s="198" t="s">
-        <v>196</v>
+      <c r="B20" s="190" t="s">
+        <v>239</v>
+      </c>
+      <c r="C20" s="189" t="s">
+        <v>224</v>
+      </c>
+      <c r="D20" s="189" t="s">
+        <v>243</v>
+      </c>
+      <c r="E20" s="191" t="s">
+        <v>245</v>
+      </c>
+      <c r="F20" s="199" t="s">
+        <v>198</v>
       </c>
     </row>
     <row r="21" ht="19.5" customHeight="1">
-      <c r="A21" s="186" t="s">
-        <v>231</v>
-      </c>
-      <c r="B21" s="179"/>
-      <c r="C21" s="179"/>
-      <c r="D21" s="179"/>
-      <c r="E21" s="179"/>
-      <c r="F21" s="182"/>
+      <c r="A21" s="181" t="s">
+        <v>249</v>
+      </c>
+      <c r="B21" s="175"/>
+      <c r="C21" s="175"/>
+      <c r="D21" s="175"/>
+      <c r="E21" s="175"/>
+      <c r="F21" s="177"/>
     </row>
     <row r="22" ht="42.0" customHeight="1">
-      <c r="A22" s="187">
+      <c r="A22" s="183">
         <v>15.0</v>
       </c>
-      <c r="B22" s="188" t="s">
-        <v>237</v>
-      </c>
-      <c r="C22" s="187" t="s">
-        <v>238</v>
-      </c>
-      <c r="D22" s="187" t="s">
-        <v>239</v>
-      </c>
-      <c r="E22" s="189" t="s">
-        <v>241</v>
-      </c>
-      <c r="F22" s="191" t="s">
-        <v>150</v>
+      <c r="B22" s="184" t="s">
+        <v>258</v>
+      </c>
+      <c r="C22" s="183" t="s">
+        <v>260</v>
+      </c>
+      <c r="D22" s="183" t="s">
+        <v>261</v>
+      </c>
+      <c r="E22" s="186" t="s">
+        <v>262</v>
+      </c>
+      <c r="F22" s="187" t="s">
+        <v>139</v>
       </c>
     </row>
     <row r="23" ht="42.0" customHeight="1">
-      <c r="A23" s="192">
+      <c r="A23" s="189">
         <v>16.0</v>
       </c>
-      <c r="B23" s="194" t="s">
-        <v>244</v>
-      </c>
-      <c r="C23" s="192" t="s">
-        <v>245</v>
-      </c>
-      <c r="D23" s="192" t="s">
-        <v>246</v>
-      </c>
-      <c r="E23" s="195" t="s">
-        <v>247</v>
-      </c>
-      <c r="F23" s="196" t="s">
-        <v>165</v>
+      <c r="B23" s="190" t="s">
+        <v>264</v>
+      </c>
+      <c r="C23" s="189" t="s">
+        <v>266</v>
+      </c>
+      <c r="D23" s="189" t="s">
+        <v>270</v>
+      </c>
+      <c r="E23" s="191" t="s">
+        <v>271</v>
+      </c>
+      <c r="F23" s="194" t="s">
+        <v>169</v>
       </c>
     </row>
     <row r="24" ht="42.0" customHeight="1">
-      <c r="A24" s="187">
+      <c r="A24" s="183">
         <v>17.0</v>
       </c>
-      <c r="B24" s="188" t="s">
-        <v>248</v>
-      </c>
-      <c r="C24" s="187" t="s">
-        <v>249</v>
-      </c>
-      <c r="D24" s="187" t="s">
-        <v>250</v>
-      </c>
-      <c r="E24" s="189" t="s">
-        <v>251</v>
-      </c>
-      <c r="F24" s="196" t="s">
-        <v>165</v>
+      <c r="B24" s="184" t="s">
+        <v>275</v>
+      </c>
+      <c r="C24" s="183" t="s">
+        <v>277</v>
+      </c>
+      <c r="D24" s="183" t="s">
+        <v>279</v>
+      </c>
+      <c r="E24" s="186" t="s">
+        <v>281</v>
+      </c>
+      <c r="F24" s="194" t="s">
+        <v>169</v>
       </c>
     </row>
     <row r="25" ht="42.0" customHeight="1">
-      <c r="A25" s="192">
+      <c r="A25" s="189">
         <v>18.0</v>
       </c>
-      <c r="B25" s="194" t="s">
-        <v>255</v>
-      </c>
-      <c r="C25" s="192" t="s">
-        <v>245</v>
-      </c>
-      <c r="D25" s="192" t="s">
-        <v>257</v>
-      </c>
-      <c r="E25" s="195" t="s">
-        <v>258</v>
-      </c>
-      <c r="F25" s="198" t="s">
-        <v>196</v>
+      <c r="B25" s="190" t="s">
+        <v>285</v>
+      </c>
+      <c r="C25" s="189" t="s">
+        <v>266</v>
+      </c>
+      <c r="D25" s="189" t="s">
+        <v>287</v>
+      </c>
+      <c r="E25" s="191" t="s">
+        <v>288</v>
+      </c>
+      <c r="F25" s="199" t="s">
+        <v>198</v>
       </c>
     </row>
     <row r="26" ht="19.5" customHeight="1">
-      <c r="A26" s="186" t="s">
-        <v>260</v>
-      </c>
-      <c r="B26" s="179"/>
-      <c r="C26" s="179"/>
-      <c r="D26" s="179"/>
-      <c r="E26" s="179"/>
-      <c r="F26" s="182"/>
+      <c r="A26" s="181" t="s">
+        <v>291</v>
+      </c>
+      <c r="B26" s="175"/>
+      <c r="C26" s="175"/>
+      <c r="D26" s="175"/>
+      <c r="E26" s="175"/>
+      <c r="F26" s="177"/>
     </row>
     <row r="27" ht="42.0" customHeight="1">
-      <c r="A27" s="187">
+      <c r="A27" s="183">
         <v>19.0</v>
       </c>
-      <c r="B27" s="188" t="s">
-        <v>266</v>
-      </c>
-      <c r="C27" s="187" t="s">
-        <v>267</v>
-      </c>
-      <c r="D27" s="187" t="s">
-        <v>269</v>
-      </c>
-      <c r="E27" s="189" t="s">
-        <v>271</v>
-      </c>
-      <c r="F27" s="198" t="s">
-        <v>196</v>
+      <c r="B27" s="184" t="s">
+        <v>299</v>
+      </c>
+      <c r="C27" s="183" t="s">
+        <v>301</v>
+      </c>
+      <c r="D27" s="183" t="s">
+        <v>303</v>
+      </c>
+      <c r="E27" s="186" t="s">
+        <v>306</v>
+      </c>
+      <c r="F27" s="199" t="s">
+        <v>198</v>
       </c>
     </row>
     <row r="28" ht="42.0" customHeight="1">
-      <c r="A28" s="192">
+      <c r="A28" s="189">
         <v>20.0</v>
       </c>
-      <c r="B28" s="194" t="s">
-        <v>273</v>
-      </c>
-      <c r="C28" s="192" t="s">
-        <v>267</v>
-      </c>
-      <c r="D28" s="192" t="s">
-        <v>275</v>
-      </c>
-      <c r="E28" s="195" t="s">
-        <v>276</v>
-      </c>
-      <c r="F28" s="198" t="s">
-        <v>196</v>
+      <c r="B28" s="190" t="s">
+        <v>309</v>
+      </c>
+      <c r="C28" s="189" t="s">
+        <v>301</v>
+      </c>
+      <c r="D28" s="189" t="s">
+        <v>311</v>
+      </c>
+      <c r="E28" s="191" t="s">
+        <v>313</v>
+      </c>
+      <c r="F28" s="199" t="s">
+        <v>198</v>
       </c>
     </row>
     <row r="29" ht="42.0" customHeight="1">
-      <c r="A29" s="187">
+      <c r="A29" s="183">
         <v>21.0</v>
       </c>
-      <c r="B29" s="188" t="s">
-        <v>278</v>
-      </c>
-      <c r="C29" s="187" t="s">
-        <v>279</v>
-      </c>
-      <c r="D29" s="187" t="s">
-        <v>281</v>
-      </c>
-      <c r="E29" s="189" t="s">
-        <v>282</v>
-      </c>
-      <c r="F29" s="198" t="s">
-        <v>196</v>
+      <c r="B29" s="184" t="s">
+        <v>316</v>
+      </c>
+      <c r="C29" s="183" t="s">
+        <v>318</v>
+      </c>
+      <c r="D29" s="183" t="s">
+        <v>319</v>
+      </c>
+      <c r="E29" s="186" t="s">
+        <v>320</v>
+      </c>
+      <c r="F29" s="199" t="s">
+        <v>198</v>
       </c>
     </row>
     <row r="30" ht="19.5" customHeight="1">
-      <c r="A30" s="186" t="s">
-        <v>283</v>
-      </c>
-      <c r="B30" s="179"/>
-      <c r="C30" s="179"/>
-      <c r="D30" s="179"/>
-      <c r="E30" s="179"/>
-      <c r="F30" s="182"/>
+      <c r="A30" s="181" t="s">
+        <v>321</v>
+      </c>
+      <c r="B30" s="175"/>
+      <c r="C30" s="175"/>
+      <c r="D30" s="175"/>
+      <c r="E30" s="175"/>
+      <c r="F30" s="177"/>
     </row>
     <row r="31" ht="42.0" customHeight="1">
-      <c r="A31" s="192">
+      <c r="A31" s="189">
         <v>22.0</v>
       </c>
-      <c r="B31" s="194" t="s">
-        <v>287</v>
-      </c>
-      <c r="C31" s="192" t="s">
-        <v>289</v>
-      </c>
-      <c r="D31" s="192" t="s">
-        <v>291</v>
-      </c>
-      <c r="E31" s="195" t="s">
-        <v>292</v>
-      </c>
-      <c r="F31" s="196" t="s">
-        <v>165</v>
+      <c r="B31" s="190" t="s">
+        <v>331</v>
+      </c>
+      <c r="C31" s="189" t="s">
+        <v>334</v>
+      </c>
+      <c r="D31" s="189" t="s">
+        <v>335</v>
+      </c>
+      <c r="E31" s="191" t="s">
+        <v>337</v>
+      </c>
+      <c r="F31" s="194" t="s">
+        <v>169</v>
       </c>
     </row>
     <row r="32" ht="42.0" customHeight="1">
-      <c r="A32" s="187">
+      <c r="A32" s="183">
         <v>23.0</v>
       </c>
-      <c r="B32" s="188" t="s">
-        <v>294</v>
-      </c>
-      <c r="C32" s="187" t="s">
-        <v>296</v>
-      </c>
-      <c r="D32" s="187" t="s">
-        <v>297</v>
-      </c>
-      <c r="E32" s="189" t="s">
-        <v>299</v>
-      </c>
-      <c r="F32" s="198" t="s">
-        <v>196</v>
+      <c r="B32" s="184" t="s">
+        <v>340</v>
+      </c>
+      <c r="C32" s="183" t="s">
+        <v>341</v>
+      </c>
+      <c r="D32" s="183" t="s">
+        <v>343</v>
+      </c>
+      <c r="E32" s="186" t="s">
+        <v>345</v>
+      </c>
+      <c r="F32" s="199" t="s">
+        <v>198</v>
       </c>
     </row>
     <row r="33" ht="42.0" customHeight="1">
-      <c r="A33" s="192">
+      <c r="A33" s="189">
         <v>24.0</v>
       </c>
-      <c r="B33" s="194" t="s">
-        <v>303</v>
-      </c>
-      <c r="C33" s="192" t="s">
-        <v>304</v>
-      </c>
-      <c r="D33" s="192" t="s">
-        <v>306</v>
-      </c>
-      <c r="E33" s="195" t="s">
-        <v>308</v>
-      </c>
-      <c r="F33" s="198" t="s">
-        <v>196</v>
+      <c r="B33" s="190" t="s">
+        <v>349</v>
+      </c>
+      <c r="C33" s="189" t="s">
+        <v>351</v>
+      </c>
+      <c r="D33" s="189" t="s">
+        <v>353</v>
+      </c>
+      <c r="E33" s="191" t="s">
+        <v>355</v>
+      </c>
+      <c r="F33" s="199" t="s">
+        <v>198</v>
       </c>
     </row>
     <row r="34"/>
     <row r="35" ht="18.0" customHeight="1">
-      <c r="A35" s="206" t="s">
-        <v>312</v>
-      </c>
-      <c r="B35" s="179"/>
-      <c r="C35" s="179"/>
-      <c r="D35" s="179"/>
-      <c r="E35" s="179"/>
-      <c r="F35" s="182"/>
+      <c r="A35" s="211" t="s">
+        <v>361</v>
+      </c>
+      <c r="B35" s="175"/>
+      <c r="C35" s="175"/>
+      <c r="D35" s="175"/>
+      <c r="E35" s="175"/>
+      <c r="F35" s="177"/>
     </row>
     <row r="36" ht="18.0" customHeight="1">
-      <c r="A36" s="207" t="s">
-        <v>319</v>
-      </c>
-      <c r="B36" s="208" t="s">
-        <v>323</v>
-      </c>
-      <c r="C36" s="179"/>
-      <c r="D36" s="179"/>
-      <c r="E36" s="179"/>
-      <c r="F36" s="182"/>
+      <c r="A36" s="213" t="s">
+        <v>380</v>
+      </c>
+      <c r="B36" s="216" t="s">
+        <v>381</v>
+      </c>
+      <c r="C36" s="175"/>
+      <c r="D36" s="175"/>
+      <c r="E36" s="175"/>
+      <c r="F36" s="177"/>
     </row>
     <row r="37" ht="18.0" customHeight="1">
-      <c r="A37" s="210" t="s">
-        <v>330</v>
-      </c>
-      <c r="B37" s="208" t="s">
-        <v>340</v>
-      </c>
-      <c r="C37" s="179"/>
-      <c r="D37" s="179"/>
-      <c r="E37" s="179"/>
-      <c r="F37" s="182"/>
+      <c r="A37" s="219" t="s">
+        <v>382</v>
+      </c>
+      <c r="B37" s="216" t="s">
+        <v>383</v>
+      </c>
+      <c r="C37" s="175"/>
+      <c r="D37" s="175"/>
+      <c r="E37" s="175"/>
+      <c r="F37" s="177"/>
     </row>
     <row r="38" ht="18.0" customHeight="1">
-      <c r="A38" s="213" t="s">
-        <v>346</v>
-      </c>
-      <c r="B38" s="208" t="s">
-        <v>349</v>
-      </c>
-      <c r="C38" s="179"/>
-      <c r="D38" s="179"/>
-      <c r="E38" s="179"/>
-      <c r="F38" s="182"/>
+      <c r="A38" s="221" t="s">
+        <v>384</v>
+      </c>
+      <c r="B38" s="216" t="s">
+        <v>385</v>
+      </c>
+      <c r="C38" s="175"/>
+      <c r="D38" s="175"/>
+      <c r="E38" s="175"/>
+      <c r="F38" s="177"/>
     </row>
     <row r="39"/>
     <row r="40" ht="39.75" customHeight="1">
-      <c r="A40" s="214" t="s">
-        <v>357</v>
-      </c>
-      <c r="B40" s="179"/>
-      <c r="C40" s="179"/>
-      <c r="D40" s="179"/>
-      <c r="E40" s="179"/>
-      <c r="F40" s="182"/>
+      <c r="A40" s="224" t="s">
+        <v>386</v>
+      </c>
+      <c r="B40" s="175"/>
+      <c r="C40" s="175"/>
+      <c r="D40" s="175"/>
+      <c r="E40" s="175"/>
+      <c r="F40" s="177"/>
     </row>
     <row r="41"/>
     <row r="42"/>
